--- a/QSExt/Resource/TinySoftDBInfo.xlsx
+++ b/QSExt/Resource/TinySoftDBInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TableInfo" sheetId="2" r:id="rId1"/>
@@ -14795,7 +14795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -15032,7 +15032,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -16441,6 +16441,7 @@
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="2" width="33.875" customWidth="1"/>
     <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="189" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -16469,7 +16470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -16486,7 +16487,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -16503,7 +16504,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -16560,7 +16561,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -16577,7 +16578,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -16594,7 +16595,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -16611,7 +16612,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -17528,7 +17529,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -17545,7 +17546,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -17562,7 +17563,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -17599,7 +17600,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -17616,7 +17617,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -18553,7 +18554,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -18570,7 +18571,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -18590,7 +18591,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -18610,7 +18611,7 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -18630,7 +18631,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -19290,7 +19291,7 @@
         <v>10043</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -19310,7 +19311,7 @@
         <v>10044</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -19330,7 +19331,7 @@
         <v>10038</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -19350,7 +19351,7 @@
         <v>10039</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -19370,7 +19371,7 @@
         <v>10040</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -19390,7 +19391,7 @@
         <v>10041</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -19410,7 +19411,7 @@
         <v>10045</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -19430,7 +19431,7 @@
         <v>10046</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>23</v>
       </c>
@@ -19447,7 +19448,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -19564,7 +19565,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>23</v>
       </c>
@@ -19701,7 +19702,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:8">
       <c r="A166" t="s">
         <v>23</v>
       </c>
@@ -19718,7 +19719,7 @@
         <v>12018</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:8">
       <c r="A167" t="s">
         <v>23</v>
       </c>
@@ -19775,7 +19776,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:8">
       <c r="A170" t="s">
         <v>23</v>
       </c>
@@ -19792,7 +19793,7 @@
         <v>12023</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:8">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -19809,7 +19810,7 @@
         <v>12024</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:8">
       <c r="A172" t="s">
         <v>23</v>
       </c>
@@ -19826,7 +19827,7 @@
         <v>12025</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:8">
       <c r="A173" t="s">
         <v>23</v>
       </c>
@@ -19843,7 +19844,7 @@
         <v>12026</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
         <v>23</v>
       </c>
@@ -19860,7 +19861,7 @@
         <v>12027</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
         <v>23</v>
       </c>
@@ -19877,7 +19878,7 @@
         <v>12001</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:8">
       <c r="A176" t="s">
         <v>23</v>
       </c>
@@ -19894,7 +19895,7 @@
         <v>12002</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>23</v>
       </c>
@@ -19911,7 +19912,7 @@
         <v>12028</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -19928,7 +19929,7 @@
         <v>12029</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -19945,7 +19946,7 @@
         <v>12033</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>23</v>
       </c>
@@ -19962,7 +19963,7 @@
         <v>12034</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -19979,7 +19980,7 @@
         <v>12035</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>23</v>
       </c>
@@ -19996,7 +19997,7 @@
         <v>12036</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>23</v>
       </c>
@@ -20013,7 +20014,7 @@
         <v>12037</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>23</v>
       </c>
@@ -20250,7 +20251,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:8">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -20267,7 +20268,7 @@
         <v>12015</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:8">
       <c r="A197" t="s">
         <v>23</v>
       </c>
@@ -20284,7 +20285,7 @@
         <v>12048</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:8">
       <c r="A198" t="s">
         <v>23</v>
       </c>
@@ -20301,7 +20302,7 @@
         <v>12049</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
         <v>23</v>
       </c>
@@ -20318,7 +20319,7 @@
         <v>12050</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:8">
       <c r="A200" t="s">
         <v>23</v>
       </c>
@@ -20335,7 +20336,7 @@
         <v>12051</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
         <v>23</v>
       </c>
@@ -20352,7 +20353,7 @@
         <v>12052</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:8">
       <c r="A202" t="s">
         <v>23</v>
       </c>
@@ -20369,7 +20370,7 @@
         <v>12053</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:8">
       <c r="A203" t="s">
         <v>23</v>
       </c>
@@ -20686,7 +20687,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:8">
       <c r="A219" t="s">
         <v>23</v>
       </c>
@@ -20703,7 +20704,7 @@
         <v>12070</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:8">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -20720,7 +20721,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:8">
       <c r="A221" t="s">
         <v>25</v>
       </c>
@@ -20743,7 +20744,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:8">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -20763,7 +20764,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:8">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -20783,7 +20784,7 @@
         <v>14002</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:8">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -20803,7 +20804,7 @@
         <v>14003</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:8">
       <c r="A225" t="s">
         <v>29</v>
       </c>
@@ -20820,7 +20821,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:8">
       <c r="A226" t="s">
         <v>29</v>
       </c>
@@ -20840,7 +20841,7 @@
         <v>15001</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:8">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -20863,7 +20864,7 @@
         <v>15003</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:8">
       <c r="A228" t="s">
         <v>29</v>
       </c>
@@ -20883,7 +20884,7 @@
         <v>15004</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:8">
       <c r="A229" t="s">
         <v>29</v>
       </c>
@@ -20903,7 +20904,7 @@
         <v>15005</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:8">
       <c r="A230" t="s">
         <v>31</v>
       </c>
@@ -20920,7 +20921,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:8">
       <c r="A231" t="s">
         <v>31</v>
       </c>
@@ -20943,7 +20944,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:8">
       <c r="A232" t="s">
         <v>31</v>
       </c>
@@ -21239,7 +21240,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:8">
       <c r="A245" t="s">
         <v>31</v>
       </c>
@@ -21489,7 +21490,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:8">
       <c r="A256" t="s">
         <v>31</v>
       </c>
@@ -21509,7 +21510,7 @@
         <v>16042</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:8">
       <c r="A257" t="s">
         <v>33</v>
       </c>
@@ -21526,7 +21527,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:8">
       <c r="A258" t="s">
         <v>33</v>
       </c>
@@ -21549,7 +21550,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:8">
       <c r="A259" t="s">
         <v>33</v>
       </c>
@@ -21569,7 +21570,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:8">
       <c r="A260" t="s">
         <v>33</v>
       </c>
@@ -21635,7 +21636,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:8">
       <c r="A263" t="s">
         <v>35</v>
       </c>
@@ -21652,7 +21653,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:8">
       <c r="A264" t="s">
         <v>35</v>
       </c>
@@ -21672,7 +21673,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:8">
       <c r="A265" t="s">
         <v>35</v>
       </c>
@@ -21692,7 +21693,7 @@
         <v>18001</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:8">
       <c r="A266" t="s">
         <v>35</v>
       </c>
@@ -21712,7 +21713,7 @@
         <v>18002</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:8">
       <c r="A267" t="s">
         <v>35</v>
       </c>
@@ -21732,7 +21733,7 @@
         <v>18003</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:8">
       <c r="A268" t="s">
         <v>35</v>
       </c>
@@ -21752,7 +21753,7 @@
         <v>18004</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:8">
       <c r="A269" t="s">
         <v>35</v>
       </c>
@@ -21772,7 +21773,7 @@
         <v>18005</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:8">
       <c r="A270" t="s">
         <v>35</v>
       </c>
@@ -21933,7 +21934,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:8">
       <c r="A277" t="s">
         <v>35</v>
       </c>
@@ -21953,7 +21954,7 @@
         <v>18012</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:8">
       <c r="A278" t="s">
         <v>35</v>
       </c>
@@ -21973,7 +21974,7 @@
         <v>18013</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:8">
       <c r="A279" t="s">
         <v>35</v>
       </c>
@@ -21993,7 +21994,7 @@
         <v>18015</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:8">
       <c r="A280" t="s">
         <v>35</v>
       </c>
@@ -22013,7 +22014,7 @@
         <v>18014</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:8">
       <c r="A281" t="s">
         <v>39</v>
       </c>
@@ -22030,7 +22031,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:8">
       <c r="A282" t="s">
         <v>39</v>
       </c>
@@ -22053,7 +22054,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:8">
       <c r="A283" t="s">
         <v>39</v>
       </c>
@@ -22073,7 +22074,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:8">
       <c r="A284" t="s">
         <v>39</v>
       </c>
@@ -22116,7 +22117,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:8">
       <c r="A286" t="s">
         <v>39</v>
       </c>
@@ -22136,7 +22137,7 @@
         <v>20008</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:8">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -22202,7 +22203,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:8">
       <c r="A290" t="s">
         <v>39</v>
       </c>
@@ -22314,7 +22315,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:8">
       <c r="A295" t="s">
         <v>39</v>
       </c>
@@ -22334,7 +22335,7 @@
         <v>20030</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:8">
       <c r="A296" t="s">
         <v>39</v>
       </c>
@@ -22354,7 +22355,7 @@
         <v>20031</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:8">
       <c r="A297" t="s">
         <v>39</v>
       </c>
@@ -22374,7 +22375,7 @@
         <v>20032</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:8">
       <c r="A298" t="s">
         <v>39</v>
       </c>
@@ -22394,7 +22395,7 @@
         <v>20033</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:8">
       <c r="A299" t="s">
         <v>39</v>
       </c>
@@ -22414,7 +22415,7 @@
         <v>20034</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:8">
       <c r="A300" t="s">
         <v>39</v>
       </c>
@@ -22434,7 +22435,7 @@
         <v>20036</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:8">
       <c r="A301" t="s">
         <v>39</v>
       </c>
@@ -22500,7 +22501,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:8">
       <c r="A304" t="s">
         <v>39</v>
       </c>
@@ -22520,7 +22521,7 @@
         <v>20043</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:8">
       <c r="A305" t="s">
         <v>39</v>
       </c>
@@ -22540,7 +22541,7 @@
         <v>20044</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:8">
       <c r="A306" t="s">
         <v>39</v>
       </c>
@@ -22560,7 +22561,7 @@
         <v>20069</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:8">
       <c r="A307" t="s">
         <v>40</v>
       </c>
@@ -22577,7 +22578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:8">
       <c r="A308" t="s">
         <v>40</v>
       </c>
@@ -22600,7 +22601,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:8">
       <c r="A309" t="s">
         <v>40</v>
       </c>
@@ -22620,7 +22621,7 @@
         <v>22001</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:8">
       <c r="A310" t="s">
         <v>40</v>
       </c>
@@ -22640,7 +22641,7 @@
         <v>22002</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:8">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -22660,7 +22661,7 @@
         <v>22003</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:8">
       <c r="A312" t="s">
         <v>40</v>
       </c>
@@ -22703,7 +22704,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:8">
       <c r="A314" t="s">
         <v>40</v>
       </c>
@@ -22723,7 +22724,7 @@
         <v>22006</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:8">
       <c r="A315" t="s">
         <v>40</v>
       </c>
@@ -22743,7 +22744,7 @@
         <v>22007</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:8">
       <c r="A316" t="s">
         <v>40</v>
       </c>
@@ -22763,7 +22764,7 @@
         <v>22008</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:8">
       <c r="A317" t="s">
         <v>40</v>
       </c>
@@ -22783,7 +22784,7 @@
         <v>22009</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:8">
       <c r="A318" t="s">
         <v>40</v>
       </c>
@@ -22826,7 +22827,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:8">
       <c r="A320" t="s">
         <v>40</v>
       </c>
@@ -23166,7 +23167,7 @@
         <v>22028</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:8">
       <c r="A337" t="s">
         <v>40</v>
       </c>
@@ -23186,7 +23187,7 @@
         <v>22029</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:8">
       <c r="A338" t="s">
         <v>40</v>
       </c>
@@ -23206,7 +23207,7 @@
         <v>22030</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:8">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -23226,7 +23227,7 @@
         <v>22031</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:8">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -23384,7 +23385,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:8">
       <c r="A347" t="s">
         <v>40</v>
       </c>
@@ -23404,7 +23405,7 @@
         <v>22039</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:8">
       <c r="A348" t="s">
         <v>40</v>
       </c>
@@ -23907,7 +23908,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:8">
       <c r="A370" t="s">
         <v>40</v>
       </c>
@@ -24019,7 +24020,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:8">
       <c r="A375" t="s">
         <v>41</v>
       </c>
@@ -24036,7 +24037,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:8">
       <c r="A376" t="s">
         <v>41</v>
       </c>
@@ -24082,7 +24083,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:8">
       <c r="A378" t="s">
         <v>41</v>
       </c>
@@ -24102,7 +24103,7 @@
         <v>24002</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:8">
       <c r="A379" t="s">
         <v>41</v>
       </c>
@@ -24168,7 +24169,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:8">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -24188,7 +24189,7 @@
         <v>24006</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:8">
       <c r="A383" t="s">
         <v>41</v>
       </c>
@@ -24208,7 +24209,7 @@
         <v>24007</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:8">
       <c r="A384" t="s">
         <v>41</v>
       </c>
@@ -24228,7 +24229,7 @@
         <v>24008</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:8">
       <c r="A385" t="s">
         <v>41</v>
       </c>
@@ -24248,7 +24249,7 @@
         <v>24009</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:8">
       <c r="A386" t="s">
         <v>41</v>
       </c>
@@ -24360,7 +24361,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:8">
       <c r="A391" t="s">
         <v>41</v>
       </c>
@@ -24380,7 +24381,7 @@
         <v>24015</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:8">
       <c r="A392" t="s">
         <v>42</v>
       </c>
@@ -24397,7 +24398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:8">
       <c r="A393" t="s">
         <v>42</v>
       </c>
@@ -24443,7 +24444,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:8">
       <c r="A395" t="s">
         <v>42</v>
       </c>
@@ -24463,7 +24464,7 @@
         <v>26002</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:8">
       <c r="A396" t="s">
         <v>42</v>
       </c>
@@ -24529,7 +24530,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:8">
       <c r="A399" t="s">
         <v>42</v>
       </c>
@@ -24549,7 +24550,7 @@
         <v>26006</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:8">
       <c r="A400" t="s">
         <v>42</v>
       </c>
@@ -24569,7 +24570,7 @@
         <v>26007</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:8">
       <c r="A401" t="s">
         <v>42</v>
       </c>
@@ -24589,7 +24590,7 @@
         <v>26008</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:8">
       <c r="A402" t="s">
         <v>42</v>
       </c>
@@ -24609,7 +24610,7 @@
         <v>26009</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:8">
       <c r="A403" t="s">
         <v>42</v>
       </c>
@@ -24721,7 +24722,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:8">
       <c r="A408" t="s">
         <v>42</v>
       </c>
@@ -24741,7 +24742,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:8">
       <c r="A409" t="s">
         <v>43</v>
       </c>
@@ -24758,7 +24759,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" spans="1:8">
       <c r="A410" t="s">
         <v>43</v>
       </c>
@@ -24781,7 +24782,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" spans="1:8">
       <c r="A411" t="s">
         <v>43</v>
       </c>
@@ -24801,7 +24802,7 @@
         <v>27001</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:8">
       <c r="A412" t="s">
         <v>43</v>
       </c>
@@ -24821,7 +24822,7 @@
         <v>27002</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" spans="1:8">
       <c r="A413" t="s">
         <v>43</v>
       </c>
@@ -24841,7 +24842,7 @@
         <v>27003</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" spans="1:8">
       <c r="A414" t="s">
         <v>43</v>
       </c>
@@ -24861,7 +24862,7 @@
         <v>27004</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:8">
       <c r="A415" t="s">
         <v>43</v>
       </c>
@@ -24881,7 +24882,7 @@
         <v>27005</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:8">
       <c r="A416" t="s">
         <v>43</v>
       </c>
@@ -26181,7 +26182,7 @@
         <v>27070</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" spans="1:8">
       <c r="A481" t="s">
         <v>43</v>
       </c>
@@ -26201,7 +26202,7 @@
         <v>27071</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" spans="1:8">
       <c r="A482" t="s">
         <v>43</v>
       </c>
@@ -26221,7 +26222,7 @@
         <v>27072</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" spans="1:8">
       <c r="A483" t="s">
         <v>43</v>
       </c>
@@ -26241,7 +26242,7 @@
         <v>27073</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" spans="1:8">
       <c r="A484" t="s">
         <v>43</v>
       </c>
@@ -26261,7 +26262,7 @@
         <v>27074</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" spans="1:8">
       <c r="A485" t="s">
         <v>43</v>
       </c>
@@ -26281,7 +26282,7 @@
         <v>27075</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" spans="1:8">
       <c r="A486" t="s">
         <v>43</v>
       </c>
@@ -26301,7 +26302,7 @@
         <v>27076</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" spans="1:8">
       <c r="A487" t="s">
         <v>43</v>
       </c>
@@ -26321,7 +26322,7 @@
         <v>27077</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" spans="1:8">
       <c r="A488" t="s">
         <v>43</v>
       </c>
@@ -26341,7 +26342,7 @@
         <v>27078</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" spans="1:8">
       <c r="A489" t="s">
         <v>43</v>
       </c>
@@ -26361,7 +26362,7 @@
         <v>27079</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" spans="1:8">
       <c r="A490" t="s">
         <v>43</v>
       </c>
@@ -26381,7 +26382,7 @@
         <v>27080</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:8">
       <c r="A491" t="s">
         <v>44</v>
       </c>
@@ -26398,7 +26399,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" spans="1:8">
       <c r="A492" t="s">
         <v>44</v>
       </c>
@@ -26421,7 +26422,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" spans="1:8">
       <c r="A493" t="s">
         <v>44</v>
       </c>
@@ -26464,7 +26465,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" spans="1:8">
       <c r="A495" t="s">
         <v>44</v>
       </c>
@@ -26484,7 +26485,7 @@
         <v>28003</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:8">
       <c r="A496" t="s">
         <v>45</v>
       </c>
@@ -26501,7 +26502,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" spans="1:8">
       <c r="A497" t="s">
         <v>45</v>
       </c>
@@ -26524,7 +26525,7 @@
         <v>29001</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" spans="1:8">
       <c r="A498" t="s">
         <v>45</v>
       </c>
@@ -26544,7 +26545,7 @@
         <v>29002</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" spans="1:8">
       <c r="A499" t="s">
         <v>45</v>
       </c>
@@ -26564,7 +26565,7 @@
         <v>29003</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" spans="1:8">
       <c r="A500" t="s">
         <v>45</v>
       </c>
@@ -26584,7 +26585,7 @@
         <v>29004</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" spans="1:8">
       <c r="A501" t="s">
         <v>45</v>
       </c>
@@ -26627,7 +26628,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:8">
       <c r="A503" t="s">
         <v>46</v>
       </c>
@@ -26644,7 +26645,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" spans="1:8">
       <c r="A504" t="s">
         <v>46</v>
       </c>
@@ -26667,7 +26668,7 @@
         <v>30001</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" spans="1:8">
       <c r="A505" t="s">
         <v>46</v>
       </c>
@@ -26690,7 +26691,7 @@
         <v>30002</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" spans="1:8">
       <c r="A506" t="s">
         <v>46</v>
       </c>
@@ -26710,7 +26711,7 @@
         <v>30003</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" spans="1:8">
       <c r="A507" t="s">
         <v>46</v>
       </c>
@@ -26730,7 +26731,7 @@
         <v>30004</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" spans="1:8">
       <c r="A508" t="s">
         <v>46</v>
       </c>
@@ -26750,7 +26751,7 @@
         <v>30005</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" spans="1:8">
       <c r="A509" t="s">
         <v>46</v>
       </c>
@@ -26770,7 +26771,7 @@
         <v>30006</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" spans="1:8">
       <c r="A510" t="s">
         <v>46</v>
       </c>
@@ -26790,7 +26791,7 @@
         <v>30007</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" spans="1:8">
       <c r="A511" t="s">
         <v>46</v>
       </c>
@@ -26810,7 +26811,7 @@
         <v>30008</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" spans="1:8">
       <c r="A512" t="s">
         <v>46</v>
       </c>
@@ -26991,7 +26992,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" spans="1:8">
       <c r="A520" t="s">
         <v>46</v>
       </c>
@@ -27011,7 +27012,7 @@
         <v>30017</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" spans="1:8">
       <c r="A521" t="s">
         <v>46</v>
       </c>
@@ -27031,7 +27032,7 @@
         <v>30018</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:8">
       <c r="A522" t="s">
         <v>48</v>
       </c>
@@ -27048,7 +27049,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" spans="1:8">
       <c r="A523" t="s">
         <v>48</v>
       </c>
@@ -27068,7 +27069,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" spans="1:8">
       <c r="A524" t="s">
         <v>48</v>
       </c>
@@ -27091,7 +27092,7 @@
         <v>40001</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" spans="1:8">
       <c r="A525" t="s">
         <v>48</v>
       </c>
@@ -27111,7 +27112,7 @@
         <v>40002</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" spans="1:8">
       <c r="A526" t="s">
         <v>48</v>
       </c>
@@ -27177,7 +27178,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" spans="1:8">
       <c r="A529" t="s">
         <v>48</v>
       </c>
@@ -27197,7 +27198,7 @@
         <v>40007</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" spans="1:8">
       <c r="A530" t="s">
         <v>48</v>
       </c>
@@ -27217,7 +27218,7 @@
         <v>40008</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" spans="1:8">
       <c r="A531" t="s">
         <v>48</v>
       </c>
@@ -27237,7 +27238,7 @@
         <v>40009</v>
       </c>
     </row>
-    <row r="532" spans="1:7">
+    <row r="532" spans="1:8">
       <c r="A532" t="s">
         <v>48</v>
       </c>
@@ -27257,7 +27258,7 @@
         <v>40011</v>
       </c>
     </row>
-    <row r="533" spans="1:7">
+    <row r="533" spans="1:8">
       <c r="A533" t="s">
         <v>48</v>
       </c>
@@ -27277,7 +27278,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" spans="1:8">
       <c r="A534" t="s">
         <v>48</v>
       </c>
@@ -27297,7 +27298,7 @@
         <v>40004</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:8">
       <c r="A535" t="s">
         <v>49</v>
       </c>
@@ -27314,7 +27315,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
+    <row r="536" spans="1:8">
       <c r="A536" t="s">
         <v>49</v>
       </c>
@@ -27334,7 +27335,7 @@
         <v>41001</v>
       </c>
     </row>
-    <row r="537" spans="1:7">
+    <row r="537" spans="1:8">
       <c r="A537" t="s">
         <v>49</v>
       </c>
@@ -27587,7 +27588,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:8">
       <c r="A548" t="s">
         <v>50</v>
       </c>
@@ -27604,7 +27605,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" spans="1:8">
       <c r="A549" t="s">
         <v>50</v>
       </c>
@@ -27627,7 +27628,7 @@
         <v>122001</v>
       </c>
     </row>
-    <row r="550" spans="1:7">
+    <row r="550" spans="1:8">
       <c r="A550" t="s">
         <v>50</v>
       </c>
@@ -27647,7 +27648,7 @@
         <v>122002</v>
       </c>
     </row>
-    <row r="551" spans="1:7">
+    <row r="551" spans="1:8">
       <c r="A551" t="s">
         <v>50</v>
       </c>
@@ -27667,7 +27668,7 @@
         <v>122003</v>
       </c>
     </row>
-    <row r="552" spans="1:7">
+    <row r="552" spans="1:8">
       <c r="A552" t="s">
         <v>50</v>
       </c>
@@ -27687,7 +27688,7 @@
         <v>122004</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:8">
       <c r="A553" t="s">
         <v>51</v>
       </c>
@@ -27704,7 +27705,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="554" spans="1:7">
+    <row r="554" spans="1:8">
       <c r="A554" t="s">
         <v>51</v>
       </c>
@@ -27796,7 +27797,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="558" spans="1:7">
+    <row r="558" spans="1:8">
       <c r="A558" t="s">
         <v>51</v>
       </c>
@@ -27816,7 +27817,7 @@
         <v>124005</v>
       </c>
     </row>
-    <row r="559" spans="1:7">
+    <row r="559" spans="1:8">
       <c r="A559" t="s">
         <v>51</v>
       </c>
@@ -27836,7 +27837,7 @@
         <v>124006</v>
       </c>
     </row>
-    <row r="560" spans="1:7">
+    <row r="560" spans="1:8">
       <c r="A560" t="s">
         <v>51</v>
       </c>
@@ -27856,7 +27857,7 @@
         <v>124007</v>
       </c>
     </row>
-    <row r="561" spans="1:7">
+    <row r="561" spans="1:8">
       <c r="A561" t="s">
         <v>51</v>
       </c>
@@ -27876,7 +27877,7 @@
         <v>124008</v>
       </c>
     </row>
-    <row r="562" spans="1:7">
+    <row r="562" spans="1:8">
       <c r="A562" t="s">
         <v>51</v>
       </c>
@@ -27896,7 +27897,7 @@
         <v>124009</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:8">
       <c r="A563" t="s">
         <v>52</v>
       </c>
@@ -27913,7 +27914,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="564" spans="1:7">
+    <row r="564" spans="1:8">
       <c r="A564" t="s">
         <v>52</v>
       </c>
@@ -28120,7 +28121,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:8">
       <c r="A573" t="s">
         <v>53</v>
       </c>
@@ -28137,7 +28138,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="574" spans="1:7">
+    <row r="574" spans="1:8">
       <c r="A574" t="s">
         <v>53</v>
       </c>
@@ -28160,7 +28161,7 @@
         <v>127001</v>
       </c>
     </row>
-    <row r="575" spans="1:7">
+    <row r="575" spans="1:8">
       <c r="A575" t="s">
         <v>53</v>
       </c>
@@ -28180,7 +28181,7 @@
         <v>127002</v>
       </c>
     </row>
-    <row r="576" spans="1:7">
+    <row r="576" spans="1:8">
       <c r="A576" t="s">
         <v>53</v>
       </c>
@@ -28263,7 +28264,7 @@
         <v>127006</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:7">
       <c r="A580" t="s">
         <v>54</v>
       </c>
@@ -28503,7 +28504,7 @@
         <v>129011</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:7">
       <c r="A592" t="s">
         <v>55</v>
       </c>
@@ -28520,7 +28521,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="593" spans="1:7">
+    <row r="593" spans="1:8">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -28773,7 +28774,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="604" spans="1:5">
+    <row r="604" spans="1:8">
       <c r="A604" t="s">
         <v>57</v>
       </c>
@@ -28790,7 +28791,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="605" spans="1:7">
+    <row r="605" spans="1:8">
       <c r="A605" t="s">
         <v>57</v>
       </c>
@@ -28813,7 +28814,7 @@
         <v>131001</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" spans="1:8">
       <c r="A606" t="s">
         <v>57</v>
       </c>
@@ -28833,7 +28834,7 @@
         <v>131002</v>
       </c>
     </row>
-    <row r="607" spans="1:7">
+    <row r="607" spans="1:8">
       <c r="A607" t="s">
         <v>57</v>
       </c>
@@ -28922,7 +28923,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="611" spans="1:7">
+    <row r="611" spans="1:8">
       <c r="A611" t="s">
         <v>57</v>
       </c>
@@ -28945,7 +28946,7 @@
         <v>131007</v>
       </c>
     </row>
-    <row r="612" spans="1:5">
+    <row r="612" spans="1:8">
       <c r="A612" t="s">
         <v>58</v>
       </c>
@@ -28962,7 +28963,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="613" spans="1:7">
+    <row r="613" spans="1:8">
       <c r="A613" t="s">
         <v>58</v>
       </c>
@@ -28985,7 +28986,7 @@
         <v>132001</v>
       </c>
     </row>
-    <row r="614" spans="1:7">
+    <row r="614" spans="1:8">
       <c r="A614" t="s">
         <v>58</v>
       </c>
@@ -29028,7 +29029,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="616" spans="1:5">
+    <row r="616" spans="1:8">
       <c r="A616" t="s">
         <v>64</v>
       </c>
@@ -29045,7 +29046,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="617" spans="1:7">
+    <row r="617" spans="1:8">
       <c r="A617" t="s">
         <v>64</v>
       </c>
@@ -29065,7 +29066,7 @@
         <v>302000</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" spans="1:8">
       <c r="A618" t="s">
         <v>64</v>
       </c>
@@ -29085,7 +29086,7 @@
         <v>302001</v>
       </c>
     </row>
-    <row r="619" spans="1:7">
+    <row r="619" spans="1:8">
       <c r="A619" t="s">
         <v>64</v>
       </c>
@@ -29105,7 +29106,7 @@
         <v>302002</v>
       </c>
     </row>
-    <row r="620" spans="1:7">
+    <row r="620" spans="1:8">
       <c r="A620" t="s">
         <v>64</v>
       </c>
@@ -29125,7 +29126,7 @@
         <v>302003</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
+    <row r="621" spans="1:8">
       <c r="A621" t="s">
         <v>64</v>
       </c>
@@ -29237,7 +29238,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="626" spans="1:7">
+    <row r="626" spans="1:8">
       <c r="A626" t="s">
         <v>64</v>
       </c>
@@ -29257,7 +29258,7 @@
         <v>302009</v>
       </c>
     </row>
-    <row r="627" spans="1:7">
+    <row r="627" spans="1:8">
       <c r="A627" t="s">
         <v>64</v>
       </c>
@@ -29323,7 +29324,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="630" spans="1:7">
+    <row r="630" spans="1:8">
       <c r="A630" t="s">
         <v>64</v>
       </c>
@@ -29343,7 +29344,7 @@
         <v>302013</v>
       </c>
     </row>
-    <row r="631" spans="1:7">
+    <row r="631" spans="1:8">
       <c r="A631" t="s">
         <v>64</v>
       </c>
@@ -29363,7 +29364,7 @@
         <v>302014</v>
       </c>
     </row>
-    <row r="632" spans="1:7">
+    <row r="632" spans="1:8">
       <c r="A632" t="s">
         <v>64</v>
       </c>
@@ -29383,7 +29384,7 @@
         <v>302015</v>
       </c>
     </row>
-    <row r="633" spans="1:7">
+    <row r="633" spans="1:8">
       <c r="A633" t="s">
         <v>64</v>
       </c>
@@ -29403,7 +29404,7 @@
         <v>302016</v>
       </c>
     </row>
-    <row r="634" spans="1:7">
+    <row r="634" spans="1:8">
       <c r="A634" t="s">
         <v>64</v>
       </c>
@@ -29469,7 +29470,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="637" spans="1:7">
+    <row r="637" spans="1:8">
       <c r="A637" t="s">
         <v>64</v>
       </c>
@@ -29512,7 +29513,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="639" spans="1:7">
+    <row r="639" spans="1:8">
       <c r="A639" t="s">
         <v>64</v>
       </c>
@@ -29532,7 +29533,7 @@
         <v>302021</v>
       </c>
     </row>
-    <row r="640" spans="1:7">
+    <row r="640" spans="1:8">
       <c r="A640" t="s">
         <v>64</v>
       </c>
@@ -29872,7 +29873,7 @@
         <v>302038</v>
       </c>
     </row>
-    <row r="657" spans="1:7">
+    <row r="657" spans="1:8">
       <c r="A657" t="s">
         <v>64</v>
       </c>
@@ -29892,7 +29893,7 @@
         <v>302040</v>
       </c>
     </row>
-    <row r="658" spans="1:7">
+    <row r="658" spans="1:8">
       <c r="A658" t="s">
         <v>64</v>
       </c>
@@ -29912,7 +29913,7 @@
         <v>302042</v>
       </c>
     </row>
-    <row r="659" spans="1:7">
+    <row r="659" spans="1:8">
       <c r="A659" t="s">
         <v>64</v>
       </c>
@@ -29932,7 +29933,7 @@
         <v>302043</v>
       </c>
     </row>
-    <row r="660" spans="1:7">
+    <row r="660" spans="1:8">
       <c r="A660" t="s">
         <v>64</v>
       </c>
@@ -29952,7 +29953,7 @@
         <v>302044</v>
       </c>
     </row>
-    <row r="661" spans="1:7">
+    <row r="661" spans="1:8">
       <c r="A661" t="s">
         <v>64</v>
       </c>
@@ -29972,7 +29973,7 @@
         <v>302045</v>
       </c>
     </row>
-    <row r="662" spans="1:7">
+    <row r="662" spans="1:8">
       <c r="A662" t="s">
         <v>64</v>
       </c>
@@ -29992,7 +29993,7 @@
         <v>302046</v>
       </c>
     </row>
-    <row r="663" spans="1:7">
+    <row r="663" spans="1:8">
       <c r="A663" t="s">
         <v>64</v>
       </c>
@@ -30012,7 +30013,7 @@
         <v>302047</v>
       </c>
     </row>
-    <row r="664" spans="1:5">
+    <row r="664" spans="1:8">
       <c r="A664" t="s">
         <v>66</v>
       </c>
@@ -30029,7 +30030,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="665" spans="1:7">
+    <row r="665" spans="1:8">
       <c r="A665" t="s">
         <v>66</v>
       </c>
@@ -30049,7 +30050,7 @@
         <v>303010</v>
       </c>
     </row>
-    <row r="666" spans="1:7">
+    <row r="666" spans="1:8">
       <c r="A666" t="s">
         <v>66</v>
       </c>
@@ -30069,7 +30070,7 @@
         <v>303001</v>
       </c>
     </row>
-    <row r="667" spans="1:7">
+    <row r="667" spans="1:8">
       <c r="A667" t="s">
         <v>66</v>
       </c>
@@ -30135,7 +30136,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="670" spans="1:7">
+    <row r="670" spans="1:8">
       <c r="A670" t="s">
         <v>66</v>
       </c>
@@ -30178,7 +30179,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="672" spans="1:7">
+    <row r="672" spans="1:8">
       <c r="A672" t="s">
         <v>66</v>
       </c>
@@ -30238,7 +30239,7 @@
         <v>303009</v>
       </c>
     </row>
-    <row r="675" spans="1:5">
+    <row r="675" spans="1:7">
       <c r="A675" t="s">
         <v>67</v>
       </c>
@@ -30515,7 +30516,7 @@
         <v>305013</v>
       </c>
     </row>
-    <row r="689" spans="1:7">
+    <row r="689" spans="1:8">
       <c r="A689" t="s">
         <v>67</v>
       </c>
@@ -30535,7 +30536,7 @@
         <v>305014</v>
       </c>
     </row>
-    <row r="690" spans="1:7">
+    <row r="690" spans="1:8">
       <c r="A690" t="s">
         <v>67</v>
       </c>
@@ -30555,7 +30556,7 @@
         <v>305015</v>
       </c>
     </row>
-    <row r="691" spans="1:7">
+    <row r="691" spans="1:8">
       <c r="A691" t="s">
         <v>67</v>
       </c>
@@ -30575,7 +30576,7 @@
         <v>305016</v>
       </c>
     </row>
-    <row r="692" spans="1:7">
+    <row r="692" spans="1:8">
       <c r="A692" t="s">
         <v>67</v>
       </c>
@@ -30595,7 +30596,7 @@
         <v>305017</v>
       </c>
     </row>
-    <row r="693" spans="1:7">
+    <row r="693" spans="1:8">
       <c r="A693" t="s">
         <v>67</v>
       </c>
@@ -30615,7 +30616,7 @@
         <v>305018</v>
       </c>
     </row>
-    <row r="694" spans="1:7">
+    <row r="694" spans="1:8">
       <c r="A694" t="s">
         <v>67</v>
       </c>
@@ -30635,7 +30636,7 @@
         <v>305019</v>
       </c>
     </row>
-    <row r="695" spans="1:7">
+    <row r="695" spans="1:8">
       <c r="A695" t="s">
         <v>67</v>
       </c>
@@ -30655,7 +30656,7 @@
         <v>305020</v>
       </c>
     </row>
-    <row r="696" spans="1:7">
+    <row r="696" spans="1:8">
       <c r="A696" t="s">
         <v>67</v>
       </c>
@@ -30675,7 +30676,7 @@
         <v>305021</v>
       </c>
     </row>
-    <row r="697" spans="1:5">
+    <row r="697" spans="1:8">
       <c r="A697" t="s">
         <v>68</v>
       </c>
@@ -30692,7 +30693,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="698" spans="1:7">
+    <row r="698" spans="1:8">
       <c r="A698" t="s">
         <v>68</v>
       </c>
@@ -30712,7 +30713,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="699" spans="1:7">
+    <row r="699" spans="1:8">
       <c r="A699" t="s">
         <v>68</v>
       </c>
@@ -30732,7 +30733,7 @@
         <v>308001</v>
       </c>
     </row>
-    <row r="700" spans="1:7">
+    <row r="700" spans="1:8">
       <c r="A700" t="s">
         <v>68</v>
       </c>
@@ -30752,7 +30753,7 @@
         <v>308002</v>
       </c>
     </row>
-    <row r="701" spans="1:7">
+    <row r="701" spans="1:8">
       <c r="A701" t="s">
         <v>68</v>
       </c>
@@ -30772,7 +30773,7 @@
         <v>308003</v>
       </c>
     </row>
-    <row r="702" spans="1:7">
+    <row r="702" spans="1:8">
       <c r="A702" t="s">
         <v>68</v>
       </c>
@@ -30792,7 +30793,7 @@
         <v>308004</v>
       </c>
     </row>
-    <row r="703" spans="1:7">
+    <row r="703" spans="1:8">
       <c r="A703" t="s">
         <v>68</v>
       </c>
@@ -30835,7 +30836,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="705" spans="1:7">
+    <row r="705" spans="1:8">
       <c r="A705" t="s">
         <v>68</v>
       </c>
@@ -30855,7 +30856,7 @@
         <v>308007</v>
       </c>
     </row>
-    <row r="706" spans="1:7">
+    <row r="706" spans="1:8">
       <c r="A706" t="s">
         <v>68</v>
       </c>
@@ -30898,7 +30899,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="708" spans="1:7">
+    <row r="708" spans="1:8">
       <c r="A708" t="s">
         <v>68</v>
       </c>
@@ -30921,7 +30922,7 @@
         <v>308010</v>
       </c>
     </row>
-    <row r="709" spans="1:7">
+    <row r="709" spans="1:8">
       <c r="A709" t="s">
         <v>68</v>
       </c>
@@ -30944,7 +30945,7 @@
         <v>308011</v>
       </c>
     </row>
-    <row r="710" spans="1:7">
+    <row r="710" spans="1:8">
       <c r="A710" t="s">
         <v>68</v>
       </c>
@@ -30964,7 +30965,7 @@
         <v>308012</v>
       </c>
     </row>
-    <row r="711" spans="1:7">
+    <row r="711" spans="1:8">
       <c r="A711" t="s">
         <v>68</v>
       </c>
@@ -30984,7 +30985,7 @@
         <v>308013</v>
       </c>
     </row>
-    <row r="712" spans="1:7">
+    <row r="712" spans="1:8">
       <c r="A712" t="s">
         <v>68</v>
       </c>
@@ -31004,7 +31005,7 @@
         <v>308014</v>
       </c>
     </row>
-    <row r="713" spans="1:5">
+    <row r="713" spans="1:8">
       <c r="A713" t="s">
         <v>69</v>
       </c>
@@ -31021,7 +31022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="714" spans="1:7">
+    <row r="714" spans="1:8">
       <c r="A714" t="s">
         <v>69</v>
       </c>
@@ -31041,7 +31042,7 @@
         <v>309000</v>
       </c>
     </row>
-    <row r="715" spans="1:7">
+    <row r="715" spans="1:8">
       <c r="A715" t="s">
         <v>69</v>
       </c>
@@ -31064,7 +31065,7 @@
         <v>309001</v>
       </c>
     </row>
-    <row r="716" spans="1:7">
+    <row r="716" spans="1:8">
       <c r="A716" t="s">
         <v>69</v>
       </c>
@@ -31084,7 +31085,7 @@
         <v>309002</v>
       </c>
     </row>
-    <row r="717" spans="1:7">
+    <row r="717" spans="1:8">
       <c r="A717" t="s">
         <v>69</v>
       </c>
@@ -31104,7 +31105,7 @@
         <v>309003</v>
       </c>
     </row>
-    <row r="718" spans="1:7">
+    <row r="718" spans="1:8">
       <c r="A718" t="s">
         <v>69</v>
       </c>
@@ -31170,7 +31171,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="721" spans="1:7">
+    <row r="721" spans="1:8">
       <c r="A721" t="s">
         <v>69</v>
       </c>
@@ -31190,7 +31191,7 @@
         <v>309007</v>
       </c>
     </row>
-    <row r="722" spans="1:7">
+    <row r="722" spans="1:8">
       <c r="A722" t="s">
         <v>69</v>
       </c>
@@ -31210,7 +31211,7 @@
         <v>309008</v>
       </c>
     </row>
-    <row r="723" spans="1:7">
+    <row r="723" spans="1:8">
       <c r="A723" t="s">
         <v>69</v>
       </c>
@@ -31230,7 +31231,7 @@
         <v>309009</v>
       </c>
     </row>
-    <row r="724" spans="1:7">
+    <row r="724" spans="1:8">
       <c r="A724" t="s">
         <v>69</v>
       </c>
@@ -31250,7 +31251,7 @@
         <v>309010</v>
       </c>
     </row>
-    <row r="725" spans="1:5">
+    <row r="725" spans="1:8">
       <c r="A725" t="s">
         <v>70</v>
       </c>
@@ -31267,7 +31268,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="726" spans="1:7">
+    <row r="726" spans="1:8">
       <c r="A726" t="s">
         <v>70</v>
       </c>
@@ -31290,7 +31291,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="727" spans="1:7">
+    <row r="727" spans="1:8">
       <c r="A727" t="s">
         <v>70</v>
       </c>
@@ -31540,7 +31541,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="738" spans="1:7">
+    <row r="738" spans="1:8">
       <c r="A738" t="s">
         <v>70</v>
       </c>
@@ -31560,7 +31561,7 @@
         <v>310012</v>
       </c>
     </row>
-    <row r="739" spans="1:5">
+    <row r="739" spans="1:8">
       <c r="A739" t="s">
         <v>71</v>
       </c>
@@ -31577,7 +31578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="740" spans="1:7">
+    <row r="740" spans="1:8">
       <c r="A740" t="s">
         <v>71</v>
       </c>
@@ -32428,7 +32429,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="777" spans="1:5">
+    <row r="777" spans="1:8">
       <c r="A777" t="s">
         <v>76</v>
       </c>
@@ -32445,7 +32446,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="778" spans="1:7">
+    <row r="778" spans="1:8">
       <c r="A778" t="s">
         <v>76</v>
       </c>
@@ -32468,7 +32469,7 @@
         <v>318000</v>
       </c>
     </row>
-    <row r="779" spans="1:7">
+    <row r="779" spans="1:8">
       <c r="A779" t="s">
         <v>76</v>
       </c>
@@ -32488,7 +32489,7 @@
         <v>318001</v>
       </c>
     </row>
-    <row r="780" spans="1:7">
+    <row r="780" spans="1:8">
       <c r="A780" t="s">
         <v>76</v>
       </c>
@@ -32508,7 +32509,7 @@
         <v>318003</v>
       </c>
     </row>
-    <row r="781" spans="1:7">
+    <row r="781" spans="1:8">
       <c r="A781" t="s">
         <v>76</v>
       </c>
@@ -32597,7 +32598,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="785" spans="1:7">
+    <row r="785" spans="1:8">
       <c r="A785" t="s">
         <v>76</v>
       </c>
@@ -32755,7 +32756,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="792" spans="1:7">
+    <row r="792" spans="1:8">
       <c r="A792" t="s">
         <v>76</v>
       </c>
@@ -32775,7 +32776,7 @@
         <v>318007</v>
       </c>
     </row>
-    <row r="793" spans="1:7">
+    <row r="793" spans="1:8">
       <c r="A793" t="s">
         <v>76</v>
       </c>
@@ -32795,7 +32796,7 @@
         <v>318008</v>
       </c>
     </row>
-    <row r="794" spans="1:5">
+    <row r="794" spans="1:8">
       <c r="A794" t="s">
         <v>77</v>
       </c>
@@ -32812,7 +32813,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="795" spans="1:7">
+    <row r="795" spans="1:8">
       <c r="A795" t="s">
         <v>77</v>
       </c>
@@ -32835,7 +32836,7 @@
         <v>322000</v>
       </c>
     </row>
-    <row r="796" spans="1:7">
+    <row r="796" spans="1:8">
       <c r="A796" t="s">
         <v>77</v>
       </c>
@@ -33867,7 +33868,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="841" spans="1:7">
+    <row r="841" spans="1:8">
       <c r="A841" t="s">
         <v>77</v>
       </c>
@@ -33887,7 +33888,7 @@
         <v>322016</v>
       </c>
     </row>
-    <row r="842" spans="1:5">
+    <row r="842" spans="1:8">
       <c r="A842" t="s">
         <v>74</v>
       </c>
@@ -33904,7 +33905,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="843" spans="1:7">
+    <row r="843" spans="1:8">
       <c r="A843" t="s">
         <v>74</v>
       </c>
@@ -33927,7 +33928,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="844" spans="1:7">
+    <row r="844" spans="1:8">
       <c r="A844" t="s">
         <v>74</v>
       </c>
@@ -34039,7 +34040,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="849" spans="1:7">
+    <row r="849" spans="1:8">
       <c r="A849" t="s">
         <v>74</v>
       </c>
@@ -34059,7 +34060,7 @@
         <v>324006</v>
       </c>
     </row>
-    <row r="850" spans="1:7">
+    <row r="850" spans="1:8">
       <c r="A850" t="s">
         <v>74</v>
       </c>
@@ -34079,7 +34080,7 @@
         <v>324007</v>
       </c>
     </row>
-    <row r="851" spans="1:5">
+    <row r="851" spans="1:8">
       <c r="A851" t="s">
         <v>72</v>
       </c>
@@ -34096,7 +34097,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="852" spans="1:7">
+    <row r="852" spans="1:8">
       <c r="A852" t="s">
         <v>72</v>
       </c>
@@ -34116,7 +34117,7 @@
         <v>328000</v>
       </c>
     </row>
-    <row r="853" spans="1:7">
+    <row r="853" spans="1:8">
       <c r="A853" t="s">
         <v>72</v>
       </c>
@@ -34139,7 +34140,7 @@
         <v>328001</v>
       </c>
     </row>
-    <row r="854" spans="1:7">
+    <row r="854" spans="1:8">
       <c r="A854" t="s">
         <v>72</v>
       </c>
@@ -34251,7 +34252,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="859" spans="1:7">
+    <row r="859" spans="1:8">
       <c r="A859" t="s">
         <v>72</v>
       </c>
@@ -34271,7 +34272,7 @@
         <v>328007</v>
       </c>
     </row>
-    <row r="860" spans="1:5">
+    <row r="860" spans="1:8">
       <c r="A860" t="s">
         <v>73</v>
       </c>
@@ -34288,7 +34289,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="861" spans="1:7">
+    <row r="861" spans="1:8">
       <c r="A861" t="s">
         <v>73</v>
       </c>
@@ -34426,7 +34427,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="867" spans="1:7">
+    <row r="867" spans="1:8">
       <c r="A867" t="s">
         <v>73</v>
       </c>
@@ -34515,7 +34516,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="871" spans="1:7">
+    <row r="871" spans="1:8">
       <c r="A871" t="s">
         <v>73</v>
       </c>
@@ -34535,7 +34536,7 @@
         <v>346011</v>
       </c>
     </row>
-    <row r="872" spans="1:7">
+    <row r="872" spans="1:8">
       <c r="A872" t="s">
         <v>73</v>
       </c>
@@ -34555,7 +34556,7 @@
         <v>346012</v>
       </c>
     </row>
-    <row r="873" spans="1:7">
+    <row r="873" spans="1:8">
       <c r="A873" t="s">
         <v>73</v>
       </c>
@@ -34644,7 +34645,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="877" spans="1:5">
+    <row r="877" spans="1:8">
       <c r="A877" t="s">
         <v>75</v>
       </c>
@@ -34661,7 +34662,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="878" spans="1:7">
+    <row r="878" spans="1:8">
       <c r="A878" t="s">
         <v>75</v>
       </c>
@@ -34684,7 +34685,7 @@
         <v>347001</v>
       </c>
     </row>
-    <row r="879" spans="1:7">
+    <row r="879" spans="1:8">
       <c r="A879" t="s">
         <v>75</v>
       </c>
@@ -34704,7 +34705,7 @@
         <v>347002</v>
       </c>
     </row>
-    <row r="880" spans="1:7">
+    <row r="880" spans="1:8">
       <c r="A880" t="s">
         <v>75</v>
       </c>
@@ -34747,7 +34748,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="882" spans="1:7">
+    <row r="882" spans="1:8">
       <c r="A882" t="s">
         <v>75</v>
       </c>
@@ -34836,7 +34837,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="886" spans="1:7">
+    <row r="886" spans="1:8">
       <c r="A886" t="s">
         <v>75</v>
       </c>
@@ -34856,7 +34857,7 @@
         <v>347009</v>
       </c>
     </row>
-    <row r="887" spans="1:5">
+    <row r="887" spans="1:8">
       <c r="A887" t="s">
         <v>80</v>
       </c>
@@ -34873,7 +34874,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="888" spans="1:7">
+    <row r="888" spans="1:8">
       <c r="A888" t="s">
         <v>80</v>
       </c>
@@ -34893,7 +34894,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="889" spans="1:7">
+    <row r="889" spans="1:8">
       <c r="A889" t="s">
         <v>80</v>
       </c>
@@ -34913,7 +34914,7 @@
         <v>750011</v>
       </c>
     </row>
-    <row r="890" spans="1:7">
+    <row r="890" spans="1:8">
       <c r="A890" t="s">
         <v>80</v>
       </c>
@@ -34933,7 +34934,7 @@
         <v>750001</v>
       </c>
     </row>
-    <row r="891" spans="1:7">
+    <row r="891" spans="1:8">
       <c r="A891" t="s">
         <v>80</v>
       </c>
@@ -34953,7 +34954,7 @@
         <v>750002</v>
       </c>
     </row>
-    <row r="892" spans="1:7">
+    <row r="892" spans="1:8">
       <c r="A892" t="s">
         <v>80</v>
       </c>
@@ -34973,7 +34974,7 @@
         <v>750003</v>
       </c>
     </row>
-    <row r="893" spans="1:7">
+    <row r="893" spans="1:8">
       <c r="A893" t="s">
         <v>80</v>
       </c>
@@ -34993,7 +34994,7 @@
         <v>750004</v>
       </c>
     </row>
-    <row r="894" spans="1:7">
+    <row r="894" spans="1:8">
       <c r="A894" t="s">
         <v>80</v>
       </c>
@@ -35013,7 +35014,7 @@
         <v>750005</v>
       </c>
     </row>
-    <row r="895" spans="1:7">
+    <row r="895" spans="1:8">
       <c r="A895" t="s">
         <v>80</v>
       </c>
@@ -35033,7 +35034,7 @@
         <v>750006</v>
       </c>
     </row>
-    <row r="896" spans="1:7">
+    <row r="896" spans="1:8">
       <c r="A896" t="s">
         <v>80</v>
       </c>
@@ -35053,7 +35054,7 @@
         <v>750007</v>
       </c>
     </row>
-    <row r="897" spans="1:7">
+    <row r="897" spans="1:8">
       <c r="A897" t="s">
         <v>80</v>
       </c>
@@ -35073,7 +35074,7 @@
         <v>750008</v>
       </c>
     </row>
-    <row r="898" spans="1:7">
+    <row r="898" spans="1:8">
       <c r="A898" t="s">
         <v>80</v>
       </c>
@@ -35093,7 +35094,7 @@
         <v>750009</v>
       </c>
     </row>
-    <row r="899" spans="1:7">
+    <row r="899" spans="1:8">
       <c r="A899" t="s">
         <v>80</v>
       </c>
@@ -35113,7 +35114,7 @@
         <v>750010</v>
       </c>
     </row>
-    <row r="900" spans="1:5">
+    <row r="900" spans="1:8">
       <c r="A900" t="s">
         <v>82</v>
       </c>
@@ -35130,7 +35131,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="901" spans="1:7">
+    <row r="901" spans="1:8">
       <c r="A901" t="s">
         <v>82</v>
       </c>
@@ -35150,7 +35151,7 @@
         <v>752000</v>
       </c>
     </row>
-    <row r="902" spans="1:7">
+    <row r="902" spans="1:8">
       <c r="A902" t="s">
         <v>82</v>
       </c>
@@ -35173,7 +35174,7 @@
         <v>752001</v>
       </c>
     </row>
-    <row r="903" spans="1:7">
+    <row r="903" spans="1:8">
       <c r="A903" t="s">
         <v>82</v>
       </c>
@@ -35196,7 +35197,7 @@
         <v>752002</v>
       </c>
     </row>
-    <row r="904" spans="1:7">
+    <row r="904" spans="1:8">
       <c r="A904" t="s">
         <v>82</v>
       </c>
@@ -35216,7 +35217,7 @@
         <v>752003</v>
       </c>
     </row>
-    <row r="905" spans="1:7">
+    <row r="905" spans="1:8">
       <c r="A905" t="s">
         <v>82</v>
       </c>
@@ -35236,7 +35237,7 @@
         <v>752004</v>
       </c>
     </row>
-    <row r="906" spans="1:7">
+    <row r="906" spans="1:8">
       <c r="A906" t="s">
         <v>82</v>
       </c>
@@ -35256,7 +35257,7 @@
         <v>752005</v>
       </c>
     </row>
-    <row r="907" spans="1:5">
+    <row r="907" spans="1:8">
       <c r="A907" t="s">
         <v>83</v>
       </c>
@@ -35273,7 +35274,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="908" spans="1:7">
+    <row r="908" spans="1:8">
       <c r="A908" t="s">
         <v>83</v>
       </c>
@@ -35296,7 +35297,7 @@
         <v>800001</v>
       </c>
     </row>
-    <row r="909" spans="1:7">
+    <row r="909" spans="1:8">
       <c r="A909" t="s">
         <v>83</v>
       </c>
@@ -35316,7 +35317,7 @@
         <v>800002</v>
       </c>
     </row>
-    <row r="910" spans="1:7">
+    <row r="910" spans="1:8">
       <c r="A910" t="s">
         <v>83</v>
       </c>
@@ -35727,7 +35728,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="928" spans="1:5">
+    <row r="928" spans="1:8">
       <c r="A928" t="s">
         <v>85</v>
       </c>
@@ -35744,7 +35745,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="929" spans="1:7">
+    <row r="929" spans="1:8">
       <c r="A929" t="s">
         <v>85</v>
       </c>
@@ -35767,7 +35768,7 @@
         <v>802001</v>
       </c>
     </row>
-    <row r="930" spans="1:7">
+    <row r="930" spans="1:8">
       <c r="A930" t="s">
         <v>85</v>
       </c>
@@ -35787,7 +35788,7 @@
         <v>802002</v>
       </c>
     </row>
-    <row r="931" spans="1:7">
+    <row r="931" spans="1:8">
       <c r="A931" t="s">
         <v>85</v>
       </c>
@@ -39993,7 +39994,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1114" spans="1:5">
+    <row r="1114" spans="1:8">
       <c r="A1114" t="s">
         <v>86</v>
       </c>
@@ -40010,7 +40011,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1115" spans="1:7">
+    <row r="1115" spans="1:8">
       <c r="A1115" t="s">
         <v>86</v>
       </c>
@@ -40033,7 +40034,7 @@
         <v>803001</v>
       </c>
     </row>
-    <row r="1116" spans="1:7">
+    <row r="1116" spans="1:8">
       <c r="A1116" t="s">
         <v>86</v>
       </c>
@@ -40053,7 +40054,7 @@
         <v>803002</v>
       </c>
     </row>
-    <row r="1117" spans="1:7">
+    <row r="1117" spans="1:8">
       <c r="A1117" t="s">
         <v>86</v>
       </c>
@@ -42971,7 +42972,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1244" spans="1:5">
+    <row r="1244" spans="1:8">
       <c r="A1244" t="s">
         <v>87</v>
       </c>
@@ -42988,7 +42989,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1245" spans="1:7">
+    <row r="1245" spans="1:8">
       <c r="A1245" t="s">
         <v>87</v>
       </c>
@@ -43011,7 +43012,7 @@
         <v>804001</v>
       </c>
     </row>
-    <row r="1246" spans="1:7">
+    <row r="1246" spans="1:8">
       <c r="A1246" t="s">
         <v>87</v>
       </c>
@@ -43031,7 +43032,7 @@
         <v>804002</v>
       </c>
     </row>
-    <row r="1247" spans="1:7">
+    <row r="1247" spans="1:8">
       <c r="A1247" t="s">
         <v>87</v>
       </c>
@@ -45305,7 +45306,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1346" spans="1:5">
+    <row r="1346" spans="1:8">
       <c r="A1346" t="s">
         <v>88</v>
       </c>
@@ -45322,7 +45323,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1347" spans="1:7">
+    <row r="1347" spans="1:8">
       <c r="A1347" t="s">
         <v>88</v>
       </c>
@@ -45345,7 +45346,7 @@
         <v>805001</v>
       </c>
     </row>
-    <row r="1348" spans="1:7">
+    <row r="1348" spans="1:8">
       <c r="A1348" t="s">
         <v>88</v>
       </c>
@@ -45365,7 +45366,7 @@
         <v>805002</v>
       </c>
     </row>
-    <row r="1349" spans="1:7">
+    <row r="1349" spans="1:8">
       <c r="A1349" t="s">
         <v>88</v>
       </c>
@@ -47501,7 +47502,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1442" spans="1:5">
+    <row r="1442" spans="1:8">
       <c r="A1442" t="s">
         <v>89</v>
       </c>
@@ -47518,7 +47519,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1443" spans="1:7">
+    <row r="1443" spans="1:8">
       <c r="A1443" t="s">
         <v>89</v>
       </c>
@@ -47541,7 +47542,7 @@
         <v>807001</v>
       </c>
     </row>
-    <row r="1444" spans="1:7">
+    <row r="1444" spans="1:8">
       <c r="A1444" t="s">
         <v>89</v>
       </c>
@@ -47561,7 +47562,7 @@
         <v>807002</v>
       </c>
     </row>
-    <row r="1445" spans="1:7">
+    <row r="1445" spans="1:8">
       <c r="A1445" t="s">
         <v>89</v>
       </c>
@@ -50893,7 +50894,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1590" spans="1:5">
+    <row r="1590" spans="1:8">
       <c r="A1590" t="s">
         <v>90</v>
       </c>
@@ -50910,7 +50911,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1591" spans="1:7">
+    <row r="1591" spans="1:8">
       <c r="A1591" t="s">
         <v>90</v>
       </c>
@@ -50933,7 +50934,7 @@
         <v>808001</v>
       </c>
     </row>
-    <row r="1592" spans="1:7">
+    <row r="1592" spans="1:8">
       <c r="A1592" t="s">
         <v>90</v>
       </c>
@@ -50953,7 +50954,7 @@
         <v>808002</v>
       </c>
     </row>
-    <row r="1593" spans="1:7">
+    <row r="1593" spans="1:8">
       <c r="A1593" t="s">
         <v>90</v>
       </c>
@@ -54423,7 +54424,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1744" spans="1:5">
+    <row r="1744" spans="1:8">
       <c r="A1744" t="s">
         <v>91</v>
       </c>
@@ -54440,7 +54441,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1745" spans="1:7">
+    <row r="1745" spans="1:8">
       <c r="A1745" t="s">
         <v>91</v>
       </c>
@@ -54463,7 +54464,7 @@
         <v>809001</v>
       </c>
     </row>
-    <row r="1746" spans="1:7">
+    <row r="1746" spans="1:8">
       <c r="A1746" t="s">
         <v>91</v>
       </c>
@@ -54483,7 +54484,7 @@
         <v>809002</v>
       </c>
     </row>
-    <row r="1747" spans="1:7">
+    <row r="1747" spans="1:8">
       <c r="A1747" t="s">
         <v>91</v>
       </c>
@@ -54825,7 +54826,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1762" spans="1:5">
+    <row r="1762" spans="1:8">
       <c r="A1762" t="s">
         <v>92</v>
       </c>
@@ -54842,7 +54843,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1763" spans="1:7">
+    <row r="1763" spans="1:8">
       <c r="A1763" t="s">
         <v>92</v>
       </c>
@@ -54865,7 +54866,7 @@
         <v>810001</v>
       </c>
     </row>
-    <row r="1764" spans="1:7">
+    <row r="1764" spans="1:8">
       <c r="A1764" t="s">
         <v>92</v>
       </c>
@@ -54885,7 +54886,7 @@
         <v>810002</v>
       </c>
     </row>
-    <row r="1765" spans="1:7">
+    <row r="1765" spans="1:8">
       <c r="A1765" t="s">
         <v>92</v>
       </c>
@@ -55917,7 +55918,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1810" spans="1:5">
+    <row r="1810" spans="1:8">
       <c r="A1810" t="s">
         <v>94</v>
       </c>
@@ -55934,7 +55935,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1811" spans="1:7">
+    <row r="1811" spans="1:8">
       <c r="A1811" t="s">
         <v>94</v>
       </c>
@@ -55954,7 +55955,7 @@
         <v>812001</v>
       </c>
     </row>
-    <row r="1812" spans="1:7">
+    <row r="1812" spans="1:8">
       <c r="A1812" t="s">
         <v>94</v>
       </c>
@@ -55974,7 +55975,7 @@
         <v>812002</v>
       </c>
     </row>
-    <row r="1813" spans="1:7">
+    <row r="1813" spans="1:8">
       <c r="A1813" t="s">
         <v>94</v>
       </c>
@@ -55994,7 +55995,7 @@
         <v>812003</v>
       </c>
     </row>
-    <row r="1814" spans="1:7">
+    <row r="1814" spans="1:8">
       <c r="A1814" t="s">
         <v>94</v>
       </c>
@@ -56063,7 +56064,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1817" spans="1:5">
+    <row r="1817" spans="1:8">
       <c r="A1817" t="s">
         <v>93</v>
       </c>
@@ -56080,7 +56081,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1818" spans="1:7">
+    <row r="1818" spans="1:8">
       <c r="A1818" t="s">
         <v>93</v>
       </c>
@@ -56103,7 +56104,7 @@
         <v>814001</v>
       </c>
     </row>
-    <row r="1819" spans="1:7">
+    <row r="1819" spans="1:8">
       <c r="A1819" t="s">
         <v>93</v>
       </c>
@@ -56123,7 +56124,7 @@
         <v>814002</v>
       </c>
     </row>
-    <row r="1820" spans="1:7">
+    <row r="1820" spans="1:8">
       <c r="A1820" t="s">
         <v>93</v>
       </c>
@@ -57937,7 +57938,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1899" spans="1:5">
+    <row r="1899" spans="1:8">
       <c r="A1899" t="s">
         <v>96</v>
       </c>
@@ -57954,7 +57955,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1900" spans="1:7">
+    <row r="1900" spans="1:8">
       <c r="A1900" t="s">
         <v>96</v>
       </c>
@@ -57977,7 +57978,7 @@
         <v>760001</v>
       </c>
     </row>
-    <row r="1901" spans="1:7">
+    <row r="1901" spans="1:8">
       <c r="A1901" t="s">
         <v>96</v>
       </c>
@@ -57997,7 +57998,7 @@
         <v>760002</v>
       </c>
     </row>
-    <row r="1902" spans="1:7">
+    <row r="1902" spans="1:8">
       <c r="A1902" t="s">
         <v>96</v>
       </c>
@@ -58017,7 +58018,7 @@
         <v>760003</v>
       </c>
     </row>
-    <row r="1903" spans="1:7">
+    <row r="1903" spans="1:8">
       <c r="A1903" t="s">
         <v>96</v>
       </c>
@@ -58140,7 +58141,7 @@
         <v>760009</v>
       </c>
     </row>
-    <row r="1909" spans="1:5">
+    <row r="1909" spans="1:7">
       <c r="A1909" t="s">
         <v>102</v>
       </c>
@@ -58380,7 +58381,7 @@
         <v>703011</v>
       </c>
     </row>
-    <row r="1921" spans="1:7">
+    <row r="1921" spans="1:8">
       <c r="A1921" t="s">
         <v>102</v>
       </c>
@@ -58400,7 +58401,7 @@
         <v>703012</v>
       </c>
     </row>
-    <row r="1922" spans="1:7">
+    <row r="1922" spans="1:8">
       <c r="A1922" t="s">
         <v>102</v>
       </c>
@@ -58443,7 +58444,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1924" spans="1:7">
+    <row r="1924" spans="1:8">
       <c r="A1924" t="s">
         <v>102</v>
       </c>
@@ -58486,7 +58487,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1926" spans="1:7">
+    <row r="1926" spans="1:8">
       <c r="A1926" t="s">
         <v>102</v>
       </c>
@@ -58506,7 +58507,7 @@
         <v>703017</v>
       </c>
     </row>
-    <row r="1927" spans="1:7">
+    <row r="1927" spans="1:8">
       <c r="A1927" t="s">
         <v>102</v>
       </c>
@@ -58526,7 +58527,7 @@
         <v>703018</v>
       </c>
     </row>
-    <row r="1928" spans="1:7">
+    <row r="1928" spans="1:8">
       <c r="A1928" t="s">
         <v>102</v>
       </c>
@@ -58569,7 +58570,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1930" spans="1:7">
+    <row r="1930" spans="1:8">
       <c r="A1930" t="s">
         <v>102</v>
       </c>
@@ -58612,7 +58613,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1932" spans="1:7">
+    <row r="1932" spans="1:8">
       <c r="A1932" t="s">
         <v>102</v>
       </c>
@@ -58632,7 +58633,7 @@
         <v>703023</v>
       </c>
     </row>
-    <row r="1933" spans="1:7">
+    <row r="1933" spans="1:8">
       <c r="A1933" t="s">
         <v>102</v>
       </c>
@@ -58652,7 +58653,7 @@
         <v>703024</v>
       </c>
     </row>
-    <row r="1934" spans="1:7">
+    <row r="1934" spans="1:8">
       <c r="A1934" t="s">
         <v>102</v>
       </c>
@@ -58672,7 +58673,7 @@
         <v>703025</v>
       </c>
     </row>
-    <row r="1935" spans="1:7">
+    <row r="1935" spans="1:8">
       <c r="A1935" t="s">
         <v>102</v>
       </c>
@@ -58692,7 +58693,7 @@
         <v>703026</v>
       </c>
     </row>
-    <row r="1936" spans="1:7">
+    <row r="1936" spans="1:8">
       <c r="A1936" t="s">
         <v>102</v>
       </c>
@@ -58712,7 +58713,7 @@
         <v>703027</v>
       </c>
     </row>
-    <row r="1937" spans="1:7">
+    <row r="1937" spans="1:8">
       <c r="A1937" t="s">
         <v>102</v>
       </c>
@@ -58732,7 +58733,7 @@
         <v>703028</v>
       </c>
     </row>
-    <row r="1938" spans="1:7">
+    <row r="1938" spans="1:8">
       <c r="A1938" t="s">
         <v>102</v>
       </c>
@@ -58752,7 +58753,7 @@
         <v>703029</v>
       </c>
     </row>
-    <row r="1939" spans="1:7">
+    <row r="1939" spans="1:8">
       <c r="A1939" t="s">
         <v>102</v>
       </c>
@@ -58772,7 +58773,7 @@
         <v>703030</v>
       </c>
     </row>
-    <row r="1940" spans="1:5">
+    <row r="1940" spans="1:8">
       <c r="A1940" t="s">
         <v>103</v>
       </c>
@@ -58789,7 +58790,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1941" spans="1:7">
+    <row r="1941" spans="1:8">
       <c r="A1941" t="s">
         <v>103</v>
       </c>
@@ -59088,7 +59089,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="1954" spans="1:5">
+    <row r="1954" spans="1:8">
       <c r="A1954" t="s">
         <v>104</v>
       </c>
@@ -59105,7 +59106,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1955" spans="1:7">
+    <row r="1955" spans="1:8">
       <c r="A1955" t="s">
         <v>104</v>
       </c>
@@ -59125,7 +59126,7 @@
         <v>710001</v>
       </c>
     </row>
-    <row r="1956" spans="1:7">
+    <row r="1956" spans="1:8">
       <c r="A1956" t="s">
         <v>104</v>
       </c>
@@ -59171,7 +59172,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1958" spans="1:7">
+    <row r="1958" spans="1:8">
       <c r="A1958" t="s">
         <v>104</v>
       </c>
@@ -59191,7 +59192,7 @@
         <v>710004</v>
       </c>
     </row>
-    <row r="1959" spans="1:5">
+    <row r="1959" spans="1:8">
       <c r="A1959" t="s">
         <v>106</v>
       </c>
@@ -59208,7 +59209,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1960" spans="1:7">
+    <row r="1960" spans="1:8">
       <c r="A1960" t="s">
         <v>106</v>
       </c>
@@ -59231,7 +59232,7 @@
         <v>705001</v>
       </c>
     </row>
-    <row r="1961" spans="1:7">
+    <row r="1961" spans="1:8">
       <c r="A1961" t="s">
         <v>106</v>
       </c>
@@ -59366,7 +59367,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="1967" spans="1:5">
+    <row r="1967" spans="1:8">
       <c r="A1967" t="s">
         <v>107</v>
       </c>
@@ -59383,7 +59384,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1968" spans="1:7">
+    <row r="1968" spans="1:8">
       <c r="A1968" t="s">
         <v>107</v>
       </c>
@@ -59406,7 +59407,7 @@
         <v>706001</v>
       </c>
     </row>
-    <row r="1969" spans="1:7">
+    <row r="1969" spans="1:8">
       <c r="A1969" t="s">
         <v>107</v>
       </c>
@@ -59426,7 +59427,7 @@
         <v>706002</v>
       </c>
     </row>
-    <row r="1970" spans="1:7">
+    <row r="1970" spans="1:8">
       <c r="A1970" t="s">
         <v>107</v>
       </c>
@@ -59492,7 +59493,7 @@
         <v>3365</v>
       </c>
     </row>
-    <row r="1973" spans="1:5">
+    <row r="1973" spans="1:8">
       <c r="A1973" t="s">
         <v>108</v>
       </c>
@@ -59509,7 +59510,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1974" spans="1:7">
+    <row r="1974" spans="1:8">
       <c r="A1974" t="s">
         <v>108</v>
       </c>
@@ -59532,7 +59533,7 @@
         <v>707001</v>
       </c>
     </row>
-    <row r="1975" spans="1:7">
+    <row r="1975" spans="1:8">
       <c r="A1975" t="s">
         <v>108</v>
       </c>
@@ -59552,7 +59553,7 @@
         <v>707002</v>
       </c>
     </row>
-    <row r="1976" spans="1:7">
+    <row r="1976" spans="1:8">
       <c r="A1976" t="s">
         <v>108</v>
       </c>
@@ -59572,7 +59573,7 @@
         <v>707003</v>
       </c>
     </row>
-    <row r="1977" spans="1:7">
+    <row r="1977" spans="1:8">
       <c r="A1977" t="s">
         <v>108</v>
       </c>
@@ -59592,7 +59593,7 @@
         <v>707004</v>
       </c>
     </row>
-    <row r="1978" spans="1:7">
+    <row r="1978" spans="1:8">
       <c r="A1978" t="s">
         <v>108</v>
       </c>
@@ -59612,7 +59613,7 @@
         <v>707005</v>
       </c>
     </row>
-    <row r="1979" spans="1:7">
+    <row r="1979" spans="1:8">
       <c r="A1979" t="s">
         <v>108</v>
       </c>
@@ -59632,7 +59633,7 @@
         <v>707006</v>
       </c>
     </row>
-    <row r="1980" spans="1:7">
+    <row r="1980" spans="1:8">
       <c r="A1980" t="s">
         <v>108</v>
       </c>
@@ -59652,7 +59653,7 @@
         <v>707007</v>
       </c>
     </row>
-    <row r="1981" spans="1:7">
+    <row r="1981" spans="1:8">
       <c r="A1981" t="s">
         <v>108</v>
       </c>
@@ -59672,7 +59673,7 @@
         <v>707008</v>
       </c>
     </row>
-    <row r="1982" spans="1:7">
+    <row r="1982" spans="1:8">
       <c r="A1982" t="s">
         <v>108</v>
       </c>
@@ -59692,7 +59693,7 @@
         <v>707009</v>
       </c>
     </row>
-    <row r="1983" spans="1:7">
+    <row r="1983" spans="1:8">
       <c r="A1983" t="s">
         <v>108</v>
       </c>
@@ -59804,7 +59805,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="1988" spans="1:5">
+    <row r="1988" spans="1:8">
       <c r="A1988" t="s">
         <v>98</v>
       </c>
@@ -59821,7 +59822,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1989" spans="1:7">
+    <row r="1989" spans="1:8">
       <c r="A1989" t="s">
         <v>98</v>
       </c>
@@ -59841,7 +59842,7 @@
         <v>708001</v>
       </c>
     </row>
-    <row r="1990" spans="1:7">
+    <row r="1990" spans="1:8">
       <c r="A1990" t="s">
         <v>98</v>
       </c>
@@ -59864,7 +59865,7 @@
         <v>708002</v>
       </c>
     </row>
-    <row r="1991" spans="1:7">
+    <row r="1991" spans="1:8">
       <c r="A1991" t="s">
         <v>98</v>
       </c>
@@ -59884,7 +59885,7 @@
         <v>708003</v>
       </c>
     </row>
-    <row r="1992" spans="1:7">
+    <row r="1992" spans="1:8">
       <c r="A1992" t="s">
         <v>98</v>
       </c>
@@ -59904,7 +59905,7 @@
         <v>708004</v>
       </c>
     </row>
-    <row r="1993" spans="1:7">
+    <row r="1993" spans="1:8">
       <c r="A1993" t="s">
         <v>98</v>
       </c>
@@ -59924,7 +59925,7 @@
         <v>708005</v>
       </c>
     </row>
-    <row r="1994" spans="1:7">
+    <row r="1994" spans="1:8">
       <c r="A1994" t="s">
         <v>98</v>
       </c>
@@ -59944,7 +59945,7 @@
         <v>708006</v>
       </c>
     </row>
-    <row r="1995" spans="1:7">
+    <row r="1995" spans="1:8">
       <c r="A1995" t="s">
         <v>98</v>
       </c>
@@ -59964,7 +59965,7 @@
         <v>708007</v>
       </c>
     </row>
-    <row r="1996" spans="1:7">
+    <row r="1996" spans="1:8">
       <c r="A1996" t="s">
         <v>98</v>
       </c>
@@ -59984,7 +59985,7 @@
         <v>708008</v>
       </c>
     </row>
-    <row r="1997" spans="1:7">
+    <row r="1997" spans="1:8">
       <c r="A1997" t="s">
         <v>98</v>
       </c>
@@ -60004,7 +60005,7 @@
         <v>708009</v>
       </c>
     </row>
-    <row r="1998" spans="1:7">
+    <row r="1998" spans="1:8">
       <c r="A1998" t="s">
         <v>98</v>
       </c>
@@ -60024,7 +60025,7 @@
         <v>708010</v>
       </c>
     </row>
-    <row r="1999" spans="1:5">
+    <row r="1999" spans="1:8">
       <c r="A1999" t="s">
         <v>109</v>
       </c>
@@ -60041,7 +60042,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2000" spans="1:7">
+    <row r="2000" spans="1:8">
       <c r="A2000" t="s">
         <v>109</v>
       </c>
@@ -60061,7 +60062,7 @@
         <v>702001</v>
       </c>
     </row>
-    <row r="2001" spans="1:7">
+    <row r="2001" spans="1:8">
       <c r="A2001" t="s">
         <v>109</v>
       </c>
@@ -60081,7 +60082,7 @@
         <v>702002</v>
       </c>
     </row>
-    <row r="2002" spans="1:7">
+    <row r="2002" spans="1:8">
       <c r="A2002" t="s">
         <v>109</v>
       </c>
@@ -60101,7 +60102,7 @@
         <v>702003</v>
       </c>
     </row>
-    <row r="2003" spans="1:7">
+    <row r="2003" spans="1:8">
       <c r="A2003" t="s">
         <v>109</v>
       </c>
@@ -60144,7 +60145,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2005" spans="1:7">
+    <row r="2005" spans="1:8">
       <c r="A2005" t="s">
         <v>109</v>
       </c>
@@ -60164,7 +60165,7 @@
         <v>702006</v>
       </c>
     </row>
-    <row r="2006" spans="1:5">
+    <row r="2006" spans="1:8">
       <c r="A2006" t="s">
         <v>105</v>
       </c>
@@ -60181,7 +60182,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2007" spans="1:7">
+    <row r="2007" spans="1:8">
       <c r="A2007" t="s">
         <v>105</v>
       </c>
@@ -60201,7 +60202,7 @@
         <v>701001</v>
       </c>
     </row>
-    <row r="2008" spans="1:7">
+    <row r="2008" spans="1:8">
       <c r="A2008" t="s">
         <v>105</v>
       </c>
@@ -60224,7 +60225,7 @@
         <v>701002</v>
       </c>
     </row>
-    <row r="2009" spans="1:7">
+    <row r="2009" spans="1:8">
       <c r="A2009" t="s">
         <v>105</v>
       </c>
@@ -60244,7 +60245,7 @@
         <v>701003</v>
       </c>
     </row>
-    <row r="2010" spans="1:7">
+    <row r="2010" spans="1:8">
       <c r="A2010" t="s">
         <v>105</v>
       </c>
@@ -60264,7 +60265,7 @@
         <v>701004</v>
       </c>
     </row>
-    <row r="2011" spans="1:7">
+    <row r="2011" spans="1:8">
       <c r="A2011" t="s">
         <v>105</v>
       </c>
@@ -60330,7 +60331,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="2014" spans="1:7">
+    <row r="2014" spans="1:8">
       <c r="A2014" t="s">
         <v>105</v>
       </c>
@@ -60350,7 +60351,7 @@
         <v>701008</v>
       </c>
     </row>
-    <row r="2015" spans="1:5">
+    <row r="2015" spans="1:8">
       <c r="A2015" t="s">
         <v>100</v>
       </c>
@@ -60367,7 +60368,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2016" spans="1:7">
+    <row r="2016" spans="1:8">
       <c r="A2016" t="s">
         <v>100</v>
       </c>
@@ -60390,7 +60391,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="2017" spans="1:7">
+    <row r="2017" spans="1:8">
       <c r="A2017" t="s">
         <v>100</v>
       </c>
@@ -60410,7 +60411,7 @@
         <v>700001</v>
       </c>
     </row>
-    <row r="2018" spans="1:7">
+    <row r="2018" spans="1:8">
       <c r="A2018" t="s">
         <v>100</v>
       </c>
@@ -60430,7 +60431,7 @@
         <v>700002</v>
       </c>
     </row>
-    <row r="2019" spans="1:7">
+    <row r="2019" spans="1:8">
       <c r="A2019" t="s">
         <v>100</v>
       </c>
@@ -60450,7 +60451,7 @@
         <v>700003</v>
       </c>
     </row>
-    <row r="2020" spans="1:5">
+    <row r="2020" spans="1:8">
       <c r="A2020" t="s">
         <v>110</v>
       </c>
@@ -60467,7 +60468,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2021" spans="1:7">
+    <row r="2021" spans="1:8">
       <c r="A2021" t="s">
         <v>110</v>
       </c>
@@ -60510,7 +60511,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2023" spans="1:7">
+    <row r="2023" spans="1:8">
       <c r="A2023" t="s">
         <v>110</v>
       </c>
@@ -60530,7 +60531,7 @@
         <v>502002</v>
       </c>
     </row>
-    <row r="2024" spans="1:7">
+    <row r="2024" spans="1:8">
       <c r="A2024" t="s">
         <v>110</v>
       </c>
@@ -60550,7 +60551,7 @@
         <v>502003</v>
       </c>
     </row>
-    <row r="2025" spans="1:7">
+    <row r="2025" spans="1:8">
       <c r="A2025" t="s">
         <v>110</v>
       </c>
@@ -60570,7 +60571,7 @@
         <v>502037</v>
       </c>
     </row>
-    <row r="2026" spans="1:7">
+    <row r="2026" spans="1:8">
       <c r="A2026" t="s">
         <v>110</v>
       </c>
@@ -60590,7 +60591,7 @@
         <v>502004</v>
       </c>
     </row>
-    <row r="2027" spans="1:7">
+    <row r="2027" spans="1:8">
       <c r="A2027" t="s">
         <v>110</v>
       </c>
@@ -60610,7 +60611,7 @@
         <v>502005</v>
       </c>
     </row>
-    <row r="2028" spans="1:7">
+    <row r="2028" spans="1:8">
       <c r="A2028" t="s">
         <v>110</v>
       </c>
@@ -60653,7 +60654,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2030" spans="1:7">
+    <row r="2030" spans="1:8">
       <c r="A2030" t="s">
         <v>110</v>
       </c>
@@ -60719,7 +60720,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2033" spans="1:7">
+    <row r="2033" spans="1:8">
       <c r="A2033" t="s">
         <v>110</v>
       </c>
@@ -60739,7 +60740,7 @@
         <v>502011</v>
       </c>
     </row>
-    <row r="2034" spans="1:7">
+    <row r="2034" spans="1:8">
       <c r="A2034" t="s">
         <v>110</v>
       </c>
@@ -60759,7 +60760,7 @@
         <v>502012</v>
       </c>
     </row>
-    <row r="2035" spans="1:7">
+    <row r="2035" spans="1:8">
       <c r="A2035" t="s">
         <v>110</v>
       </c>
@@ -60779,7 +60780,7 @@
         <v>502034</v>
       </c>
     </row>
-    <row r="2036" spans="1:7">
+    <row r="2036" spans="1:8">
       <c r="A2036" t="s">
         <v>110</v>
       </c>
@@ -60845,7 +60846,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2039" spans="1:7">
+    <row r="2039" spans="1:8">
       <c r="A2039" t="s">
         <v>110</v>
       </c>
@@ -60888,7 +60889,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2041" spans="1:7">
+    <row r="2041" spans="1:8">
       <c r="A2041" t="s">
         <v>110</v>
       </c>
@@ -60931,7 +60932,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2043" spans="1:7">
+    <row r="2043" spans="1:8">
       <c r="A2043" t="s">
         <v>110</v>
       </c>
@@ -60951,7 +60952,7 @@
         <v>502033</v>
       </c>
     </row>
-    <row r="2044" spans="1:7">
+    <row r="2044" spans="1:8">
       <c r="A2044" t="s">
         <v>110</v>
       </c>
@@ -60971,7 +60972,7 @@
         <v>502020</v>
       </c>
     </row>
-    <row r="2045" spans="1:7">
+    <row r="2045" spans="1:8">
       <c r="A2045" t="s">
         <v>110</v>
       </c>
@@ -61037,7 +61038,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2048" spans="1:7">
+    <row r="2048" spans="1:8">
       <c r="A2048" t="s">
         <v>110</v>
       </c>
@@ -61557,7 +61558,7 @@
         <v>502055</v>
       </c>
     </row>
-    <row r="2074" spans="1:5">
+    <row r="2074" spans="1:7">
       <c r="A2074" t="s">
         <v>112</v>
       </c>
@@ -61697,7 +61698,7 @@
         <v>503005</v>
       </c>
     </row>
-    <row r="2081" spans="1:7">
+    <row r="2081" spans="1:8">
       <c r="A2081" t="s">
         <v>112</v>
       </c>
@@ -61717,7 +61718,7 @@
         <v>503006</v>
       </c>
     </row>
-    <row r="2082" spans="1:7">
+    <row r="2082" spans="1:8">
       <c r="A2082" t="s">
         <v>112</v>
       </c>
@@ -61737,7 +61738,7 @@
         <v>503007</v>
       </c>
     </row>
-    <row r="2083" spans="1:7">
+    <row r="2083" spans="1:8">
       <c r="A2083" t="s">
         <v>112</v>
       </c>
@@ -61757,7 +61758,7 @@
         <v>503008</v>
       </c>
     </row>
-    <row r="2084" spans="1:5">
+    <row r="2084" spans="1:8">
       <c r="A2084" t="s">
         <v>113</v>
       </c>
@@ -61774,7 +61775,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2085" spans="1:7">
+    <row r="2085" spans="1:8">
       <c r="A2085" t="s">
         <v>113</v>
       </c>
@@ -61794,7 +61795,7 @@
         <v>505001</v>
       </c>
     </row>
-    <row r="2086" spans="1:7">
+    <row r="2086" spans="1:8">
       <c r="A2086" t="s">
         <v>113</v>
       </c>
@@ -61814,7 +61815,7 @@
         <v>505002</v>
       </c>
     </row>
-    <row r="2087" spans="1:7">
+    <row r="2087" spans="1:8">
       <c r="A2087" t="s">
         <v>113</v>
       </c>
@@ -61903,7 +61904,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2091" spans="1:7">
+    <row r="2091" spans="1:8">
       <c r="A2091" t="s">
         <v>113</v>
       </c>
@@ -61923,7 +61924,7 @@
         <v>505007</v>
       </c>
     </row>
-    <row r="2092" spans="1:7">
+    <row r="2092" spans="1:8">
       <c r="A2092" t="s">
         <v>113</v>
       </c>
@@ -61943,7 +61944,7 @@
         <v>505008</v>
       </c>
     </row>
-    <row r="2093" spans="1:7">
+    <row r="2093" spans="1:8">
       <c r="A2093" t="s">
         <v>113</v>
       </c>
@@ -61963,7 +61964,7 @@
         <v>505009</v>
       </c>
     </row>
-    <row r="2094" spans="1:5">
+    <row r="2094" spans="1:8">
       <c r="A2094" t="s">
         <v>114</v>
       </c>
@@ -61980,7 +61981,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2095" spans="1:7">
+    <row r="2095" spans="1:8">
       <c r="A2095" t="s">
         <v>114</v>
       </c>
@@ -62000,7 +62001,7 @@
         <v>507000</v>
       </c>
     </row>
-    <row r="2096" spans="1:7">
+    <row r="2096" spans="1:8">
       <c r="A2096" t="s">
         <v>114</v>
       </c>
@@ -62183,7 +62184,7 @@
         <v>507009</v>
       </c>
     </row>
-    <row r="2105" spans="1:5">
+    <row r="2105" spans="1:7">
       <c r="A2105" t="s">
         <v>115</v>
       </c>
@@ -62403,7 +62404,7 @@
         <v>508009</v>
       </c>
     </row>
-    <row r="2116" spans="1:5">
+    <row r="2116" spans="1:7">
       <c r="A2116" t="s">
         <v>116</v>
       </c>
@@ -62503,7 +62504,7 @@
         <v>568004</v>
       </c>
     </row>
-    <row r="2121" spans="1:5">
+    <row r="2121" spans="1:7">
       <c r="A2121" t="s">
         <v>117</v>
       </c>
@@ -63260,7 +63261,7 @@
         <v>569036</v>
       </c>
     </row>
-    <row r="2159" spans="1:5">
+    <row r="2159" spans="1:7">
       <c r="A2159" t="s">
         <v>118</v>
       </c>
@@ -63300,7 +63301,7 @@
         <v>504000</v>
       </c>
     </row>
-    <row r="2161" spans="1:7">
+    <row r="2161" spans="1:8">
       <c r="A2161" t="s">
         <v>118</v>
       </c>
@@ -63320,7 +63321,7 @@
         <v>504001</v>
       </c>
     </row>
-    <row r="2162" spans="1:7">
+    <row r="2162" spans="1:8">
       <c r="A2162" t="s">
         <v>118</v>
       </c>
@@ -63340,7 +63341,7 @@
         <v>504002</v>
       </c>
     </row>
-    <row r="2163" spans="1:7">
+    <row r="2163" spans="1:8">
       <c r="A2163" t="s">
         <v>118</v>
       </c>
@@ -63360,7 +63361,7 @@
         <v>504003</v>
       </c>
     </row>
-    <row r="2164" spans="1:7">
+    <row r="2164" spans="1:8">
       <c r="A2164" t="s">
         <v>118</v>
       </c>
@@ -63380,7 +63381,7 @@
         <v>504004</v>
       </c>
     </row>
-    <row r="2165" spans="1:5">
+    <row r="2165" spans="1:8">
       <c r="A2165" t="s">
         <v>119</v>
       </c>
@@ -63397,7 +63398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2166" spans="1:7">
+    <row r="2166" spans="1:8">
       <c r="A2166" t="s">
         <v>119</v>
       </c>
@@ -63417,7 +63418,7 @@
         <v>570001</v>
       </c>
     </row>
-    <row r="2167" spans="1:7">
+    <row r="2167" spans="1:8">
       <c r="A2167" t="s">
         <v>119</v>
       </c>
@@ -63555,7 +63556,7 @@
         <v>3384</v>
       </c>
     </row>
-    <row r="2173" spans="1:5">
+    <row r="2173" spans="1:8">
       <c r="A2173" t="s">
         <v>120</v>
       </c>
@@ -63572,7 +63573,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2174" spans="1:7">
+    <row r="2174" spans="1:8">
       <c r="A2174" t="s">
         <v>120</v>
       </c>
@@ -63592,7 +63593,7 @@
         <v>571001</v>
       </c>
     </row>
-    <row r="2175" spans="1:7">
+    <row r="2175" spans="1:8">
       <c r="A2175" t="s">
         <v>120</v>
       </c>
@@ -63612,7 +63613,7 @@
         <v>571002</v>
       </c>
     </row>
-    <row r="2176" spans="1:7">
+    <row r="2176" spans="1:8">
       <c r="A2176" t="s">
         <v>120</v>
       </c>
@@ -63632,7 +63633,7 @@
         <v>571003</v>
       </c>
     </row>
-    <row r="2177" spans="1:7">
+    <row r="2177" spans="1:8">
       <c r="A2177" t="s">
         <v>120</v>
       </c>
@@ -63698,7 +63699,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2180" spans="1:7">
+    <row r="2180" spans="1:8">
       <c r="A2180" t="s">
         <v>120</v>
       </c>
@@ -63718,7 +63719,7 @@
         <v>571007</v>
       </c>
     </row>
-    <row r="2181" spans="1:7">
+    <row r="2181" spans="1:8">
       <c r="A2181" t="s">
         <v>120</v>
       </c>
@@ -63738,7 +63739,7 @@
         <v>571008</v>
       </c>
     </row>
-    <row r="2182" spans="1:7">
+    <row r="2182" spans="1:8">
       <c r="A2182" t="s">
         <v>120</v>
       </c>
@@ -63758,7 +63759,7 @@
         <v>571009</v>
       </c>
     </row>
-    <row r="2183" spans="1:7">
+    <row r="2183" spans="1:8">
       <c r="A2183" t="s">
         <v>120</v>
       </c>
@@ -63778,7 +63779,7 @@
         <v>571010</v>
       </c>
     </row>
-    <row r="2184" spans="1:5">
+    <row r="2184" spans="1:8">
       <c r="A2184" t="s">
         <v>121</v>
       </c>
@@ -63795,7 +63796,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2185" spans="1:7">
+    <row r="2185" spans="1:8">
       <c r="A2185" t="s">
         <v>121</v>
       </c>
@@ -63815,7 +63816,7 @@
         <v>572001</v>
       </c>
     </row>
-    <row r="2186" spans="1:7">
+    <row r="2186" spans="1:8">
       <c r="A2186" t="s">
         <v>121</v>
       </c>
@@ -63904,7 +63905,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2190" spans="1:7">
+    <row r="2190" spans="1:8">
       <c r="A2190" t="s">
         <v>121</v>
       </c>
@@ -63924,7 +63925,7 @@
         <v>572006</v>
       </c>
     </row>
-    <row r="2191" spans="1:7">
+    <row r="2191" spans="1:8">
       <c r="A2191" t="s">
         <v>121</v>
       </c>
@@ -63944,7 +63945,7 @@
         <v>572007</v>
       </c>
     </row>
-    <row r="2192" spans="1:7">
+    <row r="2192" spans="1:8">
       <c r="A2192" t="s">
         <v>121</v>
       </c>
@@ -63964,7 +63965,7 @@
         <v>572008</v>
       </c>
     </row>
-    <row r="2193" spans="1:7">
+    <row r="2193" spans="1:8">
       <c r="A2193" t="s">
         <v>121</v>
       </c>
@@ -63984,7 +63985,7 @@
         <v>572009</v>
       </c>
     </row>
-    <row r="2194" spans="1:7">
+    <row r="2194" spans="1:8">
       <c r="A2194" t="s">
         <v>121</v>
       </c>
@@ -64004,7 +64005,7 @@
         <v>572010</v>
       </c>
     </row>
-    <row r="2195" spans="1:5">
+    <row r="2195" spans="1:8">
       <c r="A2195" t="s">
         <v>78</v>
       </c>
@@ -64021,7 +64022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2196" spans="1:7">
+    <row r="2196" spans="1:8">
       <c r="A2196" t="s">
         <v>78</v>
       </c>
@@ -64044,7 +64045,7 @@
         <v>602000</v>
       </c>
     </row>
-    <row r="2197" spans="1:7">
+    <row r="2197" spans="1:8">
       <c r="A2197" t="s">
         <v>78</v>
       </c>
@@ -64064,7 +64065,7 @@
         <v>602001</v>
       </c>
     </row>
-    <row r="2198" spans="1:7">
+    <row r="2198" spans="1:8">
       <c r="A2198" t="s">
         <v>78</v>
       </c>
@@ -64084,7 +64085,7 @@
         <v>602002</v>
       </c>
     </row>
-    <row r="2199" spans="1:7">
+    <row r="2199" spans="1:8">
       <c r="A2199" t="s">
         <v>78</v>
       </c>
@@ -64150,7 +64151,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2202" spans="1:7">
+    <row r="2202" spans="1:8">
       <c r="A2202" t="s">
         <v>78</v>
       </c>
@@ -64193,7 +64194,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2204" spans="1:7">
+    <row r="2204" spans="1:8">
       <c r="A2204" t="s">
         <v>78</v>
       </c>
@@ -64213,7 +64214,7 @@
         <v>602008</v>
       </c>
     </row>
-    <row r="2205" spans="1:7">
+    <row r="2205" spans="1:8">
       <c r="A2205" t="s">
         <v>78</v>
       </c>
@@ -64233,7 +64234,7 @@
         <v>602009</v>
       </c>
     </row>
-    <row r="2206" spans="1:7">
+    <row r="2206" spans="1:8">
       <c r="A2206" t="s">
         <v>78</v>
       </c>
@@ -64253,7 +64254,7 @@
         <v>602010</v>
       </c>
     </row>
-    <row r="2207" spans="1:7">
+    <row r="2207" spans="1:8">
       <c r="A2207" t="s">
         <v>78</v>
       </c>
@@ -64273,7 +64274,7 @@
         <v>602011</v>
       </c>
     </row>
-    <row r="2208" spans="1:7">
+    <row r="2208" spans="1:8">
       <c r="A2208" t="s">
         <v>78</v>
       </c>
@@ -64293,7 +64294,7 @@
         <v>602012</v>
       </c>
     </row>
-    <row r="2209" spans="1:7">
+    <row r="2209" spans="1:8">
       <c r="A2209" t="s">
         <v>78</v>
       </c>
@@ -64313,7 +64314,7 @@
         <v>602013</v>
       </c>
     </row>
-    <row r="2210" spans="1:7">
+    <row r="2210" spans="1:8">
       <c r="A2210" t="s">
         <v>78</v>
       </c>
@@ -64333,7 +64334,7 @@
         <v>602014</v>
       </c>
     </row>
-    <row r="2211" spans="1:7">
+    <row r="2211" spans="1:8">
       <c r="A2211" t="s">
         <v>78</v>
       </c>
@@ -64353,7 +64354,7 @@
         <v>602015</v>
       </c>
     </row>
-    <row r="2212" spans="1:5">
+    <row r="2212" spans="1:8">
       <c r="A2212" t="s">
         <v>79</v>
       </c>
@@ -64370,7 +64371,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2213" spans="1:7">
+    <row r="2213" spans="1:8">
       <c r="A2213" t="s">
         <v>79</v>
       </c>
@@ -64393,7 +64394,7 @@
         <v>604000</v>
       </c>
     </row>
-    <row r="2214" spans="1:7">
+    <row r="2214" spans="1:8">
       <c r="A2214" t="s">
         <v>79</v>
       </c>
@@ -64413,7 +64414,7 @@
         <v>604001</v>
       </c>
     </row>
-    <row r="2215" spans="1:7">
+    <row r="2215" spans="1:8">
       <c r="A2215" t="s">
         <v>79</v>
       </c>
@@ -64433,7 +64434,7 @@
         <v>604002</v>
       </c>
     </row>
-    <row r="2216" spans="1:7">
+    <row r="2216" spans="1:8">
       <c r="A2216" t="s">
         <v>79</v>
       </c>
@@ -64522,7 +64523,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2220" spans="1:7">
+    <row r="2220" spans="1:8">
       <c r="A2220" t="s">
         <v>79</v>
       </c>
@@ -64634,7 +64635,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2225" spans="1:7">
+    <row r="2225" spans="1:8">
       <c r="A2225" t="s">
         <v>79</v>
       </c>
@@ -64654,7 +64655,7 @@
         <v>604012</v>
       </c>
     </row>
-    <row r="2226" spans="1:7">
+    <row r="2226" spans="1:8">
       <c r="A2226" t="s">
         <v>79</v>
       </c>
@@ -64674,7 +64675,7 @@
         <v>604013</v>
       </c>
     </row>
-    <row r="2227" spans="1:7">
+    <row r="2227" spans="1:8">
       <c r="A2227" t="s">
         <v>79</v>
       </c>
@@ -64694,7 +64695,7 @@
         <v>604014</v>
       </c>
     </row>
-    <row r="2228" spans="1:7">
+    <row r="2228" spans="1:8">
       <c r="A2228" t="s">
         <v>79</v>
       </c>
@@ -64714,7 +64715,7 @@
         <v>604015</v>
       </c>
     </row>
-    <row r="2229" spans="1:7">
+    <row r="2229" spans="1:8">
       <c r="A2229" t="s">
         <v>79</v>
       </c>
@@ -64734,7 +64735,7 @@
         <v>604016</v>
       </c>
     </row>
-    <row r="2230" spans="1:7">
+    <row r="2230" spans="1:8">
       <c r="A2230" t="s">
         <v>79</v>
       </c>
@@ -64754,7 +64755,7 @@
         <v>604017</v>
       </c>
     </row>
-    <row r="2231" spans="1:7">
+    <row r="2231" spans="1:8">
       <c r="A2231" t="s">
         <v>79</v>
       </c>
@@ -64774,7 +64775,7 @@
         <v>604018</v>
       </c>
     </row>
-    <row r="2232" spans="1:5">
+    <row r="2232" spans="1:8">
       <c r="A2232" t="s">
         <v>59</v>
       </c>
@@ -64817,7 +64818,7 @@
         <v>3721</v>
       </c>
     </row>
-    <row r="2234" spans="1:7">
+    <row r="2234" spans="1:8">
       <c r="A2234" t="s">
         <v>59</v>
       </c>
@@ -64837,7 +64838,7 @@
         <v>44001</v>
       </c>
     </row>
-    <row r="2235" spans="1:7">
+    <row r="2235" spans="1:8">
       <c r="A2235" t="s">
         <v>59</v>
       </c>
@@ -64972,7 +64973,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2241" spans="1:7">
+    <row r="2241" spans="1:8">
       <c r="A2241" t="s">
         <v>59</v>
       </c>
@@ -65383,7 +65384,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2259" spans="1:7">
+    <row r="2259" spans="1:8">
       <c r="A2259" t="s">
         <v>59</v>
       </c>
@@ -65403,7 +65404,7 @@
         <v>44185</v>
       </c>
     </row>
-    <row r="2260" spans="1:7">
+    <row r="2260" spans="1:8">
       <c r="A2260" t="s">
         <v>59</v>
       </c>
@@ -67148,7 +67149,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2336" spans="1:7">
+    <row r="2336" spans="1:8">
       <c r="A2336" t="s">
         <v>59</v>
       </c>
@@ -67536,7 +67537,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2353" spans="1:7">
+    <row r="2353" spans="1:8">
       <c r="A2353" t="s">
         <v>59</v>
       </c>
@@ -67556,7 +67557,7 @@
         <v>44188</v>
       </c>
     </row>
-    <row r="2354" spans="1:7">
+    <row r="2354" spans="1:8">
       <c r="A2354" t="s">
         <v>59</v>
       </c>
@@ -68956,7 +68957,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2415" spans="1:5">
+    <row r="2415" spans="1:8">
       <c r="A2415" t="s">
         <v>61</v>
       </c>
@@ -68996,7 +68997,7 @@
         <v>3721</v>
       </c>
     </row>
-    <row r="2417" spans="1:7">
+    <row r="2417" spans="1:8">
       <c r="A2417" t="s">
         <v>61</v>
       </c>
@@ -69016,7 +69017,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="2418" spans="1:7">
+    <row r="2418" spans="1:8">
       <c r="A2418" t="s">
         <v>61</v>
       </c>
@@ -69036,7 +69037,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="2419" spans="1:7">
+    <row r="2419" spans="1:8">
       <c r="A2419" t="s">
         <v>61</v>
       </c>
@@ -69470,7 +69471,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2438" spans="1:7">
+    <row r="2438" spans="1:8">
       <c r="A2438" t="s">
         <v>61</v>
       </c>
@@ -69490,7 +69491,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="2439" spans="1:7">
+    <row r="2439" spans="1:8">
       <c r="A2439" t="s">
         <v>61</v>
       </c>
@@ -69924,7 +69925,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2458" spans="1:7">
+    <row r="2458" spans="1:8">
       <c r="A2458" t="s">
         <v>61</v>
       </c>
@@ -69944,7 +69945,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="2459" spans="1:7">
+    <row r="2459" spans="1:8">
       <c r="A2459" t="s">
         <v>61</v>
       </c>
@@ -71160,7 +71161,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="2512" spans="1:5">
+    <row r="2512" spans="1:8">
       <c r="A2512" t="s">
         <v>62</v>
       </c>
@@ -71177,7 +71178,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2513" spans="1:7">
+    <row r="2513" spans="1:8">
       <c r="A2513" t="s">
         <v>62</v>
       </c>
@@ -71197,7 +71198,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="2514" spans="1:7">
+    <row r="2514" spans="1:8">
       <c r="A2514" t="s">
         <v>62</v>
       </c>
@@ -71217,7 +71218,7 @@
         <v>48001</v>
       </c>
     </row>
-    <row r="2515" spans="1:7">
+    <row r="2515" spans="1:8">
       <c r="A2515" t="s">
         <v>62</v>
       </c>
@@ -71237,7 +71238,7 @@
         <v>48163</v>
       </c>
     </row>
-    <row r="2516" spans="1:7">
+    <row r="2516" spans="1:8">
       <c r="A2516" t="s">
         <v>62</v>
       </c>
@@ -74914,7 +74915,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2676" spans="1:7">
+    <row r="2676" spans="1:8">
       <c r="A2676" t="s">
         <v>62</v>
       </c>
@@ -74934,7 +74935,7 @@
         <v>48101</v>
       </c>
     </row>
-    <row r="2677" spans="1:5">
+    <row r="2677" spans="1:8">
       <c r="A2677" t="s">
         <v>63</v>
       </c>
@@ -74951,7 +74952,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2678" spans="1:7">
+    <row r="2678" spans="1:8">
       <c r="A2678" t="s">
         <v>63</v>
       </c>
@@ -74971,7 +74972,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="2679" spans="1:7">
+    <row r="2679" spans="1:8">
       <c r="A2679" t="s">
         <v>63</v>
       </c>
@@ -75359,7 +75360,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2696" spans="1:7">
+    <row r="2696" spans="1:8">
       <c r="A2696" t="s">
         <v>63</v>
       </c>

--- a/QSExt/Resource/TinySoftDBInfo.xlsx
+++ b/QSExt/Resource/TinySoftDBInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="20190" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="TableInfo" sheetId="2" r:id="rId1"/>
@@ -14795,7 +14795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -14992,7 +14992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -15032,7 +15032,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -16470,7 +16470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -16487,7 +16487,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -16595,7 +16595,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -16612,7 +16612,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -17546,7 +17546,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -17563,7 +17563,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -17617,7 +17617,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -18554,7 +18554,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -18571,7 +18571,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -18611,7 +18611,7 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -19291,7 +19291,7 @@
         <v>10043</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -19311,7 +19311,7 @@
         <v>10044</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>10038</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -19351,7 +19351,7 @@
         <v>10039</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -19371,7 +19371,7 @@
         <v>10040</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -19391,7 +19391,7 @@
         <v>10041</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -19411,7 +19411,7 @@
         <v>10045</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -19431,7 +19431,7 @@
         <v>10046</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>23</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -19565,7 +19565,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>23</v>
       </c>
@@ -19702,7 +19702,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>23</v>
       </c>
@@ -19719,7 +19719,7 @@
         <v>12018</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>23</v>
       </c>
@@ -19776,7 +19776,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>23</v>
       </c>
@@ -19793,7 +19793,7 @@
         <v>12023</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -19810,7 +19810,7 @@
         <v>12024</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>23</v>
       </c>
@@ -19827,7 +19827,7 @@
         <v>12025</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>23</v>
       </c>
@@ -19844,7 +19844,7 @@
         <v>12026</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>23</v>
       </c>
@@ -19861,7 +19861,7 @@
         <v>12027</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>23</v>
       </c>
@@ -19878,7 +19878,7 @@
         <v>12001</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>23</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>12002</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>23</v>
       </c>
@@ -19912,7 +19912,7 @@
         <v>12028</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>12029</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -19946,7 +19946,7 @@
         <v>12033</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>23</v>
       </c>
@@ -19963,7 +19963,7 @@
         <v>12034</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>12035</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>23</v>
       </c>
@@ -19997,7 +19997,7 @@
         <v>12036</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>23</v>
       </c>
@@ -20014,7 +20014,7 @@
         <v>12037</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>23</v>
       </c>
@@ -20251,7 +20251,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:7">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>12015</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:7">
       <c r="A197" t="s">
         <v>23</v>
       </c>
@@ -20285,7 +20285,7 @@
         <v>12048</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>23</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>12049</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:7">
       <c r="A199" t="s">
         <v>23</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>12050</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:7">
       <c r="A200" t="s">
         <v>23</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>12051</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:7">
       <c r="A201" t="s">
         <v>23</v>
       </c>
@@ -20353,7 +20353,7 @@
         <v>12052</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:7">
       <c r="A202" t="s">
         <v>23</v>
       </c>
@@ -20370,7 +20370,7 @@
         <v>12053</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:7">
       <c r="A203" t="s">
         <v>23</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
         <v>23</v>
       </c>
@@ -20704,7 +20704,7 @@
         <v>12070</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
         <v>25</v>
       </c>
@@ -20744,7 +20744,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -20764,7 +20764,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -20784,7 +20784,7 @@
         <v>14002</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>14003</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
         <v>29</v>
       </c>
@@ -20821,7 +20821,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>29</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>15001</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -20864,7 +20864,7 @@
         <v>15003</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:7">
       <c r="A228" t="s">
         <v>29</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>15004</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:7">
       <c r="A229" t="s">
         <v>29</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>15005</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
         <v>31</v>
       </c>
@@ -20921,7 +20921,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>31</v>
       </c>
@@ -20944,7 +20944,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>31</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>31</v>
       </c>
@@ -21490,7 +21490,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>31</v>
       </c>
@@ -21510,7 +21510,7 @@
         <v>16042</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
         <v>33</v>
       </c>
@@ -21527,7 +21527,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>33</v>
       </c>
@@ -21550,7 +21550,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>33</v>
       </c>
@@ -21570,7 +21570,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>33</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
         <v>35</v>
       </c>
@@ -21653,7 +21653,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>35</v>
       </c>
@@ -21673,7 +21673,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>35</v>
       </c>
@@ -21693,7 +21693,7 @@
         <v>18001</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>35</v>
       </c>
@@ -21713,7 +21713,7 @@
         <v>18002</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>35</v>
       </c>
@@ -21733,7 +21733,7 @@
         <v>18003</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>35</v>
       </c>
@@ -21753,7 +21753,7 @@
         <v>18004</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>35</v>
       </c>
@@ -21773,7 +21773,7 @@
         <v>18005</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>35</v>
       </c>
@@ -21934,7 +21934,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>35</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>18012</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>35</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>18013</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>35</v>
       </c>
@@ -21994,7 +21994,7 @@
         <v>18015</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>35</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>18014</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>39</v>
       </c>
@@ -22031,7 +22031,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>39</v>
       </c>
@@ -22054,7 +22054,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>39</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>39</v>
       </c>
@@ -22117,7 +22117,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>39</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>20008</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>39</v>
       </c>
@@ -22315,7 +22315,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>39</v>
       </c>
@@ -22335,7 +22335,7 @@
         <v>20030</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>39</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>20031</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
         <v>39</v>
       </c>
@@ -22375,7 +22375,7 @@
         <v>20032</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
         <v>39</v>
       </c>
@@ -22395,7 +22395,7 @@
         <v>20033</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
         <v>39</v>
       </c>
@@ -22415,7 +22415,7 @@
         <v>20034</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
         <v>39</v>
       </c>
@@ -22435,7 +22435,7 @@
         <v>20036</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
         <v>39</v>
       </c>
@@ -22501,7 +22501,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
         <v>39</v>
       </c>
@@ -22521,7 +22521,7 @@
         <v>20043</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
         <v>39</v>
       </c>
@@ -22541,7 +22541,7 @@
         <v>20044</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
         <v>39</v>
       </c>
@@ -22561,7 +22561,7 @@
         <v>20069</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:5">
       <c r="A307" t="s">
         <v>40</v>
       </c>
@@ -22578,7 +22578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
         <v>40</v>
       </c>
@@ -22601,7 +22601,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:7">
       <c r="A309" t="s">
         <v>40</v>
       </c>
@@ -22621,7 +22621,7 @@
         <v>22001</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:7">
       <c r="A310" t="s">
         <v>40</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>22002</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:7">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -22661,7 +22661,7 @@
         <v>22003</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:7">
       <c r="A312" t="s">
         <v>40</v>
       </c>
@@ -22704,7 +22704,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:7">
       <c r="A314" t="s">
         <v>40</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>22006</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:7">
       <c r="A315" t="s">
         <v>40</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>22007</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:7">
       <c r="A316" t="s">
         <v>40</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>22008</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:7">
       <c r="A317" t="s">
         <v>40</v>
       </c>
@@ -22784,7 +22784,7 @@
         <v>22009</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:7">
       <c r="A318" t="s">
         <v>40</v>
       </c>
@@ -22827,7 +22827,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:7">
       <c r="A320" t="s">
         <v>40</v>
       </c>
@@ -23167,7 +23167,7 @@
         <v>22028</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:7">
       <c r="A337" t="s">
         <v>40</v>
       </c>
@@ -23187,7 +23187,7 @@
         <v>22029</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:7">
       <c r="A338" t="s">
         <v>40</v>
       </c>
@@ -23207,7 +23207,7 @@
         <v>22030</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:7">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -23227,7 +23227,7 @@
         <v>22031</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:7">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:7">
       <c r="A347" t="s">
         <v>40</v>
       </c>
@@ -23405,7 +23405,7 @@
         <v>22039</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:7">
       <c r="A348" t="s">
         <v>40</v>
       </c>
@@ -23908,7 +23908,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:7">
       <c r="A370" t="s">
         <v>40</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:5">
       <c r="A375" t="s">
         <v>41</v>
       </c>
@@ -24037,7 +24037,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:7">
       <c r="A376" t="s">
         <v>41</v>
       </c>
@@ -24083,7 +24083,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:7">
       <c r="A378" t="s">
         <v>41</v>
       </c>
@@ -24103,7 +24103,7 @@
         <v>24002</v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:7">
       <c r="A379" t="s">
         <v>41</v>
       </c>
@@ -24169,7 +24169,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:7">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -24189,7 +24189,7 @@
         <v>24006</v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:7">
       <c r="A383" t="s">
         <v>41</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>24007</v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:7">
       <c r="A384" t="s">
         <v>41</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>24008</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:7">
       <c r="A385" t="s">
         <v>41</v>
       </c>
@@ -24249,7 +24249,7 @@
         <v>24009</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:7">
       <c r="A386" t="s">
         <v>41</v>
       </c>
@@ -24361,7 +24361,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:7">
       <c r="A391" t="s">
         <v>41</v>
       </c>
@@ -24381,7 +24381,7 @@
         <v>24015</v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:5">
       <c r="A392" t="s">
         <v>42</v>
       </c>
@@ -24398,7 +24398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:7">
       <c r="A393" t="s">
         <v>42</v>
       </c>
@@ -24444,7 +24444,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:7">
       <c r="A395" t="s">
         <v>42</v>
       </c>
@@ -24464,7 +24464,7 @@
         <v>26002</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:7">
       <c r="A396" t="s">
         <v>42</v>
       </c>
@@ -24530,7 +24530,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:7">
       <c r="A399" t="s">
         <v>42</v>
       </c>
@@ -24550,7 +24550,7 @@
         <v>26006</v>
       </c>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" spans="1:7">
       <c r="A400" t="s">
         <v>42</v>
       </c>
@@ -24570,7 +24570,7 @@
         <v>26007</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:7">
       <c r="A401" t="s">
         <v>42</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>26008</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:7">
       <c r="A402" t="s">
         <v>42</v>
       </c>
@@ -24610,7 +24610,7 @@
         <v>26009</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:7">
       <c r="A403" t="s">
         <v>42</v>
       </c>
@@ -24722,7 +24722,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:7">
       <c r="A408" t="s">
         <v>42</v>
       </c>
@@ -24742,7 +24742,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:5">
       <c r="A409" t="s">
         <v>43</v>
       </c>
@@ -24759,7 +24759,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:7">
       <c r="A410" t="s">
         <v>43</v>
       </c>
@@ -24782,7 +24782,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:7">
       <c r="A411" t="s">
         <v>43</v>
       </c>
@@ -24802,7 +24802,7 @@
         <v>27001</v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" spans="1:7">
       <c r="A412" t="s">
         <v>43</v>
       </c>
@@ -24822,7 +24822,7 @@
         <v>27002</v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" spans="1:7">
       <c r="A413" t="s">
         <v>43</v>
       </c>
@@ -24842,7 +24842,7 @@
         <v>27003</v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" spans="1:7">
       <c r="A414" t="s">
         <v>43</v>
       </c>
@@ -24862,7 +24862,7 @@
         <v>27004</v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" spans="1:7">
       <c r="A415" t="s">
         <v>43</v>
       </c>
@@ -24882,7 +24882,7 @@
         <v>27005</v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" spans="1:7">
       <c r="A416" t="s">
         <v>43</v>
       </c>
@@ -26182,7 +26182,7 @@
         <v>27070</v>
       </c>
     </row>
-    <row r="481" spans="1:8">
+    <row r="481" spans="1:7">
       <c r="A481" t="s">
         <v>43</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>27071</v>
       </c>
     </row>
-    <row r="482" spans="1:8">
+    <row r="482" spans="1:7">
       <c r="A482" t="s">
         <v>43</v>
       </c>
@@ -26222,7 +26222,7 @@
         <v>27072</v>
       </c>
     </row>
-    <row r="483" spans="1:8">
+    <row r="483" spans="1:7">
       <c r="A483" t="s">
         <v>43</v>
       </c>
@@ -26242,7 +26242,7 @@
         <v>27073</v>
       </c>
     </row>
-    <row r="484" spans="1:8">
+    <row r="484" spans="1:7">
       <c r="A484" t="s">
         <v>43</v>
       </c>
@@ -26262,7 +26262,7 @@
         <v>27074</v>
       </c>
     </row>
-    <row r="485" spans="1:8">
+    <row r="485" spans="1:7">
       <c r="A485" t="s">
         <v>43</v>
       </c>
@@ -26282,7 +26282,7 @@
         <v>27075</v>
       </c>
     </row>
-    <row r="486" spans="1:8">
+    <row r="486" spans="1:7">
       <c r="A486" t="s">
         <v>43</v>
       </c>
@@ -26302,7 +26302,7 @@
         <v>27076</v>
       </c>
     </row>
-    <row r="487" spans="1:8">
+    <row r="487" spans="1:7">
       <c r="A487" t="s">
         <v>43</v>
       </c>
@@ -26322,7 +26322,7 @@
         <v>27077</v>
       </c>
     </row>
-    <row r="488" spans="1:8">
+    <row r="488" spans="1:7">
       <c r="A488" t="s">
         <v>43</v>
       </c>
@@ -26342,7 +26342,7 @@
         <v>27078</v>
       </c>
     </row>
-    <row r="489" spans="1:8">
+    <row r="489" spans="1:7">
       <c r="A489" t="s">
         <v>43</v>
       </c>
@@ -26362,7 +26362,7 @@
         <v>27079</v>
       </c>
     </row>
-    <row r="490" spans="1:8">
+    <row r="490" spans="1:7">
       <c r="A490" t="s">
         <v>43</v>
       </c>
@@ -26382,7 +26382,7 @@
         <v>27080</v>
       </c>
     </row>
-    <row r="491" spans="1:8">
+    <row r="491" spans="1:5">
       <c r="A491" t="s">
         <v>44</v>
       </c>
@@ -26399,7 +26399,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="492" spans="1:8">
+    <row r="492" spans="1:7">
       <c r="A492" t="s">
         <v>44</v>
       </c>
@@ -26422,7 +26422,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="493" spans="1:8">
+    <row r="493" spans="1:7">
       <c r="A493" t="s">
         <v>44</v>
       </c>
@@ -26465,7 +26465,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="495" spans="1:8">
+    <row r="495" spans="1:7">
       <c r="A495" t="s">
         <v>44</v>
       </c>
@@ -26485,7 +26485,7 @@
         <v>28003</v>
       </c>
     </row>
-    <row r="496" spans="1:8">
+    <row r="496" spans="1:5">
       <c r="A496" t="s">
         <v>45</v>
       </c>
@@ -26502,7 +26502,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" spans="1:7">
       <c r="A497" t="s">
         <v>45</v>
       </c>
@@ -26525,7 +26525,7 @@
         <v>29001</v>
       </c>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" spans="1:7">
       <c r="A498" t="s">
         <v>45</v>
       </c>
@@ -26545,7 +26545,7 @@
         <v>29002</v>
       </c>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" spans="1:7">
       <c r="A499" t="s">
         <v>45</v>
       </c>
@@ -26565,7 +26565,7 @@
         <v>29003</v>
       </c>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" spans="1:7">
       <c r="A500" t="s">
         <v>45</v>
       </c>
@@ -26585,7 +26585,7 @@
         <v>29004</v>
       </c>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" spans="1:7">
       <c r="A501" t="s">
         <v>45</v>
       </c>
@@ -26628,7 +26628,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" spans="1:5">
       <c r="A503" t="s">
         <v>46</v>
       </c>
@@ -26645,7 +26645,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" spans="1:7">
       <c r="A504" t="s">
         <v>46</v>
       </c>
@@ -26668,7 +26668,7 @@
         <v>30001</v>
       </c>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" spans="1:7">
       <c r="A505" t="s">
         <v>46</v>
       </c>
@@ -26691,7 +26691,7 @@
         <v>30002</v>
       </c>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" spans="1:7">
       <c r="A506" t="s">
         <v>46</v>
       </c>
@@ -26711,7 +26711,7 @@
         <v>30003</v>
       </c>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" spans="1:7">
       <c r="A507" t="s">
         <v>46</v>
       </c>
@@ -26731,7 +26731,7 @@
         <v>30004</v>
       </c>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" spans="1:7">
       <c r="A508" t="s">
         <v>46</v>
       </c>
@@ -26751,7 +26751,7 @@
         <v>30005</v>
       </c>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" spans="1:7">
       <c r="A509" t="s">
         <v>46</v>
       </c>
@@ -26771,7 +26771,7 @@
         <v>30006</v>
       </c>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" spans="1:7">
       <c r="A510" t="s">
         <v>46</v>
       </c>
@@ -26791,7 +26791,7 @@
         <v>30007</v>
       </c>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" spans="1:7">
       <c r="A511" t="s">
         <v>46</v>
       </c>
@@ -26811,7 +26811,7 @@
         <v>30008</v>
       </c>
     </row>
-    <row r="512" spans="1:8">
+    <row r="512" spans="1:7">
       <c r="A512" t="s">
         <v>46</v>
       </c>
@@ -26992,7 +26992,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="520" spans="1:8">
+    <row r="520" spans="1:7">
       <c r="A520" t="s">
         <v>46</v>
       </c>
@@ -27012,7 +27012,7 @@
         <v>30017</v>
       </c>
     </row>
-    <row r="521" spans="1:8">
+    <row r="521" spans="1:7">
       <c r="A521" t="s">
         <v>46</v>
       </c>
@@ -27032,7 +27032,7 @@
         <v>30018</v>
       </c>
     </row>
-    <row r="522" spans="1:8">
+    <row r="522" spans="1:5">
       <c r="A522" t="s">
         <v>48</v>
       </c>
@@ -27049,7 +27049,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="523" spans="1:8">
+    <row r="523" spans="1:7">
       <c r="A523" t="s">
         <v>48</v>
       </c>
@@ -27069,7 +27069,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="524" spans="1:8">
+    <row r="524" spans="1:7">
       <c r="A524" t="s">
         <v>48</v>
       </c>
@@ -27092,7 +27092,7 @@
         <v>40001</v>
       </c>
     </row>
-    <row r="525" spans="1:8">
+    <row r="525" spans="1:7">
       <c r="A525" t="s">
         <v>48</v>
       </c>
@@ -27112,7 +27112,7 @@
         <v>40002</v>
       </c>
     </row>
-    <row r="526" spans="1:8">
+    <row r="526" spans="1:7">
       <c r="A526" t="s">
         <v>48</v>
       </c>
@@ -27178,7 +27178,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="529" spans="1:8">
+    <row r="529" spans="1:7">
       <c r="A529" t="s">
         <v>48</v>
       </c>
@@ -27198,7 +27198,7 @@
         <v>40007</v>
       </c>
     </row>
-    <row r="530" spans="1:8">
+    <row r="530" spans="1:7">
       <c r="A530" t="s">
         <v>48</v>
       </c>
@@ -27218,7 +27218,7 @@
         <v>40008</v>
       </c>
     </row>
-    <row r="531" spans="1:8">
+    <row r="531" spans="1:7">
       <c r="A531" t="s">
         <v>48</v>
       </c>
@@ -27238,7 +27238,7 @@
         <v>40009</v>
       </c>
     </row>
-    <row r="532" spans="1:8">
+    <row r="532" spans="1:7">
       <c r="A532" t="s">
         <v>48</v>
       </c>
@@ -27258,7 +27258,7 @@
         <v>40011</v>
       </c>
     </row>
-    <row r="533" spans="1:8">
+    <row r="533" spans="1:7">
       <c r="A533" t="s">
         <v>48</v>
       </c>
@@ -27278,7 +27278,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="534" spans="1:8">
+    <row r="534" spans="1:7">
       <c r="A534" t="s">
         <v>48</v>
       </c>
@@ -27298,7 +27298,7 @@
         <v>40004</v>
       </c>
     </row>
-    <row r="535" spans="1:8">
+    <row r="535" spans="1:5">
       <c r="A535" t="s">
         <v>49</v>
       </c>
@@ -27315,7 +27315,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" spans="1:7">
       <c r="A536" t="s">
         <v>49</v>
       </c>
@@ -27335,7 +27335,7 @@
         <v>41001</v>
       </c>
     </row>
-    <row r="537" spans="1:8">
+    <row r="537" spans="1:7">
       <c r="A537" t="s">
         <v>49</v>
       </c>
@@ -27588,7 +27588,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="548" spans="1:8">
+    <row r="548" spans="1:5">
       <c r="A548" t="s">
         <v>50</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="549" spans="1:8">
+    <row r="549" spans="1:7">
       <c r="A549" t="s">
         <v>50</v>
       </c>
@@ -27628,7 +27628,7 @@
         <v>122001</v>
       </c>
     </row>
-    <row r="550" spans="1:8">
+    <row r="550" spans="1:7">
       <c r="A550" t="s">
         <v>50</v>
       </c>
@@ -27648,7 +27648,7 @@
         <v>122002</v>
       </c>
     </row>
-    <row r="551" spans="1:8">
+    <row r="551" spans="1:7">
       <c r="A551" t="s">
         <v>50</v>
       </c>
@@ -27668,7 +27668,7 @@
         <v>122003</v>
       </c>
     </row>
-    <row r="552" spans="1:8">
+    <row r="552" spans="1:7">
       <c r="A552" t="s">
         <v>50</v>
       </c>
@@ -27688,7 +27688,7 @@
         <v>122004</v>
       </c>
     </row>
-    <row r="553" spans="1:8">
+    <row r="553" spans="1:5">
       <c r="A553" t="s">
         <v>51</v>
       </c>
@@ -27705,7 +27705,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="554" spans="1:8">
+    <row r="554" spans="1:7">
       <c r="A554" t="s">
         <v>51</v>
       </c>
@@ -27797,7 +27797,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" spans="1:7">
       <c r="A558" t="s">
         <v>51</v>
       </c>
@@ -27817,7 +27817,7 @@
         <v>124005</v>
       </c>
     </row>
-    <row r="559" spans="1:8">
+    <row r="559" spans="1:7">
       <c r="A559" t="s">
         <v>51</v>
       </c>
@@ -27837,7 +27837,7 @@
         <v>124006</v>
       </c>
     </row>
-    <row r="560" spans="1:8">
+    <row r="560" spans="1:7">
       <c r="A560" t="s">
         <v>51</v>
       </c>
@@ -27857,7 +27857,7 @@
         <v>124007</v>
       </c>
     </row>
-    <row r="561" spans="1:8">
+    <row r="561" spans="1:7">
       <c r="A561" t="s">
         <v>51</v>
       </c>
@@ -27877,7 +27877,7 @@
         <v>124008</v>
       </c>
     </row>
-    <row r="562" spans="1:8">
+    <row r="562" spans="1:7">
       <c r="A562" t="s">
         <v>51</v>
       </c>
@@ -27897,7 +27897,7 @@
         <v>124009</v>
       </c>
     </row>
-    <row r="563" spans="1:8">
+    <row r="563" spans="1:5">
       <c r="A563" t="s">
         <v>52</v>
       </c>
@@ -27914,7 +27914,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="564" spans="1:8">
+    <row r="564" spans="1:7">
       <c r="A564" t="s">
         <v>52</v>
       </c>
@@ -28121,7 +28121,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="573" spans="1:8">
+    <row r="573" spans="1:5">
       <c r="A573" t="s">
         <v>53</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="574" spans="1:8">
+    <row r="574" spans="1:7">
       <c r="A574" t="s">
         <v>53</v>
       </c>
@@ -28161,7 +28161,7 @@
         <v>127001</v>
       </c>
     </row>
-    <row r="575" spans="1:8">
+    <row r="575" spans="1:7">
       <c r="A575" t="s">
         <v>53</v>
       </c>
@@ -28181,7 +28181,7 @@
         <v>127002</v>
       </c>
     </row>
-    <row r="576" spans="1:8">
+    <row r="576" spans="1:7">
       <c r="A576" t="s">
         <v>53</v>
       </c>
@@ -28264,7 +28264,7 @@
         <v>127006</v>
       </c>
     </row>
-    <row r="580" spans="1:7">
+    <row r="580" spans="1:5">
       <c r="A580" t="s">
         <v>54</v>
       </c>
@@ -28504,7 +28504,7 @@
         <v>129011</v>
       </c>
     </row>
-    <row r="592" spans="1:7">
+    <row r="592" spans="1:5">
       <c r="A592" t="s">
         <v>55</v>
       </c>
@@ -28521,7 +28521,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="593" spans="1:8">
+    <row r="593" spans="1:7">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -28774,7 +28774,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="604" spans="1:8">
+    <row r="604" spans="1:5">
       <c r="A604" t="s">
         <v>57</v>
       </c>
@@ -28791,7 +28791,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="605" spans="1:8">
+    <row r="605" spans="1:7">
       <c r="A605" t="s">
         <v>57</v>
       </c>
@@ -28814,7 +28814,7 @@
         <v>131001</v>
       </c>
     </row>
-    <row r="606" spans="1:8">
+    <row r="606" spans="1:7">
       <c r="A606" t="s">
         <v>57</v>
       </c>
@@ -28834,7 +28834,7 @@
         <v>131002</v>
       </c>
     </row>
-    <row r="607" spans="1:8">
+    <row r="607" spans="1:7">
       <c r="A607" t="s">
         <v>57</v>
       </c>
@@ -28923,7 +28923,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="611" spans="1:8">
+    <row r="611" spans="1:7">
       <c r="A611" t="s">
         <v>57</v>
       </c>
@@ -28946,7 +28946,7 @@
         <v>131007</v>
       </c>
     </row>
-    <row r="612" spans="1:8">
+    <row r="612" spans="1:5">
       <c r="A612" t="s">
         <v>58</v>
       </c>
@@ -28963,7 +28963,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="613" spans="1:8">
+    <row r="613" spans="1:7">
       <c r="A613" t="s">
         <v>58</v>
       </c>
@@ -28986,7 +28986,7 @@
         <v>132001</v>
       </c>
     </row>
-    <row r="614" spans="1:8">
+    <row r="614" spans="1:7">
       <c r="A614" t="s">
         <v>58</v>
       </c>
@@ -29029,7 +29029,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="616" spans="1:8">
+    <row r="616" spans="1:5">
       <c r="A616" t="s">
         <v>64</v>
       </c>
@@ -29046,7 +29046,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="617" spans="1:8">
+    <row r="617" spans="1:7">
       <c r="A617" t="s">
         <v>64</v>
       </c>
@@ -29066,7 +29066,7 @@
         <v>302000</v>
       </c>
     </row>
-    <row r="618" spans="1:8">
+    <row r="618" spans="1:7">
       <c r="A618" t="s">
         <v>64</v>
       </c>
@@ -29086,7 +29086,7 @@
         <v>302001</v>
       </c>
     </row>
-    <row r="619" spans="1:8">
+    <row r="619" spans="1:7">
       <c r="A619" t="s">
         <v>64</v>
       </c>
@@ -29106,7 +29106,7 @@
         <v>302002</v>
       </c>
     </row>
-    <row r="620" spans="1:8">
+    <row r="620" spans="1:7">
       <c r="A620" t="s">
         <v>64</v>
       </c>
@@ -29126,7 +29126,7 @@
         <v>302003</v>
       </c>
     </row>
-    <row r="621" spans="1:8">
+    <row r="621" spans="1:7">
       <c r="A621" t="s">
         <v>64</v>
       </c>
@@ -29238,7 +29238,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="626" spans="1:8">
+    <row r="626" spans="1:7">
       <c r="A626" t="s">
         <v>64</v>
       </c>
@@ -29258,7 +29258,7 @@
         <v>302009</v>
       </c>
     </row>
-    <row r="627" spans="1:8">
+    <row r="627" spans="1:7">
       <c r="A627" t="s">
         <v>64</v>
       </c>
@@ -29324,7 +29324,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="630" spans="1:8">
+    <row r="630" spans="1:7">
       <c r="A630" t="s">
         <v>64</v>
       </c>
@@ -29344,7 +29344,7 @@
         <v>302013</v>
       </c>
     </row>
-    <row r="631" spans="1:8">
+    <row r="631" spans="1:7">
       <c r="A631" t="s">
         <v>64</v>
       </c>
@@ -29364,7 +29364,7 @@
         <v>302014</v>
       </c>
     </row>
-    <row r="632" spans="1:8">
+    <row r="632" spans="1:7">
       <c r="A632" t="s">
         <v>64</v>
       </c>
@@ -29384,7 +29384,7 @@
         <v>302015</v>
       </c>
     </row>
-    <row r="633" spans="1:8">
+    <row r="633" spans="1:7">
       <c r="A633" t="s">
         <v>64</v>
       </c>
@@ -29404,7 +29404,7 @@
         <v>302016</v>
       </c>
     </row>
-    <row r="634" spans="1:8">
+    <row r="634" spans="1:7">
       <c r="A634" t="s">
         <v>64</v>
       </c>
@@ -29470,7 +29470,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="637" spans="1:8">
+    <row r="637" spans="1:7">
       <c r="A637" t="s">
         <v>64</v>
       </c>
@@ -29513,7 +29513,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="639" spans="1:8">
+    <row r="639" spans="1:7">
       <c r="A639" t="s">
         <v>64</v>
       </c>
@@ -29533,7 +29533,7 @@
         <v>302021</v>
       </c>
     </row>
-    <row r="640" spans="1:8">
+    <row r="640" spans="1:7">
       <c r="A640" t="s">
         <v>64</v>
       </c>
@@ -29873,7 +29873,7 @@
         <v>302038</v>
       </c>
     </row>
-    <row r="657" spans="1:8">
+    <row r="657" spans="1:7">
       <c r="A657" t="s">
         <v>64</v>
       </c>
@@ -29893,7 +29893,7 @@
         <v>302040</v>
       </c>
     </row>
-    <row r="658" spans="1:8">
+    <row r="658" spans="1:7">
       <c r="A658" t="s">
         <v>64</v>
       </c>
@@ -29913,7 +29913,7 @@
         <v>302042</v>
       </c>
     </row>
-    <row r="659" spans="1:8">
+    <row r="659" spans="1:7">
       <c r="A659" t="s">
         <v>64</v>
       </c>
@@ -29933,7 +29933,7 @@
         <v>302043</v>
       </c>
     </row>
-    <row r="660" spans="1:8">
+    <row r="660" spans="1:7">
       <c r="A660" t="s">
         <v>64</v>
       </c>
@@ -29953,7 +29953,7 @@
         <v>302044</v>
       </c>
     </row>
-    <row r="661" spans="1:8">
+    <row r="661" spans="1:7">
       <c r="A661" t="s">
         <v>64</v>
       </c>
@@ -29973,7 +29973,7 @@
         <v>302045</v>
       </c>
     </row>
-    <row r="662" spans="1:8">
+    <row r="662" spans="1:7">
       <c r="A662" t="s">
         <v>64</v>
       </c>
@@ -29993,7 +29993,7 @@
         <v>302046</v>
       </c>
     </row>
-    <row r="663" spans="1:8">
+    <row r="663" spans="1:7">
       <c r="A663" t="s">
         <v>64</v>
       </c>
@@ -30013,7 +30013,7 @@
         <v>302047</v>
       </c>
     </row>
-    <row r="664" spans="1:8">
+    <row r="664" spans="1:5">
       <c r="A664" t="s">
         <v>66</v>
       </c>
@@ -30030,7 +30030,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="665" spans="1:8">
+    <row r="665" spans="1:7">
       <c r="A665" t="s">
         <v>66</v>
       </c>
@@ -30050,7 +30050,7 @@
         <v>303010</v>
       </c>
     </row>
-    <row r="666" spans="1:8">
+    <row r="666" spans="1:7">
       <c r="A666" t="s">
         <v>66</v>
       </c>
@@ -30070,7 +30070,7 @@
         <v>303001</v>
       </c>
     </row>
-    <row r="667" spans="1:8">
+    <row r="667" spans="1:7">
       <c r="A667" t="s">
         <v>66</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="670" spans="1:8">
+    <row r="670" spans="1:7">
       <c r="A670" t="s">
         <v>66</v>
       </c>
@@ -30179,7 +30179,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="672" spans="1:8">
+    <row r="672" spans="1:7">
       <c r="A672" t="s">
         <v>66</v>
       </c>
@@ -30239,7 +30239,7 @@
         <v>303009</v>
       </c>
     </row>
-    <row r="675" spans="1:7">
+    <row r="675" spans="1:5">
       <c r="A675" t="s">
         <v>67</v>
       </c>
@@ -30516,7 +30516,7 @@
         <v>305013</v>
       </c>
     </row>
-    <row r="689" spans="1:8">
+    <row r="689" spans="1:7">
       <c r="A689" t="s">
         <v>67</v>
       </c>
@@ -30536,7 +30536,7 @@
         <v>305014</v>
       </c>
     </row>
-    <row r="690" spans="1:8">
+    <row r="690" spans="1:7">
       <c r="A690" t="s">
         <v>67</v>
       </c>
@@ -30556,7 +30556,7 @@
         <v>305015</v>
       </c>
     </row>
-    <row r="691" spans="1:8">
+    <row r="691" spans="1:7">
       <c r="A691" t="s">
         <v>67</v>
       </c>
@@ -30576,7 +30576,7 @@
         <v>305016</v>
       </c>
     </row>
-    <row r="692" spans="1:8">
+    <row r="692" spans="1:7">
       <c r="A692" t="s">
         <v>67</v>
       </c>
@@ -30596,7 +30596,7 @@
         <v>305017</v>
       </c>
     </row>
-    <row r="693" spans="1:8">
+    <row r="693" spans="1:7">
       <c r="A693" t="s">
         <v>67</v>
       </c>
@@ -30616,7 +30616,7 @@
         <v>305018</v>
       </c>
     </row>
-    <row r="694" spans="1:8">
+    <row r="694" spans="1:7">
       <c r="A694" t="s">
         <v>67</v>
       </c>
@@ -30636,7 +30636,7 @@
         <v>305019</v>
       </c>
     </row>
-    <row r="695" spans="1:8">
+    <row r="695" spans="1:7">
       <c r="A695" t="s">
         <v>67</v>
       </c>
@@ -30656,7 +30656,7 @@
         <v>305020</v>
       </c>
     </row>
-    <row r="696" spans="1:8">
+    <row r="696" spans="1:7">
       <c r="A696" t="s">
         <v>67</v>
       </c>
@@ -30676,7 +30676,7 @@
         <v>305021</v>
       </c>
     </row>
-    <row r="697" spans="1:8">
+    <row r="697" spans="1:5">
       <c r="A697" t="s">
         <v>68</v>
       </c>
@@ -30693,7 +30693,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="698" spans="1:8">
+    <row r="698" spans="1:7">
       <c r="A698" t="s">
         <v>68</v>
       </c>
@@ -30713,7 +30713,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="699" spans="1:8">
+    <row r="699" spans="1:7">
       <c r="A699" t="s">
         <v>68</v>
       </c>
@@ -30733,7 +30733,7 @@
         <v>308001</v>
       </c>
     </row>
-    <row r="700" spans="1:8">
+    <row r="700" spans="1:7">
       <c r="A700" t="s">
         <v>68</v>
       </c>
@@ -30753,7 +30753,7 @@
         <v>308002</v>
       </c>
     </row>
-    <row r="701" spans="1:8">
+    <row r="701" spans="1:7">
       <c r="A701" t="s">
         <v>68</v>
       </c>
@@ -30773,7 +30773,7 @@
         <v>308003</v>
       </c>
     </row>
-    <row r="702" spans="1:8">
+    <row r="702" spans="1:7">
       <c r="A702" t="s">
         <v>68</v>
       </c>
@@ -30793,7 +30793,7 @@
         <v>308004</v>
       </c>
     </row>
-    <row r="703" spans="1:8">
+    <row r="703" spans="1:7">
       <c r="A703" t="s">
         <v>68</v>
       </c>
@@ -30836,7 +30836,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" spans="1:7">
       <c r="A705" t="s">
         <v>68</v>
       </c>
@@ -30856,7 +30856,7 @@
         <v>308007</v>
       </c>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" spans="1:7">
       <c r="A706" t="s">
         <v>68</v>
       </c>
@@ -30899,7 +30899,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="708" spans="1:8">
+    <row r="708" spans="1:7">
       <c r="A708" t="s">
         <v>68</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>308010</v>
       </c>
     </row>
-    <row r="709" spans="1:8">
+    <row r="709" spans="1:7">
       <c r="A709" t="s">
         <v>68</v>
       </c>
@@ -30945,7 +30945,7 @@
         <v>308011</v>
       </c>
     </row>
-    <row r="710" spans="1:8">
+    <row r="710" spans="1:7">
       <c r="A710" t="s">
         <v>68</v>
       </c>
@@ -30965,7 +30965,7 @@
         <v>308012</v>
       </c>
     </row>
-    <row r="711" spans="1:8">
+    <row r="711" spans="1:7">
       <c r="A711" t="s">
         <v>68</v>
       </c>
@@ -30985,7 +30985,7 @@
         <v>308013</v>
       </c>
     </row>
-    <row r="712" spans="1:8">
+    <row r="712" spans="1:7">
       <c r="A712" t="s">
         <v>68</v>
       </c>
@@ -31005,7 +31005,7 @@
         <v>308014</v>
       </c>
     </row>
-    <row r="713" spans="1:8">
+    <row r="713" spans="1:5">
       <c r="A713" t="s">
         <v>69</v>
       </c>
@@ -31022,7 +31022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="714" spans="1:8">
+    <row r="714" spans="1:7">
       <c r="A714" t="s">
         <v>69</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>309000</v>
       </c>
     </row>
-    <row r="715" spans="1:8">
+    <row r="715" spans="1:7">
       <c r="A715" t="s">
         <v>69</v>
       </c>
@@ -31065,7 +31065,7 @@
         <v>309001</v>
       </c>
     </row>
-    <row r="716" spans="1:8">
+    <row r="716" spans="1:7">
       <c r="A716" t="s">
         <v>69</v>
       </c>
@@ -31085,7 +31085,7 @@
         <v>309002</v>
       </c>
     </row>
-    <row r="717" spans="1:8">
+    <row r="717" spans="1:7">
       <c r="A717" t="s">
         <v>69</v>
       </c>
@@ -31105,7 +31105,7 @@
         <v>309003</v>
       </c>
     </row>
-    <row r="718" spans="1:8">
+    <row r="718" spans="1:7">
       <c r="A718" t="s">
         <v>69</v>
       </c>
@@ -31171,7 +31171,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="721" spans="1:8">
+    <row r="721" spans="1:7">
       <c r="A721" t="s">
         <v>69</v>
       </c>
@@ -31191,7 +31191,7 @@
         <v>309007</v>
       </c>
     </row>
-    <row r="722" spans="1:8">
+    <row r="722" spans="1:7">
       <c r="A722" t="s">
         <v>69</v>
       </c>
@@ -31211,7 +31211,7 @@
         <v>309008</v>
       </c>
     </row>
-    <row r="723" spans="1:8">
+    <row r="723" spans="1:7">
       <c r="A723" t="s">
         <v>69</v>
       </c>
@@ -31231,7 +31231,7 @@
         <v>309009</v>
       </c>
     </row>
-    <row r="724" spans="1:8">
+    <row r="724" spans="1:7">
       <c r="A724" t="s">
         <v>69</v>
       </c>
@@ -31251,7 +31251,7 @@
         <v>309010</v>
       </c>
     </row>
-    <row r="725" spans="1:8">
+    <row r="725" spans="1:5">
       <c r="A725" t="s">
         <v>70</v>
       </c>
@@ -31268,7 +31268,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="726" spans="1:8">
+    <row r="726" spans="1:7">
       <c r="A726" t="s">
         <v>70</v>
       </c>
@@ -31291,7 +31291,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="727" spans="1:8">
+    <row r="727" spans="1:7">
       <c r="A727" t="s">
         <v>70</v>
       </c>
@@ -31541,7 +31541,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="738" spans="1:8">
+    <row r="738" spans="1:7">
       <c r="A738" t="s">
         <v>70</v>
       </c>
@@ -31561,7 +31561,7 @@
         <v>310012</v>
       </c>
     </row>
-    <row r="739" spans="1:8">
+    <row r="739" spans="1:5">
       <c r="A739" t="s">
         <v>71</v>
       </c>
@@ -31578,7 +31578,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="740" spans="1:8">
+    <row r="740" spans="1:7">
       <c r="A740" t="s">
         <v>71</v>
       </c>
@@ -32429,7 +32429,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="777" spans="1:8">
+    <row r="777" spans="1:5">
       <c r="A777" t="s">
         <v>76</v>
       </c>
@@ -32446,7 +32446,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="778" spans="1:8">
+    <row r="778" spans="1:7">
       <c r="A778" t="s">
         <v>76</v>
       </c>
@@ -32469,7 +32469,7 @@
         <v>318000</v>
       </c>
     </row>
-    <row r="779" spans="1:8">
+    <row r="779" spans="1:7">
       <c r="A779" t="s">
         <v>76</v>
       </c>
@@ -32489,7 +32489,7 @@
         <v>318001</v>
       </c>
     </row>
-    <row r="780" spans="1:8">
+    <row r="780" spans="1:7">
       <c r="A780" t="s">
         <v>76</v>
       </c>
@@ -32509,7 +32509,7 @@
         <v>318003</v>
       </c>
     </row>
-    <row r="781" spans="1:8">
+    <row r="781" spans="1:7">
       <c r="A781" t="s">
         <v>76</v>
       </c>
@@ -32598,7 +32598,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="785" spans="1:8">
+    <row r="785" spans="1:7">
       <c r="A785" t="s">
         <v>76</v>
       </c>
@@ -32756,7 +32756,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="792" spans="1:8">
+    <row r="792" spans="1:7">
       <c r="A792" t="s">
         <v>76</v>
       </c>
@@ -32776,7 +32776,7 @@
         <v>318007</v>
       </c>
     </row>
-    <row r="793" spans="1:8">
+    <row r="793" spans="1:7">
       <c r="A793" t="s">
         <v>76</v>
       </c>
@@ -32796,7 +32796,7 @@
         <v>318008</v>
       </c>
     </row>
-    <row r="794" spans="1:8">
+    <row r="794" spans="1:5">
       <c r="A794" t="s">
         <v>77</v>
       </c>
@@ -32813,7 +32813,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="795" spans="1:8">
+    <row r="795" spans="1:7">
       <c r="A795" t="s">
         <v>77</v>
       </c>
@@ -32836,7 +32836,7 @@
         <v>322000</v>
       </c>
     </row>
-    <row r="796" spans="1:8">
+    <row r="796" spans="1:7">
       <c r="A796" t="s">
         <v>77</v>
       </c>
@@ -33868,7 +33868,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="841" spans="1:8">
+    <row r="841" spans="1:7">
       <c r="A841" t="s">
         <v>77</v>
       </c>
@@ -33888,7 +33888,7 @@
         <v>322016</v>
       </c>
     </row>
-    <row r="842" spans="1:8">
+    <row r="842" spans="1:5">
       <c r="A842" t="s">
         <v>74</v>
       </c>
@@ -33905,7 +33905,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="843" spans="1:8">
+    <row r="843" spans="1:7">
       <c r="A843" t="s">
         <v>74</v>
       </c>
@@ -33928,7 +33928,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="844" spans="1:8">
+    <row r="844" spans="1:7">
       <c r="A844" t="s">
         <v>74</v>
       </c>
@@ -34040,7 +34040,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="849" spans="1:8">
+    <row r="849" spans="1:7">
       <c r="A849" t="s">
         <v>74</v>
       </c>
@@ -34060,7 +34060,7 @@
         <v>324006</v>
       </c>
     </row>
-    <row r="850" spans="1:8">
+    <row r="850" spans="1:7">
       <c r="A850" t="s">
         <v>74</v>
       </c>
@@ -34080,7 +34080,7 @@
         <v>324007</v>
       </c>
     </row>
-    <row r="851" spans="1:8">
+    <row r="851" spans="1:5">
       <c r="A851" t="s">
         <v>72</v>
       </c>
@@ -34097,7 +34097,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="852" spans="1:8">
+    <row r="852" spans="1:7">
       <c r="A852" t="s">
         <v>72</v>
       </c>
@@ -34117,7 +34117,7 @@
         <v>328000</v>
       </c>
     </row>
-    <row r="853" spans="1:8">
+    <row r="853" spans="1:7">
       <c r="A853" t="s">
         <v>72</v>
       </c>
@@ -34140,7 +34140,7 @@
         <v>328001</v>
       </c>
     </row>
-    <row r="854" spans="1:8">
+    <row r="854" spans="1:7">
       <c r="A854" t="s">
         <v>72</v>
       </c>
@@ -34252,7 +34252,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="859" spans="1:8">
+    <row r="859" spans="1:7">
       <c r="A859" t="s">
         <v>72</v>
       </c>
@@ -34272,7 +34272,7 @@
         <v>328007</v>
       </c>
     </row>
-    <row r="860" spans="1:8">
+    <row r="860" spans="1:5">
       <c r="A860" t="s">
         <v>73</v>
       </c>
@@ -34289,7 +34289,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="861" spans="1:8">
+    <row r="861" spans="1:7">
       <c r="A861" t="s">
         <v>73</v>
       </c>
@@ -34427,7 +34427,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="867" spans="1:8">
+    <row r="867" spans="1:7">
       <c r="A867" t="s">
         <v>73</v>
       </c>
@@ -34516,7 +34516,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="871" spans="1:8">
+    <row r="871" spans="1:7">
       <c r="A871" t="s">
         <v>73</v>
       </c>
@@ -34536,7 +34536,7 @@
         <v>346011</v>
       </c>
     </row>
-    <row r="872" spans="1:8">
+    <row r="872" spans="1:7">
       <c r="A872" t="s">
         <v>73</v>
       </c>
@@ -34556,7 +34556,7 @@
         <v>346012</v>
       </c>
     </row>
-    <row r="873" spans="1:8">
+    <row r="873" spans="1:7">
       <c r="A873" t="s">
         <v>73</v>
       </c>
@@ -34645,7 +34645,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="877" spans="1:8">
+    <row r="877" spans="1:5">
       <c r="A877" t="s">
         <v>75</v>
       </c>
@@ -34662,7 +34662,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="878" spans="1:8">
+    <row r="878" spans="1:7">
       <c r="A878" t="s">
         <v>75</v>
       </c>
@@ -34685,7 +34685,7 @@
         <v>347001</v>
       </c>
     </row>
-    <row r="879" spans="1:8">
+    <row r="879" spans="1:7">
       <c r="A879" t="s">
         <v>75</v>
       </c>
@@ -34705,7 +34705,7 @@
         <v>347002</v>
       </c>
     </row>
-    <row r="880" spans="1:8">
+    <row r="880" spans="1:7">
       <c r="A880" t="s">
         <v>75</v>
       </c>
@@ -34748,7 +34748,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="882" spans="1:8">
+    <row r="882" spans="1:7">
       <c r="A882" t="s">
         <v>75</v>
       </c>
@@ -34837,7 +34837,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="886" spans="1:8">
+    <row r="886" spans="1:7">
       <c r="A886" t="s">
         <v>75</v>
       </c>
@@ -34857,7 +34857,7 @@
         <v>347009</v>
       </c>
     </row>
-    <row r="887" spans="1:8">
+    <row r="887" spans="1:5">
       <c r="A887" t="s">
         <v>80</v>
       </c>
@@ -34874,7 +34874,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="888" spans="1:8">
+    <row r="888" spans="1:7">
       <c r="A888" t="s">
         <v>80</v>
       </c>
@@ -34894,7 +34894,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="889" spans="1:8">
+    <row r="889" spans="1:7">
       <c r="A889" t="s">
         <v>80</v>
       </c>
@@ -34914,7 +34914,7 @@
         <v>750011</v>
       </c>
     </row>
-    <row r="890" spans="1:8">
+    <row r="890" spans="1:7">
       <c r="A890" t="s">
         <v>80</v>
       </c>
@@ -34934,7 +34934,7 @@
         <v>750001</v>
       </c>
     </row>
-    <row r="891" spans="1:8">
+    <row r="891" spans="1:7">
       <c r="A891" t="s">
         <v>80</v>
       </c>
@@ -34954,7 +34954,7 @@
         <v>750002</v>
       </c>
     </row>
-    <row r="892" spans="1:8">
+    <row r="892" spans="1:7">
       <c r="A892" t="s">
         <v>80</v>
       </c>
@@ -34974,7 +34974,7 @@
         <v>750003</v>
       </c>
     </row>
-    <row r="893" spans="1:8">
+    <row r="893" spans="1:7">
       <c r="A893" t="s">
         <v>80</v>
       </c>
@@ -34994,7 +34994,7 @@
         <v>750004</v>
       </c>
     </row>
-    <row r="894" spans="1:8">
+    <row r="894" spans="1:7">
       <c r="A894" t="s">
         <v>80</v>
       </c>
@@ -35014,7 +35014,7 @@
         <v>750005</v>
       </c>
     </row>
-    <row r="895" spans="1:8">
+    <row r="895" spans="1:7">
       <c r="A895" t="s">
         <v>80</v>
       </c>
@@ -35034,7 +35034,7 @@
         <v>750006</v>
       </c>
     </row>
-    <row r="896" spans="1:8">
+    <row r="896" spans="1:7">
       <c r="A896" t="s">
         <v>80</v>
       </c>
@@ -35054,7 +35054,7 @@
         <v>750007</v>
       </c>
     </row>
-    <row r="897" spans="1:8">
+    <row r="897" spans="1:7">
       <c r="A897" t="s">
         <v>80</v>
       </c>
@@ -35074,7 +35074,7 @@
         <v>750008</v>
       </c>
     </row>
-    <row r="898" spans="1:8">
+    <row r="898" spans="1:7">
       <c r="A898" t="s">
         <v>80</v>
       </c>
@@ -35094,7 +35094,7 @@
         <v>750009</v>
       </c>
     </row>
-    <row r="899" spans="1:8">
+    <row r="899" spans="1:7">
       <c r="A899" t="s">
         <v>80</v>
       </c>
@@ -35114,7 +35114,7 @@
         <v>750010</v>
       </c>
     </row>
-    <row r="900" spans="1:8">
+    <row r="900" spans="1:5">
       <c r="A900" t="s">
         <v>82</v>
       </c>
@@ -35131,7 +35131,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="901" spans="1:8">
+    <row r="901" spans="1:7">
       <c r="A901" t="s">
         <v>82</v>
       </c>
@@ -35151,7 +35151,7 @@
         <v>752000</v>
       </c>
     </row>
-    <row r="902" spans="1:8">
+    <row r="902" spans="1:7">
       <c r="A902" t="s">
         <v>82</v>
       </c>
@@ -35174,7 +35174,7 @@
         <v>752001</v>
       </c>
     </row>
-    <row r="903" spans="1:8">
+    <row r="903" spans="1:7">
       <c r="A903" t="s">
         <v>82</v>
       </c>
@@ -35197,7 +35197,7 @@
         <v>752002</v>
       </c>
     </row>
-    <row r="904" spans="1:8">
+    <row r="904" spans="1:7">
       <c r="A904" t="s">
         <v>82</v>
       </c>
@@ -35217,7 +35217,7 @@
         <v>752003</v>
       </c>
     </row>
-    <row r="905" spans="1:8">
+    <row r="905" spans="1:7">
       <c r="A905" t="s">
         <v>82</v>
       </c>
@@ -35237,7 +35237,7 @@
         <v>752004</v>
       </c>
     </row>
-    <row r="906" spans="1:8">
+    <row r="906" spans="1:7">
       <c r="A906" t="s">
         <v>82</v>
       </c>
@@ -35257,7 +35257,7 @@
         <v>752005</v>
       </c>
     </row>
-    <row r="907" spans="1:8">
+    <row r="907" spans="1:5">
       <c r="A907" t="s">
         <v>83</v>
       </c>
@@ -35274,7 +35274,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="908" spans="1:8">
+    <row r="908" spans="1:7">
       <c r="A908" t="s">
         <v>83</v>
       </c>
@@ -35297,7 +35297,7 @@
         <v>800001</v>
       </c>
     </row>
-    <row r="909" spans="1:8">
+    <row r="909" spans="1:7">
       <c r="A909" t="s">
         <v>83</v>
       </c>
@@ -35317,7 +35317,7 @@
         <v>800002</v>
       </c>
     </row>
-    <row r="910" spans="1:8">
+    <row r="910" spans="1:7">
       <c r="A910" t="s">
         <v>83</v>
       </c>
@@ -35728,7 +35728,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="928" spans="1:8">
+    <row r="928" spans="1:5">
       <c r="A928" t="s">
         <v>85</v>
       </c>
@@ -35745,7 +35745,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="929" spans="1:8">
+    <row r="929" spans="1:7">
       <c r="A929" t="s">
         <v>85</v>
       </c>
@@ -35768,7 +35768,7 @@
         <v>802001</v>
       </c>
     </row>
-    <row r="930" spans="1:8">
+    <row r="930" spans="1:7">
       <c r="A930" t="s">
         <v>85</v>
       </c>
@@ -35788,7 +35788,7 @@
         <v>802002</v>
       </c>
     </row>
-    <row r="931" spans="1:8">
+    <row r="931" spans="1:7">
       <c r="A931" t="s">
         <v>85</v>
       </c>
@@ -39994,7 +39994,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1114" spans="1:8">
+    <row r="1114" spans="1:5">
       <c r="A1114" t="s">
         <v>86</v>
       </c>
@@ -40011,7 +40011,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1115" spans="1:8">
+    <row r="1115" spans="1:7">
       <c r="A1115" t="s">
         <v>86</v>
       </c>
@@ -40034,7 +40034,7 @@
         <v>803001</v>
       </c>
     </row>
-    <row r="1116" spans="1:8">
+    <row r="1116" spans="1:7">
       <c r="A1116" t="s">
         <v>86</v>
       </c>
@@ -40054,7 +40054,7 @@
         <v>803002</v>
       </c>
     </row>
-    <row r="1117" spans="1:8">
+    <row r="1117" spans="1:7">
       <c r="A1117" t="s">
         <v>86</v>
       </c>
@@ -42972,7 +42972,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1244" spans="1:8">
+    <row r="1244" spans="1:5">
       <c r="A1244" t="s">
         <v>87</v>
       </c>
@@ -42989,7 +42989,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1245" spans="1:8">
+    <row r="1245" spans="1:7">
       <c r="A1245" t="s">
         <v>87</v>
       </c>
@@ -43012,7 +43012,7 @@
         <v>804001</v>
       </c>
     </row>
-    <row r="1246" spans="1:8">
+    <row r="1246" spans="1:7">
       <c r="A1246" t="s">
         <v>87</v>
       </c>
@@ -43032,7 +43032,7 @@
         <v>804002</v>
       </c>
     </row>
-    <row r="1247" spans="1:8">
+    <row r="1247" spans="1:7">
       <c r="A1247" t="s">
         <v>87</v>
       </c>
@@ -45306,7 +45306,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1346" spans="1:8">
+    <row r="1346" spans="1:5">
       <c r="A1346" t="s">
         <v>88</v>
       </c>
@@ -45323,7 +45323,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1347" spans="1:8">
+    <row r="1347" spans="1:7">
       <c r="A1347" t="s">
         <v>88</v>
       </c>
@@ -45346,7 +45346,7 @@
         <v>805001</v>
       </c>
     </row>
-    <row r="1348" spans="1:8">
+    <row r="1348" spans="1:7">
       <c r="A1348" t="s">
         <v>88</v>
       </c>
@@ -45366,7 +45366,7 @@
         <v>805002</v>
       </c>
     </row>
-    <row r="1349" spans="1:8">
+    <row r="1349" spans="1:7">
       <c r="A1349" t="s">
         <v>88</v>
       </c>
@@ -47502,7 +47502,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1442" spans="1:8">
+    <row r="1442" spans="1:5">
       <c r="A1442" t="s">
         <v>89</v>
       </c>
@@ -47519,7 +47519,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1443" spans="1:8">
+    <row r="1443" spans="1:7">
       <c r="A1443" t="s">
         <v>89</v>
       </c>
@@ -47542,7 +47542,7 @@
         <v>807001</v>
       </c>
     </row>
-    <row r="1444" spans="1:8">
+    <row r="1444" spans="1:7">
       <c r="A1444" t="s">
         <v>89</v>
       </c>
@@ -47562,7 +47562,7 @@
         <v>807002</v>
       </c>
     </row>
-    <row r="1445" spans="1:8">
+    <row r="1445" spans="1:7">
       <c r="A1445" t="s">
         <v>89</v>
       </c>
@@ -50894,7 +50894,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1590" spans="1:8">
+    <row r="1590" spans="1:5">
       <c r="A1590" t="s">
         <v>90</v>
       </c>
@@ -50911,7 +50911,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1591" spans="1:8">
+    <row r="1591" spans="1:7">
       <c r="A1591" t="s">
         <v>90</v>
       </c>
@@ -50934,7 +50934,7 @@
         <v>808001</v>
       </c>
     </row>
-    <row r="1592" spans="1:8">
+    <row r="1592" spans="1:7">
       <c r="A1592" t="s">
         <v>90</v>
       </c>
@@ -50954,7 +50954,7 @@
         <v>808002</v>
       </c>
     </row>
-    <row r="1593" spans="1:8">
+    <row r="1593" spans="1:7">
       <c r="A1593" t="s">
         <v>90</v>
       </c>
@@ -54424,7 +54424,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1744" spans="1:8">
+    <row r="1744" spans="1:5">
       <c r="A1744" t="s">
         <v>91</v>
       </c>
@@ -54441,7 +54441,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1745" spans="1:8">
+    <row r="1745" spans="1:7">
       <c r="A1745" t="s">
         <v>91</v>
       </c>
@@ -54464,7 +54464,7 @@
         <v>809001</v>
       </c>
     </row>
-    <row r="1746" spans="1:8">
+    <row r="1746" spans="1:7">
       <c r="A1746" t="s">
         <v>91</v>
       </c>
@@ -54484,7 +54484,7 @@
         <v>809002</v>
       </c>
     </row>
-    <row r="1747" spans="1:8">
+    <row r="1747" spans="1:7">
       <c r="A1747" t="s">
         <v>91</v>
       </c>
@@ -54826,7 +54826,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1762" spans="1:8">
+    <row r="1762" spans="1:5">
       <c r="A1762" t="s">
         <v>92</v>
       </c>
@@ -54843,7 +54843,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1763" spans="1:8">
+    <row r="1763" spans="1:7">
       <c r="A1763" t="s">
         <v>92</v>
       </c>
@@ -54866,7 +54866,7 @@
         <v>810001</v>
       </c>
     </row>
-    <row r="1764" spans="1:8">
+    <row r="1764" spans="1:7">
       <c r="A1764" t="s">
         <v>92</v>
       </c>
@@ -54886,7 +54886,7 @@
         <v>810002</v>
       </c>
     </row>
-    <row r="1765" spans="1:8">
+    <row r="1765" spans="1:7">
       <c r="A1765" t="s">
         <v>92</v>
       </c>
@@ -55918,7 +55918,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1810" spans="1:8">
+    <row r="1810" spans="1:5">
       <c r="A1810" t="s">
         <v>94</v>
       </c>
@@ -55935,7 +55935,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1811" spans="1:8">
+    <row r="1811" spans="1:7">
       <c r="A1811" t="s">
         <v>94</v>
       </c>
@@ -55955,7 +55955,7 @@
         <v>812001</v>
       </c>
     </row>
-    <row r="1812" spans="1:8">
+    <row r="1812" spans="1:7">
       <c r="A1812" t="s">
         <v>94</v>
       </c>
@@ -55975,7 +55975,7 @@
         <v>812002</v>
       </c>
     </row>
-    <row r="1813" spans="1:8">
+    <row r="1813" spans="1:7">
       <c r="A1813" t="s">
         <v>94</v>
       </c>
@@ -55995,7 +55995,7 @@
         <v>812003</v>
       </c>
     </row>
-    <row r="1814" spans="1:8">
+    <row r="1814" spans="1:7">
       <c r="A1814" t="s">
         <v>94</v>
       </c>
@@ -56064,7 +56064,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1817" spans="1:8">
+    <row r="1817" spans="1:5">
       <c r="A1817" t="s">
         <v>93</v>
       </c>
@@ -56081,7 +56081,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1818" spans="1:8">
+    <row r="1818" spans="1:7">
       <c r="A1818" t="s">
         <v>93</v>
       </c>
@@ -56104,7 +56104,7 @@
         <v>814001</v>
       </c>
     </row>
-    <row r="1819" spans="1:8">
+    <row r="1819" spans="1:7">
       <c r="A1819" t="s">
         <v>93</v>
       </c>
@@ -56124,7 +56124,7 @@
         <v>814002</v>
       </c>
     </row>
-    <row r="1820" spans="1:8">
+    <row r="1820" spans="1:7">
       <c r="A1820" t="s">
         <v>93</v>
       </c>
@@ -57938,7 +57938,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1899" spans="1:8">
+    <row r="1899" spans="1:5">
       <c r="A1899" t="s">
         <v>96</v>
       </c>
@@ -57955,7 +57955,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1900" spans="1:8">
+    <row r="1900" spans="1:7">
       <c r="A1900" t="s">
         <v>96</v>
       </c>
@@ -57978,7 +57978,7 @@
         <v>760001</v>
       </c>
     </row>
-    <row r="1901" spans="1:8">
+    <row r="1901" spans="1:7">
       <c r="A1901" t="s">
         <v>96</v>
       </c>
@@ -57998,7 +57998,7 @@
         <v>760002</v>
       </c>
     </row>
-    <row r="1902" spans="1:8">
+    <row r="1902" spans="1:7">
       <c r="A1902" t="s">
         <v>96</v>
       </c>
@@ -58018,7 +58018,7 @@
         <v>760003</v>
       </c>
     </row>
-    <row r="1903" spans="1:8">
+    <row r="1903" spans="1:7">
       <c r="A1903" t="s">
         <v>96</v>
       </c>
@@ -58141,7 +58141,7 @@
         <v>760009</v>
       </c>
     </row>
-    <row r="1909" spans="1:7">
+    <row r="1909" spans="1:5">
       <c r="A1909" t="s">
         <v>102</v>
       </c>
@@ -58381,7 +58381,7 @@
         <v>703011</v>
       </c>
     </row>
-    <row r="1921" spans="1:8">
+    <row r="1921" spans="1:7">
       <c r="A1921" t="s">
         <v>102</v>
       </c>
@@ -58401,7 +58401,7 @@
         <v>703012</v>
       </c>
     </row>
-    <row r="1922" spans="1:8">
+    <row r="1922" spans="1:7">
       <c r="A1922" t="s">
         <v>102</v>
       </c>
@@ -58444,7 +58444,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1924" spans="1:8">
+    <row r="1924" spans="1:7">
       <c r="A1924" t="s">
         <v>102</v>
       </c>
@@ -58487,7 +58487,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1926" spans="1:8">
+    <row r="1926" spans="1:7">
       <c r="A1926" t="s">
         <v>102</v>
       </c>
@@ -58507,7 +58507,7 @@
         <v>703017</v>
       </c>
     </row>
-    <row r="1927" spans="1:8">
+    <row r="1927" spans="1:7">
       <c r="A1927" t="s">
         <v>102</v>
       </c>
@@ -58527,7 +58527,7 @@
         <v>703018</v>
       </c>
     </row>
-    <row r="1928" spans="1:8">
+    <row r="1928" spans="1:7">
       <c r="A1928" t="s">
         <v>102</v>
       </c>
@@ -58570,7 +58570,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1930" spans="1:8">
+    <row r="1930" spans="1:7">
       <c r="A1930" t="s">
         <v>102</v>
       </c>
@@ -58613,7 +58613,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1932" spans="1:8">
+    <row r="1932" spans="1:7">
       <c r="A1932" t="s">
         <v>102</v>
       </c>
@@ -58633,7 +58633,7 @@
         <v>703023</v>
       </c>
     </row>
-    <row r="1933" spans="1:8">
+    <row r="1933" spans="1:7">
       <c r="A1933" t="s">
         <v>102</v>
       </c>
@@ -58653,7 +58653,7 @@
         <v>703024</v>
       </c>
     </row>
-    <row r="1934" spans="1:8">
+    <row r="1934" spans="1:7">
       <c r="A1934" t="s">
         <v>102</v>
       </c>
@@ -58673,7 +58673,7 @@
         <v>703025</v>
       </c>
     </row>
-    <row r="1935" spans="1:8">
+    <row r="1935" spans="1:7">
       <c r="A1935" t="s">
         <v>102</v>
       </c>
@@ -58693,7 +58693,7 @@
         <v>703026</v>
       </c>
     </row>
-    <row r="1936" spans="1:8">
+    <row r="1936" spans="1:7">
       <c r="A1936" t="s">
         <v>102</v>
       </c>
@@ -58713,7 +58713,7 @@
         <v>703027</v>
       </c>
     </row>
-    <row r="1937" spans="1:8">
+    <row r="1937" spans="1:7">
       <c r="A1937" t="s">
         <v>102</v>
       </c>
@@ -58733,7 +58733,7 @@
         <v>703028</v>
       </c>
     </row>
-    <row r="1938" spans="1:8">
+    <row r="1938" spans="1:7">
       <c r="A1938" t="s">
         <v>102</v>
       </c>
@@ -58753,7 +58753,7 @@
         <v>703029</v>
       </c>
     </row>
-    <row r="1939" spans="1:8">
+    <row r="1939" spans="1:7">
       <c r="A1939" t="s">
         <v>102</v>
       </c>
@@ -58773,7 +58773,7 @@
         <v>703030</v>
       </c>
     </row>
-    <row r="1940" spans="1:8">
+    <row r="1940" spans="1:5">
       <c r="A1940" t="s">
         <v>103</v>
       </c>
@@ -58790,7 +58790,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1941" spans="1:8">
+    <row r="1941" spans="1:7">
       <c r="A1941" t="s">
         <v>103</v>
       </c>
@@ -59089,7 +59089,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="1954" spans="1:8">
+    <row r="1954" spans="1:5">
       <c r="A1954" t="s">
         <v>104</v>
       </c>
@@ -59106,7 +59106,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1955" spans="1:8">
+    <row r="1955" spans="1:7">
       <c r="A1955" t="s">
         <v>104</v>
       </c>
@@ -59126,7 +59126,7 @@
         <v>710001</v>
       </c>
     </row>
-    <row r="1956" spans="1:8">
+    <row r="1956" spans="1:7">
       <c r="A1956" t="s">
         <v>104</v>
       </c>
@@ -59172,7 +59172,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1958" spans="1:8">
+    <row r="1958" spans="1:7">
       <c r="A1958" t="s">
         <v>104</v>
       </c>
@@ -59192,7 +59192,7 @@
         <v>710004</v>
       </c>
     </row>
-    <row r="1959" spans="1:8">
+    <row r="1959" spans="1:5">
       <c r="A1959" t="s">
         <v>106</v>
       </c>
@@ -59209,7 +59209,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1960" spans="1:8">
+    <row r="1960" spans="1:7">
       <c r="A1960" t="s">
         <v>106</v>
       </c>
@@ -59232,7 +59232,7 @@
         <v>705001</v>
       </c>
     </row>
-    <row r="1961" spans="1:8">
+    <row r="1961" spans="1:7">
       <c r="A1961" t="s">
         <v>106</v>
       </c>
@@ -59367,7 +59367,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="1967" spans="1:8">
+    <row r="1967" spans="1:5">
       <c r="A1967" t="s">
         <v>107</v>
       </c>
@@ -59384,7 +59384,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1968" spans="1:8">
+    <row r="1968" spans="1:7">
       <c r="A1968" t="s">
         <v>107</v>
       </c>
@@ -59407,7 +59407,7 @@
         <v>706001</v>
       </c>
     </row>
-    <row r="1969" spans="1:8">
+    <row r="1969" spans="1:7">
       <c r="A1969" t="s">
         <v>107</v>
       </c>
@@ -59427,7 +59427,7 @@
         <v>706002</v>
       </c>
     </row>
-    <row r="1970" spans="1:8">
+    <row r="1970" spans="1:7">
       <c r="A1970" t="s">
         <v>107</v>
       </c>
@@ -59493,7 +59493,7 @@
         <v>3365</v>
       </c>
     </row>
-    <row r="1973" spans="1:8">
+    <row r="1973" spans="1:5">
       <c r="A1973" t="s">
         <v>108</v>
       </c>
@@ -59510,7 +59510,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1974" spans="1:8">
+    <row r="1974" spans="1:7">
       <c r="A1974" t="s">
         <v>108</v>
       </c>
@@ -59533,7 +59533,7 @@
         <v>707001</v>
       </c>
     </row>
-    <row r="1975" spans="1:8">
+    <row r="1975" spans="1:7">
       <c r="A1975" t="s">
         <v>108</v>
       </c>
@@ -59553,7 +59553,7 @@
         <v>707002</v>
       </c>
     </row>
-    <row r="1976" spans="1:8">
+    <row r="1976" spans="1:7">
       <c r="A1976" t="s">
         <v>108</v>
       </c>
@@ -59573,7 +59573,7 @@
         <v>707003</v>
       </c>
     </row>
-    <row r="1977" spans="1:8">
+    <row r="1977" spans="1:7">
       <c r="A1977" t="s">
         <v>108</v>
       </c>
@@ -59593,7 +59593,7 @@
         <v>707004</v>
       </c>
     </row>
-    <row r="1978" spans="1:8">
+    <row r="1978" spans="1:7">
       <c r="A1978" t="s">
         <v>108</v>
       </c>
@@ -59613,7 +59613,7 @@
         <v>707005</v>
       </c>
     </row>
-    <row r="1979" spans="1:8">
+    <row r="1979" spans="1:7">
       <c r="A1979" t="s">
         <v>108</v>
       </c>
@@ -59633,7 +59633,7 @@
         <v>707006</v>
       </c>
     </row>
-    <row r="1980" spans="1:8">
+    <row r="1980" spans="1:7">
       <c r="A1980" t="s">
         <v>108</v>
       </c>
@@ -59653,7 +59653,7 @@
         <v>707007</v>
       </c>
     </row>
-    <row r="1981" spans="1:8">
+    <row r="1981" spans="1:7">
       <c r="A1981" t="s">
         <v>108</v>
       </c>
@@ -59673,7 +59673,7 @@
         <v>707008</v>
       </c>
     </row>
-    <row r="1982" spans="1:8">
+    <row r="1982" spans="1:7">
       <c r="A1982" t="s">
         <v>108</v>
       </c>
@@ -59693,7 +59693,7 @@
         <v>707009</v>
       </c>
     </row>
-    <row r="1983" spans="1:8">
+    <row r="1983" spans="1:7">
       <c r="A1983" t="s">
         <v>108</v>
       </c>
@@ -59805,7 +59805,7 @@
         <v>3391</v>
       </c>
     </row>
-    <row r="1988" spans="1:8">
+    <row r="1988" spans="1:5">
       <c r="A1988" t="s">
         <v>98</v>
       </c>
@@ -59822,7 +59822,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1989" spans="1:8">
+    <row r="1989" spans="1:7">
       <c r="A1989" t="s">
         <v>98</v>
       </c>
@@ -59842,7 +59842,7 @@
         <v>708001</v>
       </c>
     </row>
-    <row r="1990" spans="1:8">
+    <row r="1990" spans="1:7">
       <c r="A1990" t="s">
         <v>98</v>
       </c>
@@ -59865,7 +59865,7 @@
         <v>708002</v>
       </c>
     </row>
-    <row r="1991" spans="1:8">
+    <row r="1991" spans="1:7">
       <c r="A1991" t="s">
         <v>98</v>
       </c>
@@ -59885,7 +59885,7 @@
         <v>708003</v>
       </c>
     </row>
-    <row r="1992" spans="1:8">
+    <row r="1992" spans="1:7">
       <c r="A1992" t="s">
         <v>98</v>
       </c>
@@ -59905,7 +59905,7 @@
         <v>708004</v>
       </c>
     </row>
-    <row r="1993" spans="1:8">
+    <row r="1993" spans="1:7">
       <c r="A1993" t="s">
         <v>98</v>
       </c>
@@ -59925,7 +59925,7 @@
         <v>708005</v>
       </c>
     </row>
-    <row r="1994" spans="1:8">
+    <row r="1994" spans="1:7">
       <c r="A1994" t="s">
         <v>98</v>
       </c>
@@ -59945,7 +59945,7 @@
         <v>708006</v>
       </c>
     </row>
-    <row r="1995" spans="1:8">
+    <row r="1995" spans="1:7">
       <c r="A1995" t="s">
         <v>98</v>
       </c>
@@ -59965,7 +59965,7 @@
         <v>708007</v>
       </c>
     </row>
-    <row r="1996" spans="1:8">
+    <row r="1996" spans="1:7">
       <c r="A1996" t="s">
         <v>98</v>
       </c>
@@ -59985,7 +59985,7 @@
         <v>708008</v>
       </c>
     </row>
-    <row r="1997" spans="1:8">
+    <row r="1997" spans="1:7">
       <c r="A1997" t="s">
         <v>98</v>
       </c>
@@ -60005,7 +60005,7 @@
         <v>708009</v>
       </c>
     </row>
-    <row r="1998" spans="1:8">
+    <row r="1998" spans="1:7">
       <c r="A1998" t="s">
         <v>98</v>
       </c>
@@ -60025,7 +60025,7 @@
         <v>708010</v>
       </c>
     </row>
-    <row r="1999" spans="1:8">
+    <row r="1999" spans="1:5">
       <c r="A1999" t="s">
         <v>109</v>
       </c>
@@ -60042,7 +60042,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2000" spans="1:8">
+    <row r="2000" spans="1:7">
       <c r="A2000" t="s">
         <v>109</v>
       </c>
@@ -60062,7 +60062,7 @@
         <v>702001</v>
       </c>
     </row>
-    <row r="2001" spans="1:8">
+    <row r="2001" spans="1:7">
       <c r="A2001" t="s">
         <v>109</v>
       </c>
@@ -60082,7 +60082,7 @@
         <v>702002</v>
       </c>
     </row>
-    <row r="2002" spans="1:8">
+    <row r="2002" spans="1:7">
       <c r="A2002" t="s">
         <v>109</v>
       </c>
@@ -60102,7 +60102,7 @@
         <v>702003</v>
       </c>
     </row>
-    <row r="2003" spans="1:8">
+    <row r="2003" spans="1:7">
       <c r="A2003" t="s">
         <v>109</v>
       </c>
@@ -60145,7 +60145,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2005" spans="1:8">
+    <row r="2005" spans="1:7">
       <c r="A2005" t="s">
         <v>109</v>
       </c>
@@ -60165,7 +60165,7 @@
         <v>702006</v>
       </c>
     </row>
-    <row r="2006" spans="1:8">
+    <row r="2006" spans="1:5">
       <c r="A2006" t="s">
         <v>105</v>
       </c>
@@ -60182,7 +60182,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2007" spans="1:8">
+    <row r="2007" spans="1:7">
       <c r="A2007" t="s">
         <v>105</v>
       </c>
@@ -60202,7 +60202,7 @@
         <v>701001</v>
       </c>
     </row>
-    <row r="2008" spans="1:8">
+    <row r="2008" spans="1:7">
       <c r="A2008" t="s">
         <v>105</v>
       </c>
@@ -60225,7 +60225,7 @@
         <v>701002</v>
       </c>
     </row>
-    <row r="2009" spans="1:8">
+    <row r="2009" spans="1:7">
       <c r="A2009" t="s">
         <v>105</v>
       </c>
@@ -60245,7 +60245,7 @@
         <v>701003</v>
       </c>
     </row>
-    <row r="2010" spans="1:8">
+    <row r="2010" spans="1:7">
       <c r="A2010" t="s">
         <v>105</v>
       </c>
@@ -60265,7 +60265,7 @@
         <v>701004</v>
       </c>
     </row>
-    <row r="2011" spans="1:8">
+    <row r="2011" spans="1:7">
       <c r="A2011" t="s">
         <v>105</v>
       </c>
@@ -60331,7 +60331,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="2014" spans="1:8">
+    <row r="2014" spans="1:7">
       <c r="A2014" t="s">
         <v>105</v>
       </c>
@@ -60351,7 +60351,7 @@
         <v>701008</v>
       </c>
     </row>
-    <row r="2015" spans="1:8">
+    <row r="2015" spans="1:5">
       <c r="A2015" t="s">
         <v>100</v>
       </c>
@@ -60368,7 +60368,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2016" spans="1:8">
+    <row r="2016" spans="1:7">
       <c r="A2016" t="s">
         <v>100</v>
       </c>
@@ -60391,7 +60391,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="2017" spans="1:8">
+    <row r="2017" spans="1:7">
       <c r="A2017" t="s">
         <v>100</v>
       </c>
@@ -60411,7 +60411,7 @@
         <v>700001</v>
       </c>
     </row>
-    <row r="2018" spans="1:8">
+    <row r="2018" spans="1:7">
       <c r="A2018" t="s">
         <v>100</v>
       </c>
@@ -60431,7 +60431,7 @@
         <v>700002</v>
       </c>
     </row>
-    <row r="2019" spans="1:8">
+    <row r="2019" spans="1:7">
       <c r="A2019" t="s">
         <v>100</v>
       </c>
@@ -60451,7 +60451,7 @@
         <v>700003</v>
       </c>
     </row>
-    <row r="2020" spans="1:8">
+    <row r="2020" spans="1:5">
       <c r="A2020" t="s">
         <v>110</v>
       </c>
@@ -60468,7 +60468,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2021" spans="1:8">
+    <row r="2021" spans="1:7">
       <c r="A2021" t="s">
         <v>110</v>
       </c>
@@ -60511,7 +60511,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2023" spans="1:8">
+    <row r="2023" spans="1:7">
       <c r="A2023" t="s">
         <v>110</v>
       </c>
@@ -60531,7 +60531,7 @@
         <v>502002</v>
       </c>
     </row>
-    <row r="2024" spans="1:8">
+    <row r="2024" spans="1:7">
       <c r="A2024" t="s">
         <v>110</v>
       </c>
@@ -60551,7 +60551,7 @@
         <v>502003</v>
       </c>
     </row>
-    <row r="2025" spans="1:8">
+    <row r="2025" spans="1:7">
       <c r="A2025" t="s">
         <v>110</v>
       </c>
@@ -60571,7 +60571,7 @@
         <v>502037</v>
       </c>
     </row>
-    <row r="2026" spans="1:8">
+    <row r="2026" spans="1:7">
       <c r="A2026" t="s">
         <v>110</v>
       </c>
@@ -60591,7 +60591,7 @@
         <v>502004</v>
       </c>
     </row>
-    <row r="2027" spans="1:8">
+    <row r="2027" spans="1:7">
       <c r="A2027" t="s">
         <v>110</v>
       </c>
@@ -60611,7 +60611,7 @@
         <v>502005</v>
       </c>
     </row>
-    <row r="2028" spans="1:8">
+    <row r="2028" spans="1:7">
       <c r="A2028" t="s">
         <v>110</v>
       </c>
@@ -60654,7 +60654,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2030" spans="1:8">
+    <row r="2030" spans="1:7">
       <c r="A2030" t="s">
         <v>110</v>
       </c>
@@ -60720,7 +60720,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2033" spans="1:8">
+    <row r="2033" spans="1:7">
       <c r="A2033" t="s">
         <v>110</v>
       </c>
@@ -60740,7 +60740,7 @@
         <v>502011</v>
       </c>
     </row>
-    <row r="2034" spans="1:8">
+    <row r="2034" spans="1:7">
       <c r="A2034" t="s">
         <v>110</v>
       </c>
@@ -60760,7 +60760,7 @@
         <v>502012</v>
       </c>
     </row>
-    <row r="2035" spans="1:8">
+    <row r="2035" spans="1:7">
       <c r="A2035" t="s">
         <v>110</v>
       </c>
@@ -60780,7 +60780,7 @@
         <v>502034</v>
       </c>
     </row>
-    <row r="2036" spans="1:8">
+    <row r="2036" spans="1:7">
       <c r="A2036" t="s">
         <v>110</v>
       </c>
@@ -60846,7 +60846,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2039" spans="1:8">
+    <row r="2039" spans="1:7">
       <c r="A2039" t="s">
         <v>110</v>
       </c>
@@ -60889,7 +60889,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2041" spans="1:8">
+    <row r="2041" spans="1:7">
       <c r="A2041" t="s">
         <v>110</v>
       </c>
@@ -60932,7 +60932,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2043" spans="1:8">
+    <row r="2043" spans="1:7">
       <c r="A2043" t="s">
         <v>110</v>
       </c>
@@ -60952,7 +60952,7 @@
         <v>502033</v>
       </c>
     </row>
-    <row r="2044" spans="1:8">
+    <row r="2044" spans="1:7">
       <c r="A2044" t="s">
         <v>110</v>
       </c>
@@ -60972,7 +60972,7 @@
         <v>502020</v>
       </c>
     </row>
-    <row r="2045" spans="1:8">
+    <row r="2045" spans="1:7">
       <c r="A2045" t="s">
         <v>110</v>
       </c>
@@ -61038,7 +61038,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2048" spans="1:8">
+    <row r="2048" spans="1:7">
       <c r="A2048" t="s">
         <v>110</v>
       </c>
@@ -61558,7 +61558,7 @@
         <v>502055</v>
       </c>
     </row>
-    <row r="2074" spans="1:7">
+    <row r="2074" spans="1:5">
       <c r="A2074" t="s">
         <v>112</v>
       </c>
@@ -61698,7 +61698,7 @@
         <v>503005</v>
       </c>
     </row>
-    <row r="2081" spans="1:8">
+    <row r="2081" spans="1:7">
       <c r="A2081" t="s">
         <v>112</v>
       </c>
@@ -61718,7 +61718,7 @@
         <v>503006</v>
       </c>
     </row>
-    <row r="2082" spans="1:8">
+    <row r="2082" spans="1:7">
       <c r="A2082" t="s">
         <v>112</v>
       </c>
@@ -61738,7 +61738,7 @@
         <v>503007</v>
       </c>
     </row>
-    <row r="2083" spans="1:8">
+    <row r="2083" spans="1:7">
       <c r="A2083" t="s">
         <v>112</v>
       </c>
@@ -61758,7 +61758,7 @@
         <v>503008</v>
       </c>
     </row>
-    <row r="2084" spans="1:8">
+    <row r="2084" spans="1:5">
       <c r="A2084" t="s">
         <v>113</v>
       </c>
@@ -61775,7 +61775,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2085" spans="1:8">
+    <row r="2085" spans="1:7">
       <c r="A2085" t="s">
         <v>113</v>
       </c>
@@ -61795,7 +61795,7 @@
         <v>505001</v>
       </c>
     </row>
-    <row r="2086" spans="1:8">
+    <row r="2086" spans="1:7">
       <c r="A2086" t="s">
         <v>113</v>
       </c>
@@ -61815,7 +61815,7 @@
         <v>505002</v>
       </c>
     </row>
-    <row r="2087" spans="1:8">
+    <row r="2087" spans="1:7">
       <c r="A2087" t="s">
         <v>113</v>
       </c>
@@ -61904,7 +61904,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2091" spans="1:8">
+    <row r="2091" spans="1:7">
       <c r="A2091" t="s">
         <v>113</v>
       </c>
@@ -61924,7 +61924,7 @@
         <v>505007</v>
       </c>
     </row>
-    <row r="2092" spans="1:8">
+    <row r="2092" spans="1:7">
       <c r="A2092" t="s">
         <v>113</v>
       </c>
@@ -61944,7 +61944,7 @@
         <v>505008</v>
       </c>
     </row>
-    <row r="2093" spans="1:8">
+    <row r="2093" spans="1:7">
       <c r="A2093" t="s">
         <v>113</v>
       </c>
@@ -61964,7 +61964,7 @@
         <v>505009</v>
       </c>
     </row>
-    <row r="2094" spans="1:8">
+    <row r="2094" spans="1:5">
       <c r="A2094" t="s">
         <v>114</v>
       </c>
@@ -61981,7 +61981,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2095" spans="1:8">
+    <row r="2095" spans="1:7">
       <c r="A2095" t="s">
         <v>114</v>
       </c>
@@ -62001,7 +62001,7 @@
         <v>507000</v>
       </c>
     </row>
-    <row r="2096" spans="1:8">
+    <row r="2096" spans="1:7">
       <c r="A2096" t="s">
         <v>114</v>
       </c>
@@ -62184,7 +62184,7 @@
         <v>507009</v>
       </c>
     </row>
-    <row r="2105" spans="1:7">
+    <row r="2105" spans="1:5">
       <c r="A2105" t="s">
         <v>115</v>
       </c>
@@ -62404,7 +62404,7 @@
         <v>508009</v>
       </c>
     </row>
-    <row r="2116" spans="1:7">
+    <row r="2116" spans="1:5">
       <c r="A2116" t="s">
         <v>116</v>
       </c>
@@ -62504,7 +62504,7 @@
         <v>568004</v>
       </c>
     </row>
-    <row r="2121" spans="1:7">
+    <row r="2121" spans="1:5">
       <c r="A2121" t="s">
         <v>117</v>
       </c>
@@ -63261,7 +63261,7 @@
         <v>569036</v>
       </c>
     </row>
-    <row r="2159" spans="1:7">
+    <row r="2159" spans="1:5">
       <c r="A2159" t="s">
         <v>118</v>
       </c>
@@ -63301,7 +63301,7 @@
         <v>504000</v>
       </c>
     </row>
-    <row r="2161" spans="1:8">
+    <row r="2161" spans="1:7">
       <c r="A2161" t="s">
         <v>118</v>
       </c>
@@ -63321,7 +63321,7 @@
         <v>504001</v>
       </c>
     </row>
-    <row r="2162" spans="1:8">
+    <row r="2162" spans="1:7">
       <c r="A2162" t="s">
         <v>118</v>
       </c>
@@ -63341,7 +63341,7 @@
         <v>504002</v>
       </c>
     </row>
-    <row r="2163" spans="1:8">
+    <row r="2163" spans="1:7">
       <c r="A2163" t="s">
         <v>118</v>
       </c>
@@ -63361,7 +63361,7 @@
         <v>504003</v>
       </c>
     </row>
-    <row r="2164" spans="1:8">
+    <row r="2164" spans="1:7">
       <c r="A2164" t="s">
         <v>118</v>
       </c>
@@ -63381,7 +63381,7 @@
         <v>504004</v>
       </c>
     </row>
-    <row r="2165" spans="1:8">
+    <row r="2165" spans="1:5">
       <c r="A2165" t="s">
         <v>119</v>
       </c>
@@ -63398,7 +63398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2166" spans="1:8">
+    <row r="2166" spans="1:7">
       <c r="A2166" t="s">
         <v>119</v>
       </c>
@@ -63418,7 +63418,7 @@
         <v>570001</v>
       </c>
     </row>
-    <row r="2167" spans="1:8">
+    <row r="2167" spans="1:7">
       <c r="A2167" t="s">
         <v>119</v>
       </c>
@@ -63556,7 +63556,7 @@
         <v>3384</v>
       </c>
     </row>
-    <row r="2173" spans="1:8">
+    <row r="2173" spans="1:5">
       <c r="A2173" t="s">
         <v>120</v>
       </c>
@@ -63573,7 +63573,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2174" spans="1:8">
+    <row r="2174" spans="1:7">
       <c r="A2174" t="s">
         <v>120</v>
       </c>
@@ -63593,7 +63593,7 @@
         <v>571001</v>
       </c>
     </row>
-    <row r="2175" spans="1:8">
+    <row r="2175" spans="1:7">
       <c r="A2175" t="s">
         <v>120</v>
       </c>
@@ -63613,7 +63613,7 @@
         <v>571002</v>
       </c>
     </row>
-    <row r="2176" spans="1:8">
+    <row r="2176" spans="1:7">
       <c r="A2176" t="s">
         <v>120</v>
       </c>
@@ -63633,7 +63633,7 @@
         <v>571003</v>
       </c>
     </row>
-    <row r="2177" spans="1:8">
+    <row r="2177" spans="1:7">
       <c r="A2177" t="s">
         <v>120</v>
       </c>
@@ -63699,7 +63699,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2180" spans="1:8">
+    <row r="2180" spans="1:7">
       <c r="A2180" t="s">
         <v>120</v>
       </c>
@@ -63719,7 +63719,7 @@
         <v>571007</v>
       </c>
     </row>
-    <row r="2181" spans="1:8">
+    <row r="2181" spans="1:7">
       <c r="A2181" t="s">
         <v>120</v>
       </c>
@@ -63739,7 +63739,7 @@
         <v>571008</v>
       </c>
     </row>
-    <row r="2182" spans="1:8">
+    <row r="2182" spans="1:7">
       <c r="A2182" t="s">
         <v>120</v>
       </c>
@@ -63759,7 +63759,7 @@
         <v>571009</v>
       </c>
     </row>
-    <row r="2183" spans="1:8">
+    <row r="2183" spans="1:7">
       <c r="A2183" t="s">
         <v>120</v>
       </c>
@@ -63779,7 +63779,7 @@
         <v>571010</v>
       </c>
     </row>
-    <row r="2184" spans="1:8">
+    <row r="2184" spans="1:5">
       <c r="A2184" t="s">
         <v>121</v>
       </c>
@@ -63796,7 +63796,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2185" spans="1:8">
+    <row r="2185" spans="1:7">
       <c r="A2185" t="s">
         <v>121</v>
       </c>
@@ -63816,7 +63816,7 @@
         <v>572001</v>
       </c>
     </row>
-    <row r="2186" spans="1:8">
+    <row r="2186" spans="1:7">
       <c r="A2186" t="s">
         <v>121</v>
       </c>
@@ -63905,7 +63905,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2190" spans="1:8">
+    <row r="2190" spans="1:7">
       <c r="A2190" t="s">
         <v>121</v>
       </c>
@@ -63925,7 +63925,7 @@
         <v>572006</v>
       </c>
     </row>
-    <row r="2191" spans="1:8">
+    <row r="2191" spans="1:7">
       <c r="A2191" t="s">
         <v>121</v>
       </c>
@@ -63945,7 +63945,7 @@
         <v>572007</v>
       </c>
     </row>
-    <row r="2192" spans="1:8">
+    <row r="2192" spans="1:7">
       <c r="A2192" t="s">
         <v>121</v>
       </c>
@@ -63965,7 +63965,7 @@
         <v>572008</v>
       </c>
     </row>
-    <row r="2193" spans="1:8">
+    <row r="2193" spans="1:7">
       <c r="A2193" t="s">
         <v>121</v>
       </c>
@@ -63985,7 +63985,7 @@
         <v>572009</v>
       </c>
     </row>
-    <row r="2194" spans="1:8">
+    <row r="2194" spans="1:7">
       <c r="A2194" t="s">
         <v>121</v>
       </c>
@@ -64005,7 +64005,7 @@
         <v>572010</v>
       </c>
     </row>
-    <row r="2195" spans="1:8">
+    <row r="2195" spans="1:5">
       <c r="A2195" t="s">
         <v>78</v>
       </c>
@@ -64022,7 +64022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2196" spans="1:8">
+    <row r="2196" spans="1:7">
       <c r="A2196" t="s">
         <v>78</v>
       </c>
@@ -64045,7 +64045,7 @@
         <v>602000</v>
       </c>
     </row>
-    <row r="2197" spans="1:8">
+    <row r="2197" spans="1:7">
       <c r="A2197" t="s">
         <v>78</v>
       </c>
@@ -64065,7 +64065,7 @@
         <v>602001</v>
       </c>
     </row>
-    <row r="2198" spans="1:8">
+    <row r="2198" spans="1:7">
       <c r="A2198" t="s">
         <v>78</v>
       </c>
@@ -64085,7 +64085,7 @@
         <v>602002</v>
       </c>
     </row>
-    <row r="2199" spans="1:8">
+    <row r="2199" spans="1:7">
       <c r="A2199" t="s">
         <v>78</v>
       </c>
@@ -64151,7 +64151,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2202" spans="1:8">
+    <row r="2202" spans="1:7">
       <c r="A2202" t="s">
         <v>78</v>
       </c>
@@ -64194,7 +64194,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2204" spans="1:8">
+    <row r="2204" spans="1:7">
       <c r="A2204" t="s">
         <v>78</v>
       </c>
@@ -64214,7 +64214,7 @@
         <v>602008</v>
       </c>
     </row>
-    <row r="2205" spans="1:8">
+    <row r="2205" spans="1:7">
       <c r="A2205" t="s">
         <v>78</v>
       </c>
@@ -64234,7 +64234,7 @@
         <v>602009</v>
       </c>
     </row>
-    <row r="2206" spans="1:8">
+    <row r="2206" spans="1:7">
       <c r="A2206" t="s">
         <v>78</v>
       </c>
@@ -64254,7 +64254,7 @@
         <v>602010</v>
       </c>
     </row>
-    <row r="2207" spans="1:8">
+    <row r="2207" spans="1:7">
       <c r="A2207" t="s">
         <v>78</v>
       </c>
@@ -64274,7 +64274,7 @@
         <v>602011</v>
       </c>
     </row>
-    <row r="2208" spans="1:8">
+    <row r="2208" spans="1:7">
       <c r="A2208" t="s">
         <v>78</v>
       </c>
@@ -64294,7 +64294,7 @@
         <v>602012</v>
       </c>
     </row>
-    <row r="2209" spans="1:8">
+    <row r="2209" spans="1:7">
       <c r="A2209" t="s">
         <v>78</v>
       </c>
@@ -64314,7 +64314,7 @@
         <v>602013</v>
       </c>
     </row>
-    <row r="2210" spans="1:8">
+    <row r="2210" spans="1:7">
       <c r="A2210" t="s">
         <v>78</v>
       </c>
@@ -64334,7 +64334,7 @@
         <v>602014</v>
       </c>
     </row>
-    <row r="2211" spans="1:8">
+    <row r="2211" spans="1:7">
       <c r="A2211" t="s">
         <v>78</v>
       </c>
@@ -64354,7 +64354,7 @@
         <v>602015</v>
       </c>
     </row>
-    <row r="2212" spans="1:8">
+    <row r="2212" spans="1:5">
       <c r="A2212" t="s">
         <v>79</v>
       </c>
@@ -64371,7 +64371,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2213" spans="1:8">
+    <row r="2213" spans="1:7">
       <c r="A2213" t="s">
         <v>79</v>
       </c>
@@ -64394,7 +64394,7 @@
         <v>604000</v>
       </c>
     </row>
-    <row r="2214" spans="1:8">
+    <row r="2214" spans="1:7">
       <c r="A2214" t="s">
         <v>79</v>
       </c>
@@ -64414,7 +64414,7 @@
         <v>604001</v>
       </c>
     </row>
-    <row r="2215" spans="1:8">
+    <row r="2215" spans="1:7">
       <c r="A2215" t="s">
         <v>79</v>
       </c>
@@ -64434,7 +64434,7 @@
         <v>604002</v>
       </c>
     </row>
-    <row r="2216" spans="1:8">
+    <row r="2216" spans="1:7">
       <c r="A2216" t="s">
         <v>79</v>
       </c>
@@ -64523,7 +64523,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2220" spans="1:8">
+    <row r="2220" spans="1:7">
       <c r="A2220" t="s">
         <v>79</v>
       </c>
@@ -64635,7 +64635,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2225" spans="1:8">
+    <row r="2225" spans="1:7">
       <c r="A2225" t="s">
         <v>79</v>
       </c>
@@ -64655,7 +64655,7 @@
         <v>604012</v>
       </c>
     </row>
-    <row r="2226" spans="1:8">
+    <row r="2226" spans="1:7">
       <c r="A2226" t="s">
         <v>79</v>
       </c>
@@ -64675,7 +64675,7 @@
         <v>604013</v>
       </c>
     </row>
-    <row r="2227" spans="1:8">
+    <row r="2227" spans="1:7">
       <c r="A2227" t="s">
         <v>79</v>
       </c>
@@ -64695,7 +64695,7 @@
         <v>604014</v>
       </c>
     </row>
-    <row r="2228" spans="1:8">
+    <row r="2228" spans="1:7">
       <c r="A2228" t="s">
         <v>79</v>
       </c>
@@ -64715,7 +64715,7 @@
         <v>604015</v>
       </c>
     </row>
-    <row r="2229" spans="1:8">
+    <row r="2229" spans="1:7">
       <c r="A2229" t="s">
         <v>79</v>
       </c>
@@ -64735,7 +64735,7 @@
         <v>604016</v>
       </c>
     </row>
-    <row r="2230" spans="1:8">
+    <row r="2230" spans="1:7">
       <c r="A2230" t="s">
         <v>79</v>
       </c>
@@ -64755,7 +64755,7 @@
         <v>604017</v>
       </c>
     </row>
-    <row r="2231" spans="1:8">
+    <row r="2231" spans="1:7">
       <c r="A2231" t="s">
         <v>79</v>
       </c>
@@ -64775,7 +64775,7 @@
         <v>604018</v>
       </c>
     </row>
-    <row r="2232" spans="1:8">
+    <row r="2232" spans="1:5">
       <c r="A2232" t="s">
         <v>59</v>
       </c>
@@ -64818,7 +64818,7 @@
         <v>3721</v>
       </c>
     </row>
-    <row r="2234" spans="1:8">
+    <row r="2234" spans="1:7">
       <c r="A2234" t="s">
         <v>59</v>
       </c>
@@ -64838,7 +64838,7 @@
         <v>44001</v>
       </c>
     </row>
-    <row r="2235" spans="1:8">
+    <row r="2235" spans="1:7">
       <c r="A2235" t="s">
         <v>59</v>
       </c>
@@ -64973,7 +64973,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2241" spans="1:8">
+    <row r="2241" spans="1:7">
       <c r="A2241" t="s">
         <v>59</v>
       </c>
@@ -65384,7 +65384,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2259" spans="1:8">
+    <row r="2259" spans="1:7">
       <c r="A2259" t="s">
         <v>59</v>
       </c>
@@ -65404,7 +65404,7 @@
         <v>44185</v>
       </c>
     </row>
-    <row r="2260" spans="1:8">
+    <row r="2260" spans="1:7">
       <c r="A2260" t="s">
         <v>59</v>
       </c>
@@ -67149,7 +67149,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2336" spans="1:8">
+    <row r="2336" spans="1:7">
       <c r="A2336" t="s">
         <v>59</v>
       </c>
@@ -67537,7 +67537,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2353" spans="1:8">
+    <row r="2353" spans="1:7">
       <c r="A2353" t="s">
         <v>59</v>
       </c>
@@ -67557,7 +67557,7 @@
         <v>44188</v>
       </c>
     </row>
-    <row r="2354" spans="1:8">
+    <row r="2354" spans="1:7">
       <c r="A2354" t="s">
         <v>59</v>
       </c>
@@ -68957,7 +68957,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2415" spans="1:8">
+    <row r="2415" spans="1:5">
       <c r="A2415" t="s">
         <v>61</v>
       </c>
@@ -68997,7 +68997,7 @@
         <v>3721</v>
       </c>
     </row>
-    <row r="2417" spans="1:8">
+    <row r="2417" spans="1:7">
       <c r="A2417" t="s">
         <v>61</v>
       </c>
@@ -69017,7 +69017,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="2418" spans="1:8">
+    <row r="2418" spans="1:7">
       <c r="A2418" t="s">
         <v>61</v>
       </c>
@@ -69037,7 +69037,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="2419" spans="1:8">
+    <row r="2419" spans="1:7">
       <c r="A2419" t="s">
         <v>61</v>
       </c>
@@ -69471,7 +69471,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2438" spans="1:8">
+    <row r="2438" spans="1:7">
       <c r="A2438" t="s">
         <v>61</v>
       </c>
@@ -69491,7 +69491,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="2439" spans="1:8">
+    <row r="2439" spans="1:7">
       <c r="A2439" t="s">
         <v>61</v>
       </c>
@@ -69925,7 +69925,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2458" spans="1:8">
+    <row r="2458" spans="1:7">
       <c r="A2458" t="s">
         <v>61</v>
       </c>
@@ -69945,7 +69945,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="2459" spans="1:8">
+    <row r="2459" spans="1:7">
       <c r="A2459" t="s">
         <v>61</v>
       </c>
@@ -71161,7 +71161,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="2512" spans="1:8">
+    <row r="2512" spans="1:5">
       <c r="A2512" t="s">
         <v>62</v>
       </c>
@@ -71178,7 +71178,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2513" spans="1:8">
+    <row r="2513" spans="1:7">
       <c r="A2513" t="s">
         <v>62</v>
       </c>
@@ -71198,7 +71198,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="2514" spans="1:8">
+    <row r="2514" spans="1:7">
       <c r="A2514" t="s">
         <v>62</v>
       </c>
@@ -71218,7 +71218,7 @@
         <v>48001</v>
       </c>
     </row>
-    <row r="2515" spans="1:8">
+    <row r="2515" spans="1:7">
       <c r="A2515" t="s">
         <v>62</v>
       </c>
@@ -71238,7 +71238,7 @@
         <v>48163</v>
       </c>
     </row>
-    <row r="2516" spans="1:8">
+    <row r="2516" spans="1:7">
       <c r="A2516" t="s">
         <v>62</v>
       </c>
@@ -74915,7 +74915,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2676" spans="1:8">
+    <row r="2676" spans="1:7">
       <c r="A2676" t="s">
         <v>62</v>
       </c>
@@ -74935,7 +74935,7 @@
         <v>48101</v>
       </c>
     </row>
-    <row r="2677" spans="1:8">
+    <row r="2677" spans="1:5">
       <c r="A2677" t="s">
         <v>63</v>
       </c>
@@ -74952,7 +74952,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2678" spans="1:8">
+    <row r="2678" spans="1:7">
       <c r="A2678" t="s">
         <v>63</v>
       </c>
@@ -74972,7 +74972,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="2679" spans="1:8">
+    <row r="2679" spans="1:7">
       <c r="A2679" t="s">
         <v>63</v>
       </c>
@@ -75360,7 +75360,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2696" spans="1:8">
+    <row r="2696" spans="1:7">
       <c r="A2696" t="s">
         <v>63</v>
       </c>
